--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="15690" windowHeight="14160"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -43,9 +43,6 @@
     <t>MonsterId</t>
   </si>
   <si>
-    <t>MonsterEntry</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
   </si>
   <si>
     <t>怪物Id</t>
-  </si>
-  <si>
-    <t>怪物机制</t>
   </si>
   <si>
     <t>怪物类型</t>
@@ -1236,21 +1230,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H57"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="9.775" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.88333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.275" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.5083333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.7083333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.56666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="11.5083333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.7083333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.56666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.75" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,1074 +1256,935 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:8">
+    </row>
+    <row r="5" customFormat="1" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2">
         <v>1001</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:8">
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:7">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2">
         <v>1001</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" customFormat="1" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" customFormat="1" spans="1:7">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2">
         <v>1001</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" customFormat="1" spans="1:8">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:7">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2">
         <v>1001</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" customFormat="1" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:7">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2">
         <v>1001</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" customFormat="1" spans="1:8">
+        <v>28</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:7">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" customFormat="1" spans="1:8">
+    </row>
+    <row r="11" customFormat="1" spans="1:7">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2">
         <v>1002</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" customFormat="1" spans="1:8">
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:7">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2">
         <v>1002</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:7">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2">
         <v>1002</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:8">
+        <v>22</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:7">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2">
         <v>1002</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:7">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2">
         <v>1002</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" customFormat="1" spans="1:8">
+        <v>28</v>
+      </c>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:7">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" spans="1:8">
+    </row>
+    <row r="17" customFormat="1" spans="1:7">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="2">
         <v>1003</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" spans="1:8">
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:7">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2">
         <v>1003</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" customFormat="1" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:7">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2">
         <v>1003</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:8">
+        <v>22</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:7">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="2">
         <v>1003</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:7">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" s="2">
         <v>1003</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" customFormat="1" spans="1:8">
+        <v>28</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:7">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:8">
+    </row>
+    <row r="23" customFormat="1" spans="1:7">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="2">
         <v>1004</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:8">
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:7">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2">
         <v>1004</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:7">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25" s="2">
         <v>1004</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" customFormat="1" spans="1:8">
+        <v>22</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" customFormat="1" spans="1:7">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C26" s="2">
         <v>1004</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" customFormat="1" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:7">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2">
         <v>1004</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:8">
+        <v>28</v>
+      </c>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:7">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" customFormat="1" spans="1:8">
+    </row>
+    <row r="29" customFormat="1" spans="1:7">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C29" s="2">
         <v>1005</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" customFormat="1" spans="1:8">
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:7">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30" s="2">
         <v>1006</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" customFormat="1" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:7">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31" s="2">
         <v>1007</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" customFormat="1" spans="1:8">
+        <v>22</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" customFormat="1" spans="1:7">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C32" s="2">
         <v>1008</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" customFormat="1" spans="1:8">
+        <v>25</v>
+      </c>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C33" s="2">
         <v>1009</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" customFormat="1" spans="1:8">
+        <v>28</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" customFormat="1" spans="1:7">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:8">
+    </row>
+    <row r="35" spans="1:7">
       <c r="B35" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C35" s="2">
         <v>2001</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:7">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C36" s="2">
         <v>2001</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" customFormat="1" spans="1:8">
+        <v>53</v>
+      </c>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" customFormat="1" spans="1:7">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C37" s="2">
         <v>2001</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" customFormat="1" spans="1:8">
+        <v>55</v>
+      </c>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" customFormat="1" spans="1:7">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="2">
         <v>2001</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:8">
+        <v>57</v>
+      </c>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7">
       <c r="B39" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C39" s="2">
         <v>2001</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="B41" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C41" s="2">
         <v>2002</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:7">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>2002</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" customFormat="1" spans="1:8">
+        <v>53</v>
+      </c>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" customFormat="1" spans="1:7">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2">
         <v>2002</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" customFormat="1" spans="1:8">
+        <v>55</v>
+      </c>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" spans="1:7">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C44" s="2">
         <v>2002</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" spans="1:8">
+        <v>57</v>
+      </c>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7">
       <c r="B45" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C45" s="2">
         <v>2002</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="B47" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C47" s="2">
         <v>2003</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:7">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C48" s="2">
         <v>2003</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" customFormat="1" spans="1:8">
+        <v>53</v>
+      </c>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" customFormat="1" spans="1:7">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C49" s="2">
         <v>2003</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" customFormat="1" spans="1:8">
+        <v>55</v>
+      </c>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" customFormat="1" spans="1:7">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C50" s="2">
         <v>2003</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="1:8">
+        <v>57</v>
+      </c>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7">
       <c r="B51" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2">
         <v>2003</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="B53" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C53" s="2">
         <v>2004</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:7">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>2004</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" customFormat="1" spans="1:8">
+        <v>53</v>
+      </c>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" customFormat="1" spans="1:7">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>2004</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" customFormat="1" spans="1:8">
+        <v>55</v>
+      </c>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" customFormat="1" spans="1:7">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C56" s="2">
         <v>2004</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H56" s="1"/>
-    </row>
-    <row r="57" spans="1:8">
+        <v>57</v>
+      </c>
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:7">
       <c r="B57" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C57" s="2">
         <v>2004</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15690" windowHeight="14160"/>
+    <workbookView windowWidth="16965" windowHeight="13155"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -52,6 +52,9 @@
     <t>MonsterHp</t>
   </si>
   <si>
+    <t>MonsterEntry</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
   </si>
   <si>
     <t>生命值</t>
+  </si>
+  <si>
+    <t>怪物机制</t>
   </si>
   <si>
     <t>1001001</t>
@@ -1262,139 +1268,148 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2">
         <v>1001</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6" customFormat="1" spans="1:7">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2">
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" customFormat="1" spans="1:7">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2">
         <v>1001</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8" customFormat="1" spans="1:7">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2">
         <v>1001</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" customFormat="1" spans="1:7">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2">
         <v>1001</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1"/>
     </row>
@@ -1410,95 +1425,95 @@
     <row r="11" customFormat="1" spans="1:7">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2">
         <v>1002</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" customFormat="1" spans="1:7">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2">
         <v>1002</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" customFormat="1" spans="1:7">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2">
         <v>1002</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14" customFormat="1" spans="1:7">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2">
         <v>1002</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" customFormat="1" spans="1:7">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2">
         <v>1002</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G15" s="1"/>
     </row>
@@ -1514,95 +1529,95 @@
     <row r="17" customFormat="1" spans="1:7">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2">
         <v>1003</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" customFormat="1" spans="1:7">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2">
         <v>1003</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" customFormat="1" spans="1:7">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" s="2">
         <v>1003</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" customFormat="1" spans="1:7">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2">
         <v>1003</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" customFormat="1" spans="1:7">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2">
         <v>1003</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -1618,95 +1633,95 @@
     <row r="23" customFormat="1" spans="1:7">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C23" s="2">
         <v>1004</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24" customFormat="1" spans="1:7">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C24" s="2">
         <v>1004</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25" customFormat="1" spans="1:7">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C25" s="2">
         <v>1004</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" customFormat="1" spans="1:7">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2">
         <v>1004</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" customFormat="1" spans="1:7">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2">
         <v>1004</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -1722,95 +1737,95 @@
     <row r="29" customFormat="1" spans="1:7">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C29" s="2">
         <v>1005</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" customFormat="1" spans="1:7">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2">
         <v>1006</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G30" s="1"/>
     </row>
     <row r="31" customFormat="1" spans="1:7">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2">
         <v>1007</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G31" s="1"/>
     </row>
     <row r="32" customFormat="1" spans="1:7">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C32" s="2">
         <v>1008</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G32" s="1"/>
     </row>
     <row r="33" customFormat="1" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C33" s="2">
         <v>1009</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G33" s="1"/>
     </row>
@@ -1825,366 +1840,366 @@
     </row>
     <row r="35" spans="1:7">
       <c r="B35" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C35" s="2">
         <v>2001</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:7">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C36" s="2">
         <v>2001</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G36" s="1"/>
     </row>
     <row r="37" customFormat="1" spans="1:7">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C37" s="2">
         <v>2001</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G37" s="1"/>
     </row>
     <row r="38" customFormat="1" spans="1:7">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C38" s="2">
         <v>2001</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7">
       <c r="B39" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C39" s="2">
         <v>2001</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="B41" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2">
         <v>2002</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C42" s="2">
         <v>2002</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G42" s="1"/>
     </row>
     <row r="43" customFormat="1" spans="1:7">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C43" s="2">
         <v>2002</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G43" s="1"/>
     </row>
     <row r="44" customFormat="1" spans="1:7">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C44" s="2">
         <v>2002</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7">
       <c r="B45" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C45" s="2">
         <v>2002</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="B47" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C47" s="2">
         <v>2003</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:7">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C48" s="2">
         <v>2003</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G48" s="1"/>
     </row>
     <row r="49" customFormat="1" spans="1:7">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C49" s="2">
         <v>2003</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G49" s="1"/>
     </row>
     <row r="50" customFormat="1" spans="1:7">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C50" s="2">
         <v>2003</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7">
       <c r="B51" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2">
         <v>2003</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="B53" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>2004</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C54" s="2">
         <v>2004</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G54" s="1"/>
     </row>
     <row r="55" customFormat="1" spans="1:7">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C55" s="2">
         <v>2004</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G55" s="1"/>
     </row>
     <row r="56" customFormat="1" spans="1:7">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C56" s="2">
         <v>2004</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7">
       <c r="B57" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C57" s="2">
         <v>2004</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16965" windowHeight="13155"/>
+    <workbookView windowWidth="18270" windowHeight="13050"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -52,6 +52,9 @@
     <t>MonsterHp</t>
   </si>
   <si>
+    <t>MonsterDamage</t>
+  </si>
+  <si>
     <t>MonsterEntry</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t>生命值</t>
   </si>
   <si>
+    <t>攻击力</t>
+  </si>
+  <si>
     <t>怪物机制</t>
   </si>
   <si>
@@ -89,6 +95,9 @@
   </si>
   <si>
     <t>1000</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>1001002</t>
@@ -1236,8 +1245,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G57"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="9.775" style="1" customWidth="1"/>
@@ -1245,11 +1254,12 @@
     <col min="4" max="4" width="11.5083333333333" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.7083333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.56666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.75" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="15.1" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1271,149 +1281,173 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:7">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2">
         <v>1001</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2">
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" customFormat="1" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" customFormat="1" spans="1:8">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2">
         <v>1001</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" customFormat="1" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2">
         <v>1001</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" customFormat="1" spans="1:7">
+        <v>30</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2">
         <v>1001</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" customFormat="1" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
@@ -1421,103 +1455,119 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-    </row>
-    <row r="11" customFormat="1" spans="1:7">
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2">
         <v>1002</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" customFormat="1" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2">
         <v>1002</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2">
         <v>1002</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2">
         <v>1002</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:7">
+        <v>30</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:8">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2">
         <v>1002</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" customFormat="1" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
@@ -1525,103 +1575,119 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" spans="1:7">
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2">
         <v>1003</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2">
         <v>1003</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" customFormat="1" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2">
         <v>1003</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2">
         <v>1003</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:7">
+        <v>30</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2">
         <v>1003</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" customFormat="1" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="2"/>
@@ -1629,103 +1695,119 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:7">
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2">
         <v>1004</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2">
         <v>1004</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2">
         <v>1004</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" customFormat="1" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" customFormat="1" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2">
         <v>1004</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" customFormat="1" spans="1:7">
+        <v>30</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2">
         <v>1004</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="2"/>
@@ -1733,103 +1815,119 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-    </row>
-    <row r="29" customFormat="1" spans="1:7">
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C29" s="2">
         <v>1005</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" customFormat="1" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C30" s="2">
         <v>1006</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" customFormat="1" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C31" s="2">
         <v>1007</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" customFormat="1" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" customFormat="1" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C32" s="2">
         <v>1008</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" customFormat="1" spans="1:7">
+        <v>30</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:8">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C33" s="2">
         <v>1009</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" customFormat="1" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" customFormat="1" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="2"/>
@@ -1837,369 +1935,430 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8">
       <c r="B35" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C35" s="2">
         <v>2001</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:7">
+        <v>56</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C36" s="2">
         <v>2001</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37" customFormat="1" spans="1:7">
+        <v>58</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" customFormat="1" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C37" s="2">
         <v>2001</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" customFormat="1" spans="1:7">
+        <v>60</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" customFormat="1" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2">
         <v>2001</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="1:7">
+        <v>62</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="B39" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C39" s="2">
         <v>2001</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>64</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="B41" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C41" s="2">
         <v>2002</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:7">
+        <v>56</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:8">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C42" s="2">
         <v>2002</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" customFormat="1" spans="1:7">
+        <v>58</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" customFormat="1" spans="1:8">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C43" s="2">
         <v>2002</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" customFormat="1" spans="1:7">
+        <v>60</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" spans="1:8">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C44" s="2">
         <v>2002</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="1:7">
+        <v>62</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8">
       <c r="B45" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C45" s="2">
         <v>2002</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>64</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="B47" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C47" s="2">
         <v>2003</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:7">
+        <v>56</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:8">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2">
         <v>2003</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" customFormat="1" spans="1:7">
+        <v>58</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" customFormat="1" spans="1:8">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>2003</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" customFormat="1" spans="1:7">
+        <v>60</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" customFormat="1" spans="1:8">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C50" s="2">
         <v>2003</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="1:7">
+        <v>62</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8">
       <c r="B51" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C51" s="2">
         <v>2003</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>64</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="B53" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C53" s="2">
         <v>2004</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:7">
+        <v>56</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:8">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C54" s="2">
         <v>2004</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G54" s="1"/>
-    </row>
-    <row r="55" customFormat="1" spans="1:7">
+        <v>58</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" customFormat="1" spans="1:8">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C55" s="2">
         <v>2004</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G55" s="1"/>
-    </row>
-    <row r="56" customFormat="1" spans="1:7">
+        <v>60</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" customFormat="1" spans="1:8">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C56" s="2">
         <v>2004</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="1:7">
+        <v>62</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="1:8">
       <c r="B57" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C57" s="2">
         <v>2004</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -94,7 +94,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>1000</t>
+    <t>100</t>
   </si>
   <si>
     <t>10</t>
@@ -106,7 +106,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>1500</t>
+    <t>150</t>
   </si>
   <si>
     <t>1001003</t>
@@ -115,7 +115,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>2000</t>
+    <t>200</t>
   </si>
   <si>
     <t>1001004</t>
@@ -124,7 +124,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>2500</t>
+    <t>250</t>
   </si>
   <si>
     <t>1001005</t>
@@ -133,7 +133,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>3000</t>
+    <t>300</t>
   </si>
   <si>
     <t>1002001</t>
@@ -202,31 +202,16 @@
     <t>Boss</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>2001002</t>
   </si>
   <si>
-    <t>15000</t>
-  </si>
-  <si>
     <t>2001003</t>
   </si>
   <si>
-    <t>20000</t>
-  </si>
-  <si>
     <t>2001004</t>
   </si>
   <si>
-    <t>25000</t>
-  </si>
-  <si>
     <t>2001005</t>
-  </si>
-  <si>
-    <t>30000</t>
   </si>
   <si>
     <t>2002001</t>
@@ -1951,7 +1936,7 @@
         <v>19</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>21</v>
@@ -1960,7 +1945,7 @@
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" s="2">
         <v>2001</v>
@@ -1972,7 +1957,7 @@
         <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>21</v>
@@ -1982,7 +1967,7 @@
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C37" s="2">
         <v>2001</v>
@@ -1994,7 +1979,7 @@
         <v>26</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>21</v>
@@ -2004,7 +1989,7 @@
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C38" s="2">
         <v>2001</v>
@@ -2016,7 +2001,7 @@
         <v>29</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>21</v>
@@ -2025,7 +2010,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="B39" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C39" s="2">
         <v>2001</v>
@@ -2037,7 +2022,7 @@
         <v>32</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>21</v>
@@ -2045,7 +2030,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="B41" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C41" s="2">
         <v>2002</v>
@@ -2057,7 +2042,7 @@
         <v>19</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>21</v>
@@ -2066,7 +2051,7 @@
     <row r="42" customFormat="1" spans="1:8">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>2002</v>
@@ -2078,7 +2063,7 @@
         <v>23</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>21</v>
@@ -2088,7 +2073,7 @@
     <row r="43" customFormat="1" spans="1:8">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2">
         <v>2002</v>
@@ -2100,7 +2085,7 @@
         <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>21</v>
@@ -2110,7 +2095,7 @@
     <row r="44" customFormat="1" spans="1:8">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C44" s="2">
         <v>2002</v>
@@ -2122,7 +2107,7 @@
         <v>29</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>21</v>
@@ -2131,7 +2116,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C45" s="2">
         <v>2002</v>
@@ -2143,7 +2128,7 @@
         <v>32</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>21</v>
@@ -2151,7 +2136,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="B47" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C47" s="2">
         <v>2003</v>
@@ -2163,7 +2148,7 @@
         <v>19</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>21</v>
@@ -2172,7 +2157,7 @@
     <row r="48" customFormat="1" spans="1:8">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C48" s="2">
         <v>2003</v>
@@ -2184,7 +2169,7 @@
         <v>23</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>21</v>
@@ -2194,7 +2179,7 @@
     <row r="49" customFormat="1" spans="1:8">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C49" s="2">
         <v>2003</v>
@@ -2206,7 +2191,7 @@
         <v>26</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>21</v>
@@ -2216,7 +2201,7 @@
     <row r="50" customFormat="1" spans="1:8">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C50" s="2">
         <v>2003</v>
@@ -2228,7 +2213,7 @@
         <v>29</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>21</v>
@@ -2237,7 +2222,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="B51" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2">
         <v>2003</v>
@@ -2249,7 +2234,7 @@
         <v>32</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>21</v>
@@ -2257,7 +2242,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="B53" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C53" s="2">
         <v>2004</v>
@@ -2269,7 +2254,7 @@
         <v>19</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>21</v>
@@ -2278,7 +2263,7 @@
     <row r="54" customFormat="1" spans="1:8">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>2004</v>
@@ -2290,7 +2275,7 @@
         <v>23</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>21</v>
@@ -2300,7 +2285,7 @@
     <row r="55" customFormat="1" spans="1:8">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>2004</v>
@@ -2312,7 +2297,7 @@
         <v>26</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>21</v>
@@ -2322,7 +2307,7 @@
     <row r="56" customFormat="1" spans="1:8">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C56" s="2">
         <v>2004</v>
@@ -2334,7 +2319,7 @@
         <v>29</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>21</v>
@@ -2343,7 +2328,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="B57" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C57" s="2">
         <v>2004</v>
@@ -2355,7 +2340,7 @@
         <v>32</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>21</v>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18270" windowHeight="13050"/>
+    <workbookView windowWidth="16650" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="94">
   <si>
     <t>##var</t>
   </si>
@@ -94,63 +94,114 @@
     <t>1</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1001002</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1001003</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1001004</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1001005</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>1001006</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1001007</t>
+  </si>
+  <si>
+    <t>1001008</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>1001009</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>1001010</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1002001</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1001002</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>1002002</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
-    <t>1001003</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>1002003</t>
   </si>
   <si>
     <t>200</t>
   </si>
   <si>
-    <t>1001004</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>1002004</t>
   </si>
   <si>
     <t>250</t>
   </si>
   <si>
-    <t>1001005</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>1002005</t>
   </si>
   <si>
     <t>300</t>
   </si>
   <si>
-    <t>1002001</t>
-  </si>
-  <si>
-    <t>1002002</t>
-  </si>
-  <si>
-    <t>1002003</t>
-  </si>
-  <si>
-    <t>1002004</t>
-  </si>
-  <si>
-    <t>1002005</t>
-  </si>
-  <si>
     <t>1003001</t>
   </si>
   <si>
@@ -200,6 +251,12 @@
   </si>
   <si>
     <t>Boss</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>2001002</t>
@@ -1230,7 +1287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1362,14 +1419,14 @@
         <v>24</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" customFormat="1" spans="1:8">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2">
         <v>1001</v>
@@ -1378,20 +1435,20 @@
         <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" customFormat="1" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2">
         <v>1001</v>
@@ -1400,20 +1457,20 @@
         <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" customFormat="1" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2">
         <v>1001</v>
@@ -1422,42 +1479,54 @@
         <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" customFormat="1" spans="1:8">
       <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" customFormat="1" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>21</v>
@@ -1467,63 +1536,63 @@
     <row r="12" customFormat="1" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" customFormat="1" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H13" s="1"/>
     </row>
     <row r="14" customFormat="1" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C14" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>21</v>
@@ -1532,818 +1601,916 @@
     </row>
     <row r="15" customFormat="1" spans="1:8">
       <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" customFormat="1" spans="1:8">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" customFormat="1" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" customFormat="1" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C18" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H18" s="1"/>
     </row>
     <row r="19" customFormat="1" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C19" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H19" s="1"/>
     </row>
     <row r="20" customFormat="1" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C20" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H20" s="1"/>
     </row>
     <row r="21" customFormat="1" spans="1:8">
       <c r="A21" s="1"/>
-      <c r="B21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
     <row r="22" customFormat="1" spans="1:8">
       <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H22" s="1"/>
     </row>
     <row r="23" customFormat="1" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H23" s="1"/>
     </row>
     <row r="24" customFormat="1" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C24" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H24" s="1"/>
     </row>
     <row r="25" customFormat="1" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H25" s="1"/>
     </row>
     <row r="26" customFormat="1" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H26" s="1"/>
     </row>
     <row r="27" customFormat="1" spans="1:8">
       <c r="A27" s="1"/>
-      <c r="B27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
     <row r="28" customFormat="1" spans="1:8">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H28" s="1"/>
     </row>
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H29" s="1"/>
     </row>
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C30" s="2">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H30" s="1"/>
     </row>
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H31" s="1"/>
     </row>
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H32" s="1"/>
     </row>
     <row r="33" customFormat="1" spans="1:8">
       <c r="A33" s="1"/>
-      <c r="B33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1009</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" customFormat="1" spans="1:8">
+      <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C35" s="2">
-        <v>2001</v>
+        <v>1006</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H35" s="1"/>
     </row>
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C36" s="2">
-        <v>2001</v>
+        <v>1007</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H36" s="1"/>
     </row>
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C37" s="2">
-        <v>2001</v>
+        <v>1008</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H37" s="1"/>
     </row>
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C38" s="2">
+        <v>1009</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" customFormat="1" spans="1:8">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="B40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="2">
         <v>2001</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="B39" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="D40" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:8">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="2">
         <v>2001</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="B41" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="2">
-        <v>2002</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H41" s="1"/>
     </row>
     <row r="42" customFormat="1" spans="1:8">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C42" s="2">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H42" s="1"/>
     </row>
     <row r="43" customFormat="1" spans="1:8">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C43" s="2">
+        <v>2001</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="B44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2001</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="B46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="2">
         <v>2002</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" customFormat="1" spans="1:8">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="2">
+      <c r="D46" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:8">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="2">
         <v>2002</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="B45" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="2">
-        <v>2002</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="B47" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="2">
-        <v>2003</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H47" s="1"/>
     </row>
     <row r="48" customFormat="1" spans="1:8">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C48" s="2">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H48" s="1"/>
     </row>
     <row r="49" customFormat="1" spans="1:8">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C49" s="2">
+        <v>2002</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="B50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2002</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="B52" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" s="2">
         <v>2003</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" customFormat="1" spans="1:8">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="2">
+      <c r="D52" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:8">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C53" s="2">
         <v>2003</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="B51" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="2">
-        <v>2003</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="B53" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="2">
-        <v>2004</v>
-      </c>
       <c r="D53" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H53" s="1"/>
     </row>
     <row r="54" customFormat="1" spans="1:8">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C54" s="2">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H54" s="1"/>
     </row>
     <row r="55" customFormat="1" spans="1:8">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="2">
+        <v>2003</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C55" s="2">
+      <c r="E55" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="B56" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="2">
+        <v>2003</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="B58" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" s="2">
         <v>2004</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:8">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="2">
+        <v>2004</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" customFormat="1" spans="1:8">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C60" s="2">
+        <v>2004</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" customFormat="1" spans="1:8">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C61" s="2">
+        <v>2004</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="B62" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C62" s="2">
+        <v>2004</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" customFormat="1" spans="1:8">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" s="2">
-        <v>2004</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="1"/>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="B57" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="2">
-        <v>2004</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>21</v>
+      <c r="G62" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16650" windowHeight="14775"/>
+    <workbookView windowWidth="11250" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -94,76 +94,76 @@
     <t>1</t>
   </si>
   <si>
-    <t>20</t>
+    <t>45</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1001002</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1001003</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1001004</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>1001005</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>1001006</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>1001002</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>84</t>
+  </si>
+  <si>
+    <t>1001007</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>1001003</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>1001008</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>1001004</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>1001005</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>1001006</t>
-  </si>
-  <si>
-    <t>38</t>
+    <t>78</t>
+  </si>
+  <si>
+    <t>1001009</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>1001007</t>
-  </si>
-  <si>
-    <t>1001008</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>1001009</t>
-  </si>
-  <si>
-    <t>42</t>
+    <t>91</t>
   </si>
   <si>
     <t>1001010</t>
@@ -172,6 +172,9 @@
     <t>10</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>1002001</t>
   </si>
   <si>
@@ -253,10 +256,7 @@
     <t>Boss</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>160</t>
   </si>
   <si>
     <t>2001002</t>
@@ -1413,20 +1413,20 @@
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" customFormat="1" spans="1:8">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2">
         <v>1001</v>
@@ -1435,20 +1435,20 @@
         <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" customFormat="1" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2">
         <v>1001</v>
@@ -1457,20 +1457,20 @@
         <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" customFormat="1" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2">
         <v>1001</v>
@@ -1479,20 +1479,20 @@
         <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" customFormat="1" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2">
         <v>1001</v>
@@ -1501,20 +1501,20 @@
         <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" customFormat="1" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2">
         <v>1001</v>
@@ -1523,10 +1523,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>21</v>
@@ -1536,7 +1536,7 @@
     <row r="12" customFormat="1" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2">
         <v>1001</v>
@@ -1545,20 +1545,20 @@
         <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" customFormat="1" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2">
         <v>1001</v>
@@ -1567,13 +1567,13 @@
         <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H13" s="1"/>
     </row>
@@ -1592,7 +1592,7 @@
         <v>45</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>21</v>
@@ -1612,7 +1612,7 @@
     <row r="16" customFormat="1" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2">
         <v>1002</v>
@@ -1624,7 +1624,7 @@
         <v>19</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>45</v>
@@ -1634,7 +1634,7 @@
     <row r="17" customFormat="1" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2">
         <v>1002</v>
@@ -1643,10 +1643,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>45</v>
@@ -1656,7 +1656,7 @@
     <row r="18" customFormat="1" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2">
         <v>1002</v>
@@ -1665,10 +1665,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>45</v>
@@ -1678,7 +1678,7 @@
     <row r="19" customFormat="1" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2">
         <v>1002</v>
@@ -1687,10 +1687,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>45</v>
@@ -1700,7 +1700,7 @@
     <row r="20" customFormat="1" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2">
         <v>1002</v>
@@ -1709,10 +1709,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>45</v>
@@ -1732,7 +1732,7 @@
     <row r="22" customFormat="1" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2">
         <v>1003</v>
@@ -1744,7 +1744,7 @@
         <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>45</v>
@@ -1754,7 +1754,7 @@
     <row r="23" customFormat="1" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="2">
         <v>1003</v>
@@ -1763,10 +1763,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>45</v>
@@ -1776,7 +1776,7 @@
     <row r="24" customFormat="1" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2">
         <v>1003</v>
@@ -1785,10 +1785,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>45</v>
@@ -1798,7 +1798,7 @@
     <row r="25" customFormat="1" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2">
         <v>1003</v>
@@ -1807,10 +1807,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>45</v>
@@ -1820,7 +1820,7 @@
     <row r="26" customFormat="1" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
         <v>1003</v>
@@ -1829,10 +1829,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>45</v>
@@ -1852,7 +1852,7 @@
     <row r="28" customFormat="1" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>1004</v>
@@ -1864,7 +1864,7 @@
         <v>19</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>45</v>
@@ -1874,7 +1874,7 @@
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="2">
         <v>1004</v>
@@ -1883,10 +1883,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>45</v>
@@ -1896,7 +1896,7 @@
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2">
         <v>1004</v>
@@ -1905,10 +1905,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>45</v>
@@ -1918,7 +1918,7 @@
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2">
         <v>1004</v>
@@ -1927,10 +1927,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>45</v>
@@ -1940,7 +1940,7 @@
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C32" s="2">
         <v>1004</v>
@@ -1949,10 +1949,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>45</v>
@@ -1972,7 +1972,7 @@
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" s="2">
         <v>1005</v>
@@ -1984,7 +1984,7 @@
         <v>19</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>45</v>
@@ -1994,7 +1994,7 @@
     <row r="35" customFormat="1" spans="1:8">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" s="2">
         <v>1006</v>
@@ -2003,10 +2003,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>45</v>
@@ -2016,7 +2016,7 @@
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C36" s="2">
         <v>1007</v>
@@ -2025,10 +2025,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>45</v>
@@ -2038,7 +2038,7 @@
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C37" s="2">
         <v>1008</v>
@@ -2047,10 +2047,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>45</v>
@@ -2060,7 +2060,7 @@
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2">
         <v>1009</v>
@@ -2069,10 +2069,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>45</v>
@@ -2091,22 +2091,22 @@
     </row>
     <row r="40" spans="1:8">
       <c r="B40" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>2001</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:8">
@@ -2118,13 +2118,13 @@
         <v>2001</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>45</v>
@@ -2140,13 +2140,13 @@
         <v>2001</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>45</v>
@@ -2162,13 +2162,13 @@
         <v>2001</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>45</v>
@@ -2183,13 +2183,13 @@
         <v>2001</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>45</v>
@@ -2203,13 +2203,13 @@
         <v>2002</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>45</v>
@@ -2224,13 +2224,13 @@
         <v>2002</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>45</v>
@@ -2246,13 +2246,13 @@
         <v>2002</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>45</v>
@@ -2268,13 +2268,13 @@
         <v>2002</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>45</v>
@@ -2289,13 +2289,13 @@
         <v>2002</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>45</v>
@@ -2309,13 +2309,13 @@
         <v>2003</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>45</v>
@@ -2330,13 +2330,13 @@
         <v>2003</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>45</v>
@@ -2352,13 +2352,13 @@
         <v>2003</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>45</v>
@@ -2374,13 +2374,13 @@
         <v>2003</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>45</v>
@@ -2395,13 +2395,13 @@
         <v>2003</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>45</v>
@@ -2415,13 +2415,13 @@
         <v>2004</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>45</v>
@@ -2436,13 +2436,13 @@
         <v>2004</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>45</v>
@@ -2458,13 +2458,13 @@
         <v>2004</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>45</v>
@@ -2480,13 +2480,13 @@
         <v>2004</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>45</v>
@@ -2501,13 +2501,13 @@
         <v>2004</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>45</v>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11250" windowHeight="14775"/>
+    <workbookView windowWidth="15420" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Icon</t>
+  </si>
+  <si>
     <t>MonsterLevel</t>
   </si>
   <si>
@@ -67,12 +70,18 @@
     <t>MonsterType</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>怪物Id</t>
   </si>
   <si>
     <t>怪物类型</t>
   </si>
   <si>
+    <t>怪物icon</t>
+  </si>
+  <si>
     <t>怪物等级</t>
   </si>
   <si>
@@ -91,6 +100,9 @@
     <t>Normal</t>
   </si>
   <si>
+    <t>Monster1</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -103,217 +115,118 @@
     <t>1001002</t>
   </si>
   <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1001003</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>1001004</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1002001</t>
+  </si>
+  <si>
+    <t>Monster2</t>
+  </si>
+  <si>
     <t>55</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1001003</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1001004</t>
+    <t>1002002</t>
+  </si>
+  <si>
+    <t>1002003</t>
+  </si>
+  <si>
+    <t>1002004</t>
+  </si>
+  <si>
+    <t>1003001</t>
+  </si>
+  <si>
+    <t>Monster3</t>
+  </si>
+  <si>
+    <t>1003002</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1003003</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>1003004</t>
+  </si>
+  <si>
+    <t>1004001</t>
+  </si>
+  <si>
+    <t>Monster4</t>
   </si>
   <si>
     <t>60</t>
   </si>
   <si>
-    <t>1001005</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>1001006</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>1001007</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1001008</t>
+    <t>1004002</t>
+  </si>
+  <si>
+    <t>1004003</t>
+  </si>
+  <si>
+    <t>1004004</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>1005001</t>
+  </si>
+  <si>
+    <t>Monster5</t>
+  </si>
+  <si>
+    <t>1005002</t>
+  </si>
+  <si>
+    <t>1005003</t>
+  </si>
+  <si>
+    <t>1005004</t>
+  </si>
+  <si>
+    <t>2001001</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>Monster6</t>
+  </si>
+  <si>
+    <t>160</t>
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>1001009</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1001010</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>1002001</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>1002002</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>1002003</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>1002004</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>1002005</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>1003001</t>
-  </si>
-  <si>
-    <t>1003002</t>
-  </si>
-  <si>
-    <t>1003003</t>
-  </si>
-  <si>
-    <t>1003004</t>
-  </si>
-  <si>
-    <t>1003005</t>
-  </si>
-  <si>
-    <t>1004001</t>
-  </si>
-  <si>
-    <t>1004002</t>
-  </si>
-  <si>
-    <t>1004003</t>
-  </si>
-  <si>
-    <t>1004004</t>
-  </si>
-  <si>
-    <t>1004005</t>
-  </si>
-  <si>
-    <t>1005001</t>
-  </si>
-  <si>
-    <t>1005002</t>
-  </si>
-  <si>
-    <t>1005003</t>
-  </si>
-  <si>
-    <t>1005004</t>
-  </si>
-  <si>
-    <t>1005005</t>
-  </si>
-  <si>
-    <t>2001001</t>
-  </si>
-  <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>2001002</t>
-  </si>
-  <si>
-    <t>2001003</t>
-  </si>
-  <si>
-    <t>2001004</t>
-  </si>
-  <si>
-    <t>2001005</t>
-  </si>
-  <si>
-    <t>2002001</t>
-  </si>
-  <si>
-    <t>2002002</t>
-  </si>
-  <si>
-    <t>2002003</t>
-  </si>
-  <si>
-    <t>2002004</t>
-  </si>
-  <si>
-    <t>2002005</t>
-  </si>
-  <si>
-    <t>2003001</t>
-  </si>
-  <si>
-    <t>2003002</t>
-  </si>
-  <si>
-    <t>2003003</t>
-  </si>
-  <si>
-    <t>2003004</t>
-  </si>
-  <si>
-    <t>2003005</t>
-  </si>
-  <si>
-    <t>2004001</t>
-  </si>
-  <si>
-    <t>2004002</t>
-  </si>
-  <si>
-    <t>2004003</t>
-  </si>
-  <si>
-    <t>2004004</t>
-  </si>
-  <si>
-    <t>2004005</t>
   </si>
 </sst>
 </file>
@@ -1287,21 +1200,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.775" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.88333333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.5083333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.7083333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.56666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="5" max="6" width="12.7083333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.56666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.75" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1326,1191 +1239,644 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:8">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:9">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2">
         <v>1001</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:8">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:9">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2">
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" customFormat="1" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" customFormat="1" spans="1:9">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2">
         <v>1001</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" customFormat="1" spans="1:8">
+        <v>31</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:9">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2">
         <v>1001</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" customFormat="1" spans="1:8">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:9">
       <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1001</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-    </row>
-    <row r="10" customFormat="1" spans="1:8">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:9">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" customFormat="1" spans="1:8">
+        <v>36</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:9">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" customFormat="1" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:9">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:8">
+        <v>31</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:9">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:9">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:9">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="2">
-        <v>1001</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:8">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1001</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:8">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" customFormat="1" spans="1:8">
+      <c r="F15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" spans="1:8">
+        <v>43</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:9">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" spans="1:8">
+        <v>46</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:9">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" customFormat="1" spans="1:8">
+        <v>33</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:9">
       <c r="A19" s="1"/>
-      <c r="B19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:8">
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:8">
+        <v>50</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:9">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" customFormat="1" spans="1:8">
+      <c r="B21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:9">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:8">
+        <v>46</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:9">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:8">
+        <v>54</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:9">
       <c r="A24" s="1"/>
-      <c r="B24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:8">
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:9">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" customFormat="1" spans="1:8">
+        <v>50</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" customFormat="1" spans="1:9">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C26" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="H26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:9">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:8">
+      <c r="F27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:9">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:9">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="B30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2001</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" customFormat="1" spans="1:8">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1" t="s">
+      <c r="F30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" customFormat="1" spans="1:8">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" customFormat="1" spans="1:8">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" customFormat="1" spans="1:8">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" customFormat="1" spans="1:8">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" customFormat="1" spans="1:8">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" customFormat="1" spans="1:8">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="2">
-        <v>1006</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" customFormat="1" spans="1:8">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="2">
-        <v>1007</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" customFormat="1" spans="1:8">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="2">
-        <v>1008</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" customFormat="1" spans="1:8">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" s="2">
-        <v>1009</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" customFormat="1" spans="1:8">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="B40" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="2">
-        <v>2001</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:8">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="2">
-        <v>2001</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" customFormat="1" spans="1:8">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="2">
-        <v>2001</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" customFormat="1" spans="1:8">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" s="2">
-        <v>2001</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="B44" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" s="2">
-        <v>2001</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="B46" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="2">
-        <v>2002</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:8">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" s="2">
-        <v>2002</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" customFormat="1" spans="1:8">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" s="2">
-        <v>2002</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" customFormat="1" spans="1:8">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="2">
-        <v>2002</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="B50" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="2">
-        <v>2002</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="B52" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="2">
-        <v>2003</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:8">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C53" s="2">
-        <v>2003</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H53" s="1"/>
-    </row>
-    <row r="54" customFormat="1" spans="1:8">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="2">
-        <v>2003</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" customFormat="1" spans="1:8">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="2">
-        <v>2003</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="B56" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" s="2">
-        <v>2003</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="B58" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" s="2">
-        <v>2004</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" spans="1:8">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" s="2">
-        <v>2004</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H59" s="1"/>
-    </row>
-    <row r="60" customFormat="1" spans="1:8">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C60" s="2">
-        <v>2004</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H60" s="1"/>
-    </row>
-    <row r="61" customFormat="1" spans="1:8">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C61" s="2">
-        <v>2004</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H61" s="1"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="B62" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C62" s="2">
-        <v>2004</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15420" windowHeight="14775"/>
+    <workbookView windowWidth="9210" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -43,21 +43,24 @@
     <t>MonsterId</t>
   </si>
   <si>
+    <t>MonsterLevel</t>
+  </si>
+  <si>
+    <t>MonsterHp</t>
+  </si>
+  <si>
+    <t>MonsterDamage</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>Icon</t>
   </si>
   <si>
-    <t>MonsterLevel</t>
-  </si>
-  <si>
-    <t>MonsterHp</t>
-  </si>
-  <si>
-    <t>MonsterDamage</t>
-  </si>
-  <si>
     <t>MonsterEntry</t>
   </si>
   <si>
@@ -76,42 +79,48 @@
     <t>怪物Id</t>
   </si>
   <si>
+    <t>怪物等级</t>
+  </si>
+  <si>
+    <t>生命值</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
     <t>怪物类型</t>
   </si>
   <si>
+    <t>怪物名字</t>
+  </si>
+  <si>
     <t>怪物icon</t>
   </si>
   <si>
-    <t>怪物等级</t>
-  </si>
-  <si>
-    <t>生命值</t>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
     <t>怪物机制</t>
   </si>
   <si>
     <t>1001001</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Normal</t>
   </si>
   <si>
+    <t>屎莱姆</t>
+  </si>
+  <si>
     <t>Monster1</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>1001002</t>
   </si>
   <si>
@@ -136,15 +145,33 @@
     <t>91</t>
   </si>
   <si>
+    <t>1001005</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>1001006</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>1002001</t>
   </si>
   <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>狼哥</t>
+  </si>
+  <si>
     <t>Monster2</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>1002002</t>
   </si>
   <si>
@@ -154,9 +181,18 @@
     <t>1002004</t>
   </si>
   <si>
+    <t>1002005</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
     <t>1003001</t>
   </si>
   <si>
+    <t>蛙弟</t>
+  </si>
+  <si>
     <t>Monster3</t>
   </si>
   <si>
@@ -166,9 +202,6 @@
     <t>84</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>1003003</t>
   </si>
   <si>
@@ -178,15 +211,21 @@
     <t>1003004</t>
   </si>
   <si>
+    <t>1003005</t>
+  </si>
+  <si>
     <t>1004001</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>小蜜蜂</t>
+  </si>
+  <si>
     <t>Monster4</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>1004002</t>
   </si>
   <si>
@@ -199,9 +238,15 @@
     <t>50</t>
   </si>
   <si>
+    <t>1004005</t>
+  </si>
+  <si>
     <t>1005001</t>
   </si>
   <si>
+    <t>蘑菇人</t>
+  </si>
+  <si>
     <t>Monster5</t>
   </si>
   <si>
@@ -214,19 +259,25 @@
     <t>1005004</t>
   </si>
   <si>
+    <t>1005005</t>
+  </si>
+  <si>
     <t>2001001</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>Boss</t>
   </si>
   <si>
+    <t>大眼仔</t>
+  </si>
+  <si>
     <t>Monster6</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
 </sst>
 </file>
@@ -1200,21 +1251,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.775" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.88333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.5083333333333" style="2" customWidth="1"/>
-    <col min="5" max="6" width="12.7083333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.56666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.75" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="12.175" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.56666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5083333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.475" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.91666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.4916666666667" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,7 +1277,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1233,7 +1286,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1242,641 +1295,886 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:9">
+        <v>20</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2">
         <v>1001</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:9">
+        <v>27</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:10">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2">
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" customFormat="1" spans="1:9">
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" customFormat="1" spans="1:10">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2">
         <v>1001</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" customFormat="1" spans="1:9">
+        <v>27</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:10">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2">
         <v>1001</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:10">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" customFormat="1" spans="1:9">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" customFormat="1" spans="1:9">
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:10">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" customFormat="1" spans="1:9">
+        <v>27</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:10">
       <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-    </row>
-    <row r="12" customFormat="1" spans="1:9">
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:10">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2">
         <v>1002</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:9">
+        <v>44</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:10">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2">
         <v>1002</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:10">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:9">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:9">
+      <c r="E14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:10">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" customFormat="1" spans="1:9">
+        <v>44</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:10">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" spans="1:9">
+      <c r="I16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:10">
       <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" spans="1:9">
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:10">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2">
         <v>1003</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" customFormat="1" spans="1:9">
+        <v>52</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:10">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:9">
+      <c r="B19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:10">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:9">
+        <v>52</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:10">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C21" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" customFormat="1" spans="1:9">
+        <v>52</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:10">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="2">
+      <c r="I22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:10">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:10">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="2">
         <v>1004</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:9">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:9">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:9">
+      <c r="D24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:10">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" customFormat="1" spans="1:9">
+        <v>62</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" customFormat="1" spans="1:10">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" customFormat="1" spans="1:9">
+        <v>62</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:10">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C27" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:9">
+        <v>62</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:10">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C28" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" customFormat="1" spans="1:9">
+        <v>62</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:10">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="2"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:10">
+      <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:10">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" customFormat="1" spans="1:10">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:10">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" customFormat="1" spans="1:10">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" customFormat="1" spans="1:10">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="B36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="2">
         <v>2001</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>64</v>
+      <c r="E36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="9210" windowHeight="14775"/>
+    <workbookView windowWidth="8940" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="105">
   <si>
     <t>##var</t>
   </si>
@@ -79,7 +79,7 @@
     <t>怪物Id</t>
   </si>
   <si>
-    <t>怪物等级</t>
+    <t>等级</t>
   </si>
   <si>
     <t>生命值</t>
@@ -160,6 +160,24 @@
     <t>6</t>
   </si>
   <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>1001007</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1001008</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
     <t>1002001</t>
   </si>
   <si>
@@ -187,6 +205,15 @@
     <t>77</t>
   </si>
   <si>
+    <t>1002006</t>
+  </si>
+  <si>
+    <t>1002007</t>
+  </si>
+  <si>
+    <t>1002008</t>
+  </si>
+  <si>
     <t>1003001</t>
   </si>
   <si>
@@ -214,6 +241,21 @@
     <t>1003005</t>
   </si>
   <si>
+    <t>1003006</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>1003007</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1003008</t>
+  </si>
+  <si>
     <t>1004001</t>
   </si>
   <si>
@@ -241,6 +283,18 @@
     <t>1004005</t>
   </si>
   <si>
+    <t>1004006</t>
+  </si>
+  <si>
+    <t>1004007</t>
+  </si>
+  <si>
+    <t>1004008</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>1005001</t>
   </si>
   <si>
@@ -262,15 +316,21 @@
     <t>1005005</t>
   </si>
   <si>
+    <t>1005006</t>
+  </si>
+  <si>
+    <t>1005007</t>
+  </si>
+  <si>
+    <t>1005008</t>
+  </si>
+  <si>
     <t>2001001</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>Boss</t>
   </si>
   <si>
@@ -278,6 +338,15 @@
   </si>
   <si>
     <t>Monster6</t>
+  </si>
+  <si>
+    <t>2001002</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -1251,16 +1320,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.775" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.175" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.56666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5083333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.03333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="4.55833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.96666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.95" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.475" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.91666666666667" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.4916666666667" style="1" customWidth="1"/>
@@ -1515,10 +1584,10 @@
         <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>26</v>
@@ -1533,113 +1602,113 @@
     </row>
     <row r="11" customFormat="1" spans="1:10">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" customFormat="1" spans="1:10">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="J12" s="1"/>
     </row>
     <row r="13" customFormat="1" spans="1:10">
       <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
     <row r="14" customFormat="1" spans="1:10">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2">
         <v>1002</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="G14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J14" s="1"/>
     </row>
     <row r="15" customFormat="1" spans="1:10">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2">
         <v>1002</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>31</v>
@@ -1648,66 +1717,82 @@
         <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J15" s="1"/>
     </row>
     <row r="16" customFormat="1" spans="1:10">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2">
         <v>1002</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I16" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J16" s="1"/>
     </row>
     <row r="17" customFormat="1" spans="1:10">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="J17" s="1"/>
     </row>
     <row r="18" customFormat="1" spans="1:10">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C18" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>31</v>
@@ -1716,26 +1801,26 @@
         <v>26</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J18" s="1"/>
     </row>
     <row r="19" customFormat="1" spans="1:10">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>38</v>
@@ -1744,330 +1829,330 @@
         <v>26</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" customFormat="1" spans="1:10">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" customFormat="1" spans="1:10">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J21" s="1"/>
     </row>
     <row r="22" customFormat="1" spans="1:10">
       <c r="A22" s="1"/>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" customFormat="1" spans="1:10">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="J23" s="1"/>
     </row>
     <row r="24" customFormat="1" spans="1:10">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C24" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J24" s="1"/>
     </row>
     <row r="25" customFormat="1" spans="1:10">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J25" s="1"/>
     </row>
     <row r="26" customFormat="1" spans="1:10">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J26" s="1"/>
     </row>
     <row r="27" customFormat="1" spans="1:10">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J27" s="1"/>
     </row>
     <row r="28" customFormat="1" spans="1:10">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J28" s="1"/>
     </row>
     <row r="29" customFormat="1" spans="1:10">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="J29" s="1"/>
     </row>
     <row r="30" customFormat="1" spans="1:10">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="I30" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="J30" s="1"/>
     </row>
     <row r="31" customFormat="1" spans="1:10">
       <c r="A31" s="1"/>
-      <c r="B31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" customFormat="1" spans="1:10">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>33</v>
@@ -2076,105 +2161,507 @@
         <v>26</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J32" s="1"/>
     </row>
     <row r="33" customFormat="1" spans="1:10">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C33" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J33" s="1"/>
     </row>
     <row r="34" customFormat="1" spans="1:10">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C34" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J34" s="1"/>
     </row>
     <row r="35" customFormat="1" spans="1:10">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="B35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" customFormat="1" spans="1:10">
+      <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="2">
+      <c r="I36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" customFormat="1" spans="1:10">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" customFormat="1" spans="1:10">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" customFormat="1" spans="1:10">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" customFormat="1" spans="1:10">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" spans="1:10">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" customFormat="1" spans="1:10">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" customFormat="1" spans="1:10">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" spans="1:10">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" customFormat="1" spans="1:10">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" customFormat="1" spans="1:10">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" customFormat="1" spans="1:10">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" customFormat="1" spans="1:10">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" customFormat="1" spans="1:10">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="B50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="2">
         <v>2001</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>81</v>
+      <c r="E50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="B51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2001</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="8940" windowHeight="11805"/>
+    <workbookView windowWidth="11850" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
     <t>屎莱姆</t>
   </si>
   <si>
-    <t>Monster1</t>
+    <t>enemy1</t>
   </si>
   <si>
     <t>1001002</t>
@@ -187,7 +187,7 @@
     <t>狼哥</t>
   </si>
   <si>
-    <t>Monster2</t>
+    <t>enemy2</t>
   </si>
   <si>
     <t>1002002</t>
@@ -220,7 +220,7 @@
     <t>蛙弟</t>
   </si>
   <si>
-    <t>Monster3</t>
+    <t>enemy3</t>
   </si>
   <si>
     <t>1003002</t>
@@ -265,7 +265,7 @@
     <t>小蜜蜂</t>
   </si>
   <si>
-    <t>Monster4</t>
+    <t>enemy4</t>
   </si>
   <si>
     <t>1004002</t>
@@ -301,7 +301,7 @@
     <t>蘑菇人</t>
   </si>
   <si>
-    <t>Monster5</t>
+    <t>enemy5</t>
   </si>
   <si>
     <t>1005002</t>
@@ -337,7 +337,7 @@
     <t>大眼仔</t>
   </si>
   <si>
-    <t>Monster6</t>
+    <t>enemy6</t>
   </si>
   <si>
     <t>2001002</t>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14415" windowHeight="11400"/>
+    <workbookView windowWidth="14445" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1437,19 +1437,19 @@
       <c r="B13" s="2">
         <v>1001009</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>1001</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>9</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>93</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>3</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H13" t="s">
@@ -1463,19 +1463,19 @@
       <c r="B14" s="2">
         <v>1001010</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>1001</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>10</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>104</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>5</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H14" t="s">
@@ -1489,19 +1489,19 @@
       <c r="B15" s="2">
         <v>1001011</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>1001</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>11</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>117</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>5</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H15" t="s">
@@ -1515,19 +1515,19 @@
       <c r="B16" s="2">
         <v>1001012</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>1001</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>12</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>132</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>6</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H16" t="s">
@@ -1541,19 +1541,19 @@
       <c r="B17" s="2">
         <v>1001013</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>1001</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>13</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>121</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>4</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H17" t="s">
@@ -1567,19 +1567,19 @@
       <c r="B18" s="2">
         <v>1001014</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>1001</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>14</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>135</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>6</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H18" t="s">
@@ -1593,19 +1593,19 @@
       <c r="B19" s="2">
         <v>1001015</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>1001</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>15</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>152</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>6</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H19" t="s">
@@ -1619,19 +1619,19 @@
       <c r="B20" s="2">
         <v>1001016</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>1001</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>16</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>172</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>8</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H20" t="s">
@@ -1645,19 +1645,19 @@
       <c r="B21" s="2">
         <v>1001017</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>1001</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>17</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>157</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>5</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H21" t="s">
@@ -1671,19 +1671,19 @@
       <c r="B22" s="2">
         <v>1001018</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>1001</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>18</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>176</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>7</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H22" t="s">
@@ -1697,19 +1697,19 @@
       <c r="B23" s="2">
         <v>1001019</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>1001</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>19</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="2">
         <v>198</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>7</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H23" t="s">
@@ -1723,19 +1723,19 @@
       <c r="B24" s="2">
         <v>1001020</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>1001</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>20</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="2">
         <v>223</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>10</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H24" t="s">
@@ -1749,19 +1749,19 @@
       <c r="B25" s="2">
         <v>1001021</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>1001</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>21</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="2">
         <v>204</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>6</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H25" t="s">
@@ -1775,19 +1775,19 @@
       <c r="B26" s="2">
         <v>1001022</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>1001</v>
       </c>
-      <c r="D26">
-        <v>22</v>
-      </c>
-      <c r="E26">
+      <c r="D26" s="2">
+        <v>22</v>
+      </c>
+      <c r="E26" s="2">
         <v>229</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>9</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H26" t="s">
@@ -1801,19 +1801,19 @@
       <c r="B27" s="2">
         <v>1001023</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>1001</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>23</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>257</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>9</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H27" t="s">
@@ -1827,19 +1827,19 @@
       <c r="B28" s="2">
         <v>1001024</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>1001</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>24</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2">
         <v>290</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>12</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H28" t="s">
@@ -1853,19 +1853,19 @@
       <c r="B29" s="2">
         <v>1001025</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>1001</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>25</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2">
         <v>265</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>8</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H29" t="s">
@@ -1879,19 +1879,19 @@
       <c r="B30" s="2">
         <v>1001026</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>1001</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>26</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="2">
         <v>297</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="2">
         <v>11</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H30" t="s">
@@ -1905,19 +1905,19 @@
       <c r="B31" s="2">
         <v>1001027</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <v>1001</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>27</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="2">
         <v>334</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="2">
         <v>11</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H31" t="s">
@@ -1931,19 +1931,19 @@
       <c r="B32" s="2">
         <v>1001028</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <v>1001</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>28</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="2">
         <v>377</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="2">
         <v>15</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H32" t="s">
@@ -1957,19 +1957,19 @@
       <c r="B33" s="2">
         <v>1001029</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2">
         <v>1001</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>29</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="2">
         <v>345</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="2">
         <v>10</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H33" t="s">
@@ -1983,19 +1983,19 @@
       <c r="B34" s="2">
         <v>1001030</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2">
         <v>1001</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>30</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="2">
         <v>387</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2">
         <v>14</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H34" t="s">
@@ -2009,19 +2009,19 @@
       <c r="B35" s="2">
         <v>1001031</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <v>1001</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>31</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="2">
         <v>435</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2">
         <v>14</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H35" t="s">
@@ -2035,19 +2035,19 @@
       <c r="B36" s="2">
         <v>1001032</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <v>1001</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>32</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="2">
         <v>490</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2">
         <v>19</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H36" t="s">
@@ -2061,19 +2061,19 @@
       <c r="B37" s="2">
         <v>1001033</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>1001</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>33</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="2">
         <v>449</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2">
         <v>12</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H37" t="s">
@@ -2087,19 +2087,19 @@
       <c r="B38" s="2">
         <v>1001034</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>1001</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>34</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="2">
         <v>502</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2">
         <v>18</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H38" t="s">
@@ -2113,19 +2113,19 @@
       <c r="B39" s="2">
         <v>1001035</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>1001</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>35</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="2">
         <v>565</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2">
         <v>18</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H39" t="s">
@@ -2139,19 +2139,19 @@
       <c r="B40" s="2">
         <v>1001036</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2">
         <v>1001</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>36</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="2">
         <v>637</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="2">
         <v>24</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H40" t="s">
@@ -2165,19 +2165,19 @@
       <c r="B41" s="2">
         <v>1001037</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2">
         <v>1001</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <v>37</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="2">
         <v>583</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="2">
         <v>15</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H41" t="s">
@@ -2191,19 +2191,19 @@
       <c r="B42" s="2">
         <v>1001038</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2">
         <v>1001</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <v>38</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="2">
         <v>653</v>
       </c>
-      <c r="F42">
-        <v>22</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="F42" s="2">
+        <v>22</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H42" t="s">
@@ -2217,19 +2217,19 @@
       <c r="B43" s="2">
         <v>1001039</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="2">
         <v>1001</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>39</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="2">
         <v>735</v>
       </c>
-      <c r="F43">
-        <v>22</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="F43" s="2">
+        <v>22</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H43" t="s">
@@ -2243,19 +2243,19 @@
       <c r="B44" s="2">
         <v>1001040</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="2">
         <v>1001</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="2">
         <v>40</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="2">
         <v>828</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="2">
         <v>30</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H44" t="s">
@@ -2269,19 +2269,19 @@
       <c r="B45" s="2">
         <v>1001041</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="2">
         <v>1001</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="2">
         <v>41</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="2">
         <v>758</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="2">
         <v>19</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H45" t="s">
@@ -2295,19 +2295,19 @@
       <c r="B46" s="2">
         <v>1001042</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="2">
         <v>1001</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="2">
         <v>42</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="2">
         <v>849</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="2">
         <v>28</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H46" t="s">
@@ -2321,19 +2321,19 @@
       <c r="B47" s="2">
         <v>1001043</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="2">
         <v>1001</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <v>43</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="2">
         <v>955</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="2">
         <v>28</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H47" t="s">
@@ -2347,19 +2347,19 @@
       <c r="B48" s="2">
         <v>1001044</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="2">
         <v>1001</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <v>44</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="2">
         <v>1077</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="2">
         <v>37</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H48" t="s">
@@ -2581,19 +2581,19 @@
       <c r="B58" s="2">
         <v>1002009</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="2">
         <v>1002</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <v>9</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="2">
         <v>85</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="2">
         <v>5</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H58" t="s">
@@ -2607,19 +2607,19 @@
       <c r="B59" s="2">
         <v>1002010</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="2">
         <v>1002</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="2">
         <v>10</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="2">
         <v>95</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="2">
         <v>6</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H59" t="s">
@@ -2633,19 +2633,19 @@
       <c r="B60" s="2">
         <v>1002011</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="2">
         <v>1002</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="2">
         <v>11</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="2">
         <v>106</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="2">
         <v>6</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H60" t="s">
@@ -2659,19 +2659,19 @@
       <c r="B61" s="2">
         <v>1002012</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="2">
         <v>1002</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <v>12</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="2">
         <v>120</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="2">
         <v>8</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H61" t="s">
@@ -2685,19 +2685,19 @@
       <c r="B62" s="2">
         <v>1002013</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="2">
         <v>1002</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="2">
         <v>13</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="2">
         <v>110</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="2">
         <v>6</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H62" t="s">
@@ -2711,19 +2711,19 @@
       <c r="B63" s="2">
         <v>1002014</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="2">
         <v>1002</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="2">
         <v>14</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="2">
         <v>123</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="2">
         <v>8</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H63" t="s">
@@ -2737,19 +2737,19 @@
       <c r="B64" s="2">
         <v>1002015</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="2">
         <v>1002</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="2">
         <v>15</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="2">
         <v>138</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="2">
         <v>8</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H64" t="s">
@@ -2763,19 +2763,19 @@
       <c r="B65" s="2">
         <v>1002016</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="2">
         <v>1002</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="2">
         <v>16</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="2">
         <v>156</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="2">
         <v>10</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H65" t="s">
@@ -2789,19 +2789,19 @@
       <c r="B66" s="2">
         <v>1002017</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="2">
         <v>1002</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="2">
         <v>17</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="2">
         <v>143</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="2">
         <v>7</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H66" t="s">
@@ -2815,19 +2815,19 @@
       <c r="B67" s="2">
         <v>1002018</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="2">
         <v>1002</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="2">
         <v>18</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="2">
         <v>160</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="2">
         <v>10</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H67" t="s">
@@ -2841,19 +2841,19 @@
       <c r="B68" s="2">
         <v>1002019</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="2">
         <v>1002</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="2">
         <v>19</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="2">
         <v>180</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="2">
         <v>10</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H68" t="s">
@@ -2867,19 +2867,19 @@
       <c r="B69" s="2">
         <v>1002020</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="2">
         <v>1002</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="2">
         <v>20</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="2">
         <v>203</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="2">
         <v>12</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H69" t="s">
@@ -2893,19 +2893,19 @@
       <c r="B70" s="2">
         <v>1002021</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="2">
         <v>1002</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="2">
         <v>21</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="2">
         <v>186</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="2">
         <v>9</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G70" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H70" t="s">
@@ -2919,19 +2919,19 @@
       <c r="B71" s="2">
         <v>1002022</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="2">
         <v>1002</v>
       </c>
-      <c r="D71">
-        <v>22</v>
-      </c>
-      <c r="E71">
+      <c r="D71" s="2">
+        <v>22</v>
+      </c>
+      <c r="E71" s="2">
         <v>208</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="2">
         <v>12</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H71" t="s">
@@ -2945,19 +2945,19 @@
       <c r="B72" s="2">
         <v>1002023</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="2">
         <v>1002</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="2">
         <v>23</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="2">
         <v>234</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="2">
         <v>12</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G72" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H72" t="s">
@@ -2971,19 +2971,19 @@
       <c r="B73" s="2">
         <v>1002024</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="2">
         <v>1002</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="2">
         <v>24</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="2">
         <v>264</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="2">
         <v>15</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H73" t="s">
@@ -2997,19 +2997,19 @@
       <c r="B74" s="2">
         <v>1002025</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="2">
         <v>1002</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="2">
         <v>25</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="2">
         <v>241</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="2">
         <v>11</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G74" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H74" t="s">
@@ -3023,19 +3023,19 @@
       <c r="B75" s="2">
         <v>1002026</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="2">
         <v>1002</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="2">
         <v>26</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="2">
         <v>270</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="2">
         <v>15</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H75" t="s">
@@ -3049,19 +3049,19 @@
       <c r="B76" s="2">
         <v>1002027</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="2">
         <v>1002</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="2">
         <v>27</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="2">
         <v>304</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="2">
         <v>15</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H76" t="s">
@@ -3075,19 +3075,19 @@
       <c r="B77" s="2">
         <v>1002028</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="2">
         <v>1002</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="2">
         <v>28</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="2">
         <v>343</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="2">
         <v>19</v>
       </c>
-      <c r="G77" t="s">
+      <c r="G77" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H77" t="s">
@@ -3101,19 +3101,19 @@
       <c r="B78" s="2">
         <v>1002029</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="2">
         <v>1002</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="2">
         <v>29</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="2">
         <v>314</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="2">
         <v>14</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G78" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H78" t="s">
@@ -3127,19 +3127,19 @@
       <c r="B79" s="2">
         <v>1002030</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="2">
         <v>1002</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="2">
         <v>30</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="2">
         <v>351</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="2">
         <v>19</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G79" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H79" t="s">
@@ -3153,19 +3153,19 @@
       <c r="B80" s="2">
         <v>1002031</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="2">
         <v>1002</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="2">
         <v>31</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="2">
         <v>395</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="2">
         <v>19</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G80" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H80" t="s">
@@ -3179,19 +3179,19 @@
       <c r="B81" s="2">
         <v>1002032</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="2">
         <v>1002</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="2">
         <v>32</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="2">
         <v>446</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="2">
         <v>24</v>
       </c>
-      <c r="G81" t="s">
+      <c r="G81" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H81" t="s">
@@ -3205,19 +3205,19 @@
       <c r="B82" s="2">
         <v>1002033</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="2">
         <v>1002</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="2">
         <v>33</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="2">
         <v>408</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="2">
         <v>18</v>
       </c>
-      <c r="G82" t="s">
+      <c r="G82" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H82" t="s">
@@ -3231,19 +3231,19 @@
       <c r="B83" s="2">
         <v>1002034</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="2">
         <v>1002</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="2">
         <v>34</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="2">
         <v>457</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="2">
         <v>24</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G83" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H83" t="s">
@@ -3257,19 +3257,19 @@
       <c r="B84" s="2">
         <v>1002035</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="2">
         <v>1002</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="2">
         <v>35</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="2">
         <v>514</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="2">
         <v>24</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H84" t="s">
@@ -3283,19 +3283,19 @@
       <c r="B85" s="2">
         <v>1002036</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="2">
         <v>1002</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="2">
         <v>36</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="2">
         <v>579</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="2">
         <v>30</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G85" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H85" t="s">
@@ -3309,19 +3309,19 @@
       <c r="B86" s="2">
         <v>1002037</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="2">
         <v>1002</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="2">
         <v>37</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="2">
         <v>530</v>
       </c>
-      <c r="F86">
-        <v>22</v>
-      </c>
-      <c r="G86" t="s">
+      <c r="F86" s="2">
+        <v>22</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H86" t="s">
@@ -3335,19 +3335,19 @@
       <c r="B87" s="2">
         <v>1002038</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="2">
         <v>1002</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="2">
         <v>38</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="2">
         <v>594</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="2">
         <v>30</v>
       </c>
-      <c r="G87" t="s">
+      <c r="G87" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H87" t="s">
@@ -3361,19 +3361,19 @@
       <c r="B88" s="2">
         <v>1002039</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="2">
         <v>1002</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="2">
         <v>39</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="2">
         <v>668</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="2">
         <v>30</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G88" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H88" t="s">
@@ -3387,19 +3387,19 @@
       <c r="B89" s="2">
         <v>1002040</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="2">
         <v>1002</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="2">
         <v>40</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="2">
         <v>753</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="2">
         <v>37</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G89" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H89" t="s">
@@ -3413,19 +3413,19 @@
       <c r="B90" s="2">
         <v>1002041</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="2">
         <v>1002</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="2">
         <v>41</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="2">
         <v>689</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="2">
         <v>28</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G90" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H90" t="s">
@@ -3439,19 +3439,19 @@
       <c r="B91" s="2">
         <v>1002042</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="2">
         <v>1002</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="2">
         <v>42</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="2">
         <v>772</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="2">
         <v>37</v>
       </c>
-      <c r="G91" t="s">
+      <c r="G91" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H91" t="s">
@@ -3465,19 +3465,19 @@
       <c r="B92" s="2">
         <v>1002043</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="2">
         <v>1002</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="2">
         <v>43</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="2">
         <v>869</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="2">
         <v>37</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G92" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H92" t="s">
@@ -3491,19 +3491,19 @@
       <c r="B93" s="2">
         <v>1002044</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="2">
         <v>1002</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="2">
         <v>44</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="2">
         <v>979</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="2">
         <v>47</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G93" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H93" t="s">
@@ -3725,19 +3725,19 @@
       <c r="B103" s="2">
         <v>1003009</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="2">
         <v>1003</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <v>9</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="2">
         <v>81</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="2">
         <v>6</v>
       </c>
-      <c r="G103" t="s">
+      <c r="G103" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H103" t="s">
@@ -3751,19 +3751,19 @@
       <c r="B104" s="2">
         <v>1003010</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="2">
         <v>1003</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="2">
         <v>10</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="2">
         <v>91</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="2">
         <v>8</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G104" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H104" t="s">
@@ -3777,19 +3777,19 @@
       <c r="B105" s="2">
         <v>1003011</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="2">
         <v>1003</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="2">
         <v>11</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="2">
         <v>102</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="2">
         <v>8</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G105" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H105" t="s">
@@ -3803,19 +3803,19 @@
       <c r="B106" s="2">
         <v>1003012</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="2">
         <v>1003</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="2">
         <v>12</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="2">
         <v>115</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="2">
         <v>9</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G106" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H106" t="s">
@@ -3829,19 +3829,19 @@
       <c r="B107" s="2">
         <v>1003013</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="2">
         <v>1003</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="2">
         <v>13</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="2">
         <v>105</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="2">
         <v>8</v>
       </c>
-      <c r="G107" t="s">
+      <c r="G107" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H107" t="s">
@@ -3855,19 +3855,19 @@
       <c r="B108" s="2">
         <v>1003014</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="2">
         <v>1003</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="2">
         <v>14</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="2">
         <v>118</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="2">
         <v>10</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G108" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H108" t="s">
@@ -3881,19 +3881,19 @@
       <c r="B109" s="2">
         <v>1003015</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="2">
         <v>1003</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="2">
         <v>15</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="2">
         <v>133</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="2">
         <v>10</v>
       </c>
-      <c r="G109" t="s">
+      <c r="G109" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H109" t="s">
@@ -3907,19 +3907,19 @@
       <c r="B110" s="2">
         <v>1003016</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="2">
         <v>1003</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="2">
         <v>16</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="2">
         <v>150</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="2">
         <v>12</v>
       </c>
-      <c r="G110" t="s">
+      <c r="G110" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H110" t="s">
@@ -3933,19 +3933,19 @@
       <c r="B111" s="2">
         <v>1003017</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="2">
         <v>1003</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="2">
         <v>17</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="2">
         <v>137</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="2">
         <v>10</v>
       </c>
-      <c r="G111" t="s">
+      <c r="G111" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H111" t="s">
@@ -3959,19 +3959,19 @@
       <c r="B112" s="2">
         <v>1003018</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="2">
         <v>1003</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="2">
         <v>18</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="2">
         <v>154</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="2">
         <v>12</v>
       </c>
-      <c r="G112" t="s">
+      <c r="G112" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H112" t="s">
@@ -3985,19 +3985,19 @@
       <c r="B113" s="2">
         <v>1003019</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="2">
         <v>1003</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="2">
         <v>19</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="2">
         <v>173</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="2">
         <v>12</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G113" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H113" t="s">
@@ -4011,19 +4011,19 @@
       <c r="B114" s="2">
         <v>1003020</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="2">
         <v>1003</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="2">
         <v>20</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="2">
         <v>195</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="2">
         <v>15</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G114" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H114" t="s">
@@ -4037,19 +4037,19 @@
       <c r="B115" s="2">
         <v>1003021</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="2">
         <v>1003</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="2">
         <v>21</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="2">
         <v>178</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="2">
         <v>12</v>
       </c>
-      <c r="G115" t="s">
+      <c r="G115" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H115" t="s">
@@ -4063,19 +4063,19 @@
       <c r="B116" s="2">
         <v>1003022</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="2">
         <v>1003</v>
       </c>
-      <c r="D116">
-        <v>22</v>
-      </c>
-      <c r="E116">
+      <c r="D116" s="2">
+        <v>22</v>
+      </c>
+      <c r="E116" s="2">
         <v>200</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="2">
         <v>15</v>
       </c>
-      <c r="G116" t="s">
+      <c r="G116" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H116" t="s">
@@ -4089,19 +4089,19 @@
       <c r="B117" s="2">
         <v>1003023</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="2">
         <v>1003</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="2">
         <v>23</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="2">
         <v>225</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="2">
         <v>15</v>
       </c>
-      <c r="G117" t="s">
+      <c r="G117" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H117" t="s">
@@ -4115,19 +4115,19 @@
       <c r="B118" s="2">
         <v>1003024</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="2">
         <v>1003</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="2">
         <v>24</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="2">
         <v>253</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="2">
         <v>18</v>
       </c>
-      <c r="G118" t="s">
+      <c r="G118" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H118" t="s">
@@ -4141,19 +4141,19 @@
       <c r="B119" s="2">
         <v>1003025</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="2">
         <v>1003</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="2">
         <v>25</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="2">
         <v>232</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="2">
         <v>15</v>
       </c>
-      <c r="G119" t="s">
+      <c r="G119" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H119" t="s">
@@ -4167,19 +4167,19 @@
       <c r="B120" s="2">
         <v>1003026</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="2">
         <v>1003</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="2">
         <v>26</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="2">
         <v>259</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="2">
         <v>19</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G120" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H120" t="s">
@@ -4193,19 +4193,19 @@
       <c r="B121" s="2">
         <v>1003027</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="2">
         <v>1003</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="2">
         <v>27</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="2">
         <v>292</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="2">
         <v>19</v>
       </c>
-      <c r="G121" t="s">
+      <c r="G121" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H121" t="s">
@@ -4219,19 +4219,19 @@
       <c r="B122" s="2">
         <v>1003028</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="2">
         <v>1003</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="2">
         <v>28</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="2">
         <v>329</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="2">
         <v>23</v>
       </c>
-      <c r="G122" t="s">
+      <c r="G122" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H122" t="s">
@@ -4245,19 +4245,19 @@
       <c r="B123" s="2">
         <v>1003029</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="2">
         <v>1003</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="2">
         <v>29</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="2">
         <v>301</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="2">
         <v>19</v>
       </c>
-      <c r="G123" t="s">
+      <c r="G123" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H123" t="s">
@@ -4271,19 +4271,19 @@
       <c r="B124" s="2">
         <v>1003030</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="2">
         <v>1003</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="2">
         <v>30</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="2">
         <v>337</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="2">
         <v>24</v>
       </c>
-      <c r="G124" t="s">
+      <c r="G124" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H124" t="s">
@@ -4297,19 +4297,19 @@
       <c r="B125" s="2">
         <v>1003031</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="2">
         <v>1003</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="2">
         <v>31</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="2">
         <v>380</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="2">
         <v>24</v>
       </c>
-      <c r="G125" t="s">
+      <c r="G125" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H125" t="s">
@@ -4323,19 +4323,19 @@
       <c r="B126" s="2">
         <v>1003032</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="2">
         <v>1003</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="2">
         <v>32</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="2">
         <v>428</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="2">
         <v>29</v>
       </c>
-      <c r="G126" t="s">
+      <c r="G126" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H126" t="s">
@@ -4349,19 +4349,19 @@
       <c r="B127" s="2">
         <v>1003033</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="2">
         <v>1003</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="2">
         <v>33</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="2">
         <v>392</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="2">
         <v>24</v>
       </c>
-      <c r="G127" t="s">
+      <c r="G127" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H127" t="s">
@@ -4375,19 +4375,19 @@
       <c r="B128" s="2">
         <v>1003034</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="2">
         <v>1003</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="2">
         <v>34</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="2">
         <v>439</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="2">
         <v>30</v>
       </c>
-      <c r="G128" t="s">
+      <c r="G128" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H128" t="s">
@@ -4401,19 +4401,19 @@
       <c r="B129" s="2">
         <v>1003035</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="2">
         <v>1003</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="2">
         <v>35</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="2">
         <v>493</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="2">
         <v>30</v>
       </c>
-      <c r="G129" t="s">
+      <c r="G129" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H129" t="s">
@@ -4427,19 +4427,19 @@
       <c r="B130" s="2">
         <v>1003036</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="2">
         <v>1003</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="2">
         <v>36</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="2">
         <v>556</v>
       </c>
-      <c r="F130">
+      <c r="F130" s="2">
         <v>36</v>
       </c>
-      <c r="G130" t="s">
+      <c r="G130" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H130" t="s">
@@ -4453,19 +4453,19 @@
       <c r="B131" s="2">
         <v>1003037</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="2">
         <v>1003</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="2">
         <v>37</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="2">
         <v>509</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="2">
         <v>30</v>
       </c>
-      <c r="G131" t="s">
+      <c r="G131" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H131" t="s">
@@ -4479,19 +4479,19 @@
       <c r="B132" s="2">
         <v>1003038</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="2">
         <v>1003</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="2">
         <v>38</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="2">
         <v>570</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="2">
         <v>37</v>
       </c>
-      <c r="G132" t="s">
+      <c r="G132" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H132" t="s">
@@ -4505,19 +4505,19 @@
       <c r="B133" s="2">
         <v>1003039</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="2">
         <v>1003</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="2">
         <v>39</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="2">
         <v>641</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="2">
         <v>37</v>
       </c>
-      <c r="G133" t="s">
+      <c r="G133" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H133" t="s">
@@ -4531,19 +4531,19 @@
       <c r="B134" s="2">
         <v>1003040</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="2">
         <v>1003</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="2">
         <v>40</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="2">
         <v>723</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="2">
         <v>45</v>
       </c>
-      <c r="G134" t="s">
+      <c r="G134" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H134" t="s">
@@ -4557,19 +4557,19 @@
       <c r="B135" s="2">
         <v>1003041</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="2">
         <v>1003</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="2">
         <v>41</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="2">
         <v>662</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="2">
         <v>37</v>
       </c>
-      <c r="G135" t="s">
+      <c r="G135" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H135" t="s">
@@ -4583,19 +4583,19 @@
       <c r="B136" s="2">
         <v>1003042</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="2">
         <v>1003</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="2">
         <v>42</v>
       </c>
-      <c r="E136">
+      <c r="E136" s="2">
         <v>741</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="2">
         <v>47</v>
       </c>
-      <c r="G136" t="s">
+      <c r="G136" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H136" t="s">
@@ -4609,19 +4609,19 @@
       <c r="B137" s="2">
         <v>1003043</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="2">
         <v>1003</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="2">
         <v>43</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="2">
         <v>834</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="2">
         <v>47</v>
       </c>
-      <c r="G137" t="s">
+      <c r="G137" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H137" t="s">
@@ -4635,19 +4635,19 @@
       <c r="B138" s="2">
         <v>1003044</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="2">
         <v>1003</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="2">
         <v>44</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="2">
         <v>940</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="2">
         <v>56</v>
       </c>
-      <c r="G138" t="s">
+      <c r="G138" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H138" t="s">
@@ -4869,19 +4869,19 @@
       <c r="B148" s="2">
         <v>1004009</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="2">
         <v>1004</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="2">
         <v>9</v>
       </c>
-      <c r="E148">
+      <c r="E148" s="2">
         <v>71</v>
       </c>
-      <c r="F148">
+      <c r="F148" s="2">
         <v>5</v>
       </c>
-      <c r="G148" t="s">
+      <c r="G148" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H148" t="s">
@@ -4895,19 +4895,19 @@
       <c r="B149" s="2">
         <v>1004010</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="2">
         <v>1004</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="2">
         <v>10</v>
       </c>
-      <c r="E149">
+      <c r="E149" s="2">
         <v>79</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="2">
         <v>6</v>
       </c>
-      <c r="G149" t="s">
+      <c r="G149" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H149" t="s">
@@ -4921,19 +4921,19 @@
       <c r="B150" s="2">
         <v>1004011</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="2">
         <v>1004</v>
       </c>
-      <c r="D150">
+      <c r="D150" s="2">
         <v>11</v>
       </c>
-      <c r="E150">
+      <c r="E150" s="2">
         <v>89</v>
       </c>
-      <c r="F150">
+      <c r="F150" s="2">
         <v>6</v>
       </c>
-      <c r="G150" t="s">
+      <c r="G150" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H150" t="s">
@@ -4947,19 +4947,19 @@
       <c r="B151" s="2">
         <v>1004012</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="2">
         <v>1004</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="2">
         <v>12</v>
       </c>
-      <c r="E151">
+      <c r="E151" s="2">
         <v>101</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="2">
         <v>8</v>
       </c>
-      <c r="G151" t="s">
+      <c r="G151" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H151" t="s">
@@ -4973,19 +4973,19 @@
       <c r="B152" s="2">
         <v>1004013</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="2">
         <v>1004</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="2">
         <v>13</v>
       </c>
-      <c r="E152">
+      <c r="E152" s="2">
         <v>92</v>
       </c>
-      <c r="F152">
+      <c r="F152" s="2">
         <v>6</v>
       </c>
-      <c r="G152" t="s">
+      <c r="G152" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H152" t="s">
@@ -4999,19 +4999,19 @@
       <c r="B153" s="2">
         <v>1004014</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="2">
         <v>1004</v>
       </c>
-      <c r="D153">
+      <c r="D153" s="2">
         <v>14</v>
       </c>
-      <c r="E153">
+      <c r="E153" s="2">
         <v>103</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="2">
         <v>8</v>
       </c>
-      <c r="G153" t="s">
+      <c r="G153" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H153" t="s">
@@ -5025,19 +5025,19 @@
       <c r="B154" s="2">
         <v>1004015</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="2">
         <v>1004</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="2">
         <v>15</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="2">
         <v>116</v>
       </c>
-      <c r="F154">
+      <c r="F154" s="2">
         <v>8</v>
       </c>
-      <c r="G154" t="s">
+      <c r="G154" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H154" t="s">
@@ -5051,19 +5051,19 @@
       <c r="B155" s="2">
         <v>1004016</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="2">
         <v>1004</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="2">
         <v>16</v>
       </c>
-      <c r="E155">
+      <c r="E155" s="2">
         <v>131</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="2">
         <v>10</v>
       </c>
-      <c r="G155" t="s">
+      <c r="G155" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H155" t="s">
@@ -5077,19 +5077,19 @@
       <c r="B156" s="2">
         <v>1004017</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="2">
         <v>1004</v>
       </c>
-      <c r="D156">
+      <c r="D156" s="2">
         <v>17</v>
       </c>
-      <c r="E156">
+      <c r="E156" s="2">
         <v>120</v>
       </c>
-      <c r="F156">
+      <c r="F156" s="2">
         <v>7</v>
       </c>
-      <c r="G156" t="s">
+      <c r="G156" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H156" t="s">
@@ -5103,19 +5103,19 @@
       <c r="B157" s="2">
         <v>1004018</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="2">
         <v>1004</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="2">
         <v>18</v>
       </c>
-      <c r="E157">
+      <c r="E157" s="2">
         <v>134</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="2">
         <v>10</v>
       </c>
-      <c r="G157" t="s">
+      <c r="G157" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H157" t="s">
@@ -5129,19 +5129,19 @@
       <c r="B158" s="2">
         <v>1004019</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="2">
         <v>1004</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="2">
         <v>19</v>
       </c>
-      <c r="E158">
+      <c r="E158" s="2">
         <v>151</v>
       </c>
-      <c r="F158">
+      <c r="F158" s="2">
         <v>10</v>
       </c>
-      <c r="G158" t="s">
+      <c r="G158" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H158" t="s">
@@ -5155,19 +5155,19 @@
       <c r="B159" s="2">
         <v>1004020</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="2">
         <v>1004</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="2">
         <v>20</v>
       </c>
-      <c r="E159">
+      <c r="E159" s="2">
         <v>170</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="2">
         <v>12</v>
       </c>
-      <c r="G159" t="s">
+      <c r="G159" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H159" t="s">
@@ -5181,19 +5181,19 @@
       <c r="B160" s="2">
         <v>1004021</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="2">
         <v>1004</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="2">
         <v>21</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="2">
         <v>156</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="2">
         <v>9</v>
       </c>
-      <c r="G160" t="s">
+      <c r="G160" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H160" t="s">
@@ -5207,19 +5207,19 @@
       <c r="B161" s="2">
         <v>1004022</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="2">
         <v>1004</v>
       </c>
-      <c r="D161">
-        <v>22</v>
-      </c>
-      <c r="E161">
+      <c r="D161" s="2">
+        <v>22</v>
+      </c>
+      <c r="E161" s="2">
         <v>175</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="2">
         <v>12</v>
       </c>
-      <c r="G161" t="s">
+      <c r="G161" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H161" t="s">
@@ -5233,19 +5233,19 @@
       <c r="B162" s="2">
         <v>1004023</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="2">
         <v>1004</v>
       </c>
-      <c r="D162">
+      <c r="D162" s="2">
         <v>23</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="2">
         <v>196</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="2">
         <v>12</v>
       </c>
-      <c r="G162" t="s">
+      <c r="G162" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H162" t="s">
@@ -5259,19 +5259,19 @@
       <c r="B163" s="2">
         <v>1004024</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="2">
         <v>1004</v>
       </c>
-      <c r="D163">
+      <c r="D163" s="2">
         <v>24</v>
       </c>
-      <c r="E163">
+      <c r="E163" s="2">
         <v>221</v>
       </c>
-      <c r="F163">
+      <c r="F163" s="2">
         <v>15</v>
       </c>
-      <c r="G163" t="s">
+      <c r="G163" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H163" t="s">
@@ -5285,19 +5285,19 @@
       <c r="B164" s="2">
         <v>1004025</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="2">
         <v>1004</v>
       </c>
-      <c r="D164">
+      <c r="D164" s="2">
         <v>25</v>
       </c>
-      <c r="E164">
+      <c r="E164" s="2">
         <v>203</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="2">
         <v>11</v>
       </c>
-      <c r="G164" t="s">
+      <c r="G164" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H164" t="s">
@@ -5311,19 +5311,19 @@
       <c r="B165" s="2">
         <v>1004026</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="2">
         <v>1004</v>
       </c>
-      <c r="D165">
+      <c r="D165" s="2">
         <v>26</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="2">
         <v>227</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="2">
         <v>15</v>
       </c>
-      <c r="G165" t="s">
+      <c r="G165" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H165" t="s">
@@ -5337,19 +5337,19 @@
       <c r="B166" s="2">
         <v>1004027</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="2">
         <v>1004</v>
       </c>
-      <c r="D166">
+      <c r="D166" s="2">
         <v>27</v>
       </c>
-      <c r="E166">
+      <c r="E166" s="2">
         <v>255</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="2">
         <v>15</v>
       </c>
-      <c r="G166" t="s">
+      <c r="G166" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H166" t="s">
@@ -5363,19 +5363,19 @@
       <c r="B167" s="2">
         <v>1004028</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="2">
         <v>1004</v>
       </c>
-      <c r="D167">
+      <c r="D167" s="2">
         <v>28</v>
       </c>
-      <c r="E167">
+      <c r="E167" s="2">
         <v>288</v>
       </c>
-      <c r="F167">
+      <c r="F167" s="2">
         <v>19</v>
       </c>
-      <c r="G167" t="s">
+      <c r="G167" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H167" t="s">
@@ -5389,19 +5389,19 @@
       <c r="B168" s="2">
         <v>1004029</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="2">
         <v>1004</v>
       </c>
-      <c r="D168">
+      <c r="D168" s="2">
         <v>29</v>
       </c>
-      <c r="E168">
+      <c r="E168" s="2">
         <v>264</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="2">
         <v>14</v>
       </c>
-      <c r="G168" t="s">
+      <c r="G168" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H168" t="s">
@@ -5415,19 +5415,19 @@
       <c r="B169" s="2">
         <v>1004030</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="2">
         <v>1004</v>
       </c>
-      <c r="D169">
+      <c r="D169" s="2">
         <v>30</v>
       </c>
-      <c r="E169">
+      <c r="E169" s="2">
         <v>295</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="2">
         <v>19</v>
       </c>
-      <c r="G169" t="s">
+      <c r="G169" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H169" t="s">
@@ -5441,19 +5441,19 @@
       <c r="B170" s="2">
         <v>1004031</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="2">
         <v>1004</v>
       </c>
-      <c r="D170">
+      <c r="D170" s="2">
         <v>31</v>
       </c>
-      <c r="E170">
+      <c r="E170" s="2">
         <v>332</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="2">
         <v>19</v>
       </c>
-      <c r="G170" t="s">
+      <c r="G170" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H170" t="s">
@@ -5467,19 +5467,19 @@
       <c r="B171" s="2">
         <v>1004032</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="2">
         <v>1004</v>
       </c>
-      <c r="D171">
+      <c r="D171" s="2">
         <v>32</v>
       </c>
-      <c r="E171">
+      <c r="E171" s="2">
         <v>374</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="2">
         <v>24</v>
       </c>
-      <c r="G171" t="s">
+      <c r="G171" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H171" t="s">
@@ -5493,19 +5493,19 @@
       <c r="B172" s="2">
         <v>1004033</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="2">
         <v>1004</v>
       </c>
-      <c r="D172">
+      <c r="D172" s="2">
         <v>33</v>
       </c>
-      <c r="E172">
+      <c r="E172" s="2">
         <v>343</v>
       </c>
-      <c r="F172">
+      <c r="F172" s="2">
         <v>18</v>
       </c>
-      <c r="G172" t="s">
+      <c r="G172" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H172" t="s">
@@ -5519,19 +5519,19 @@
       <c r="B173" s="2">
         <v>1004034</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="2">
         <v>1004</v>
       </c>
-      <c r="D173">
+      <c r="D173" s="2">
         <v>34</v>
       </c>
-      <c r="E173">
+      <c r="E173" s="2">
         <v>384</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="2">
         <v>24</v>
       </c>
-      <c r="G173" t="s">
+      <c r="G173" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H173" t="s">
@@ -5545,19 +5545,19 @@
       <c r="B174" s="2">
         <v>1004035</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="2">
         <v>1004</v>
       </c>
-      <c r="D174">
+      <c r="D174" s="2">
         <v>35</v>
       </c>
-      <c r="E174">
+      <c r="E174" s="2">
         <v>432</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="2">
         <v>24</v>
       </c>
-      <c r="G174" t="s">
+      <c r="G174" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H174" t="s">
@@ -5571,19 +5571,19 @@
       <c r="B175" s="2">
         <v>1004036</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="2">
         <v>1004</v>
       </c>
-      <c r="D175">
+      <c r="D175" s="2">
         <v>36</v>
       </c>
-      <c r="E175">
+      <c r="E175" s="2">
         <v>487</v>
       </c>
-      <c r="F175">
+      <c r="F175" s="2">
         <v>30</v>
       </c>
-      <c r="G175" t="s">
+      <c r="G175" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H175" t="s">
@@ -5597,19 +5597,19 @@
       <c r="B176" s="2">
         <v>1004037</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="2">
         <v>1004</v>
       </c>
-      <c r="D176">
+      <c r="D176" s="2">
         <v>37</v>
       </c>
-      <c r="E176">
+      <c r="E176" s="2">
         <v>445</v>
       </c>
-      <c r="F176">
-        <v>22</v>
-      </c>
-      <c r="G176" t="s">
+      <c r="F176" s="2">
+        <v>22</v>
+      </c>
+      <c r="G176" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H176" t="s">
@@ -5623,19 +5623,19 @@
       <c r="B177" s="2">
         <v>1004038</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="2">
         <v>1004</v>
       </c>
-      <c r="D177">
+      <c r="D177" s="2">
         <v>38</v>
       </c>
-      <c r="E177">
+      <c r="E177" s="2">
         <v>499</v>
       </c>
-      <c r="F177">
+      <c r="F177" s="2">
         <v>30</v>
       </c>
-      <c r="G177" t="s">
+      <c r="G177" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H177" t="s">
@@ -5649,19 +5649,19 @@
       <c r="B178" s="2">
         <v>1004039</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="2">
         <v>1004</v>
       </c>
-      <c r="D178">
+      <c r="D178" s="2">
         <v>39</v>
       </c>
-      <c r="E178">
+      <c r="E178" s="2">
         <v>561</v>
       </c>
-      <c r="F178">
+      <c r="F178" s="2">
         <v>30</v>
       </c>
-      <c r="G178" t="s">
+      <c r="G178" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H178" t="s">
@@ -5675,19 +5675,19 @@
       <c r="B179" s="2">
         <v>1004040</v>
       </c>
-      <c r="C179">
+      <c r="C179" s="2">
         <v>1004</v>
       </c>
-      <c r="D179">
+      <c r="D179" s="2">
         <v>40</v>
       </c>
-      <c r="E179">
+      <c r="E179" s="2">
         <v>632</v>
       </c>
-      <c r="F179">
+      <c r="F179" s="2">
         <v>37</v>
       </c>
-      <c r="G179" t="s">
+      <c r="G179" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H179" t="s">
@@ -5701,19 +5701,19 @@
       <c r="B180" s="2">
         <v>1004041</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="2">
         <v>1004</v>
       </c>
-      <c r="D180">
+      <c r="D180" s="2">
         <v>41</v>
       </c>
-      <c r="E180">
+      <c r="E180" s="2">
         <v>579</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="2">
         <v>28</v>
       </c>
-      <c r="G180" t="s">
+      <c r="G180" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H180" t="s">
@@ -5727,19 +5727,19 @@
       <c r="B181" s="2">
         <v>1004042</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="2">
         <v>1004</v>
       </c>
-      <c r="D181">
+      <c r="D181" s="2">
         <v>42</v>
       </c>
-      <c r="E181">
+      <c r="E181" s="2">
         <v>648</v>
       </c>
-      <c r="F181">
+      <c r="F181" s="2">
         <v>37</v>
       </c>
-      <c r="G181" t="s">
+      <c r="G181" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H181" t="s">
@@ -5753,19 +5753,19 @@
       <c r="B182" s="2">
         <v>1004043</v>
       </c>
-      <c r="C182">
+      <c r="C182" s="2">
         <v>1004</v>
       </c>
-      <c r="D182">
+      <c r="D182" s="2">
         <v>43</v>
       </c>
-      <c r="E182">
+      <c r="E182" s="2">
         <v>730</v>
       </c>
-      <c r="F182">
+      <c r="F182" s="2">
         <v>37</v>
       </c>
-      <c r="G182" t="s">
+      <c r="G182" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H182" t="s">
@@ -5779,19 +5779,19 @@
       <c r="B183" s="2">
         <v>1004044</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="2">
         <v>1004</v>
       </c>
-      <c r="D183">
+      <c r="D183" s="2">
         <v>44</v>
       </c>
-      <c r="E183">
+      <c r="E183" s="2">
         <v>822</v>
       </c>
-      <c r="F183">
+      <c r="F183" s="2">
         <v>47</v>
       </c>
-      <c r="G183" t="s">
+      <c r="G183" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H183" t="s">
@@ -6013,19 +6013,19 @@
       <c r="B193" s="2">
         <v>1005009</v>
       </c>
-      <c r="C193">
+      <c r="C193" s="2">
         <v>1005</v>
       </c>
-      <c r="D193">
+      <c r="D193" s="2">
         <v>9</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="2">
         <v>98</v>
       </c>
-      <c r="F193">
+      <c r="F193" s="2">
         <v>3</v>
       </c>
-      <c r="G193" t="s">
+      <c r="G193" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H193" t="s">
@@ -6039,19 +6039,19 @@
       <c r="B194" s="2">
         <v>1005010</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="2">
         <v>1005</v>
       </c>
-      <c r="D194">
+      <c r="D194" s="2">
         <v>10</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="2">
         <v>110</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="2">
         <v>5</v>
       </c>
-      <c r="G194" t="s">
+      <c r="G194" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H194" t="s">
@@ -6065,19 +6065,19 @@
       <c r="B195" s="2">
         <v>1005011</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="2">
         <v>1005</v>
       </c>
-      <c r="D195">
+      <c r="D195" s="2">
         <v>11</v>
       </c>
-      <c r="E195">
+      <c r="E195" s="2">
         <v>124</v>
       </c>
-      <c r="F195">
+      <c r="F195" s="2">
         <v>5</v>
       </c>
-      <c r="G195" t="s">
+      <c r="G195" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H195" t="s">
@@ -6091,19 +6091,19 @@
       <c r="B196" s="2">
         <v>1005012</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="2">
         <v>1005</v>
       </c>
-      <c r="D196">
+      <c r="D196" s="2">
         <v>12</v>
       </c>
-      <c r="E196">
+      <c r="E196" s="2">
         <v>139</v>
       </c>
-      <c r="F196">
+      <c r="F196" s="2">
         <v>6</v>
       </c>
-      <c r="G196" t="s">
+      <c r="G196" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H196" t="s">
@@ -6117,19 +6117,19 @@
       <c r="B197" s="2">
         <v>1005013</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="2">
         <v>1005</v>
       </c>
-      <c r="D197">
+      <c r="D197" s="2">
         <v>13</v>
       </c>
-      <c r="E197">
+      <c r="E197" s="2">
         <v>127</v>
       </c>
-      <c r="F197">
+      <c r="F197" s="2">
         <v>4</v>
       </c>
-      <c r="G197" t="s">
+      <c r="G197" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H197" t="s">
@@ -6143,19 +6143,19 @@
       <c r="B198" s="2">
         <v>1005014</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="2">
         <v>1005</v>
       </c>
-      <c r="D198">
+      <c r="D198" s="2">
         <v>14</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="2">
         <v>143</v>
       </c>
-      <c r="F198">
+      <c r="F198" s="2">
         <v>6</v>
       </c>
-      <c r="G198" t="s">
+      <c r="G198" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H198" t="s">
@@ -6169,19 +6169,19 @@
       <c r="B199" s="2">
         <v>1005015</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="2">
         <v>1005</v>
       </c>
-      <c r="D199">
+      <c r="D199" s="2">
         <v>15</v>
       </c>
-      <c r="E199">
+      <c r="E199" s="2">
         <v>161</v>
       </c>
-      <c r="F199">
+      <c r="F199" s="2">
         <v>6</v>
       </c>
-      <c r="G199" t="s">
+      <c r="G199" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H199" t="s">
@@ -6195,19 +6195,19 @@
       <c r="B200" s="2">
         <v>1005016</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="2">
         <v>1005</v>
       </c>
-      <c r="D200">
+      <c r="D200" s="2">
         <v>16</v>
       </c>
-      <c r="E200">
+      <c r="E200" s="2">
         <v>181</v>
       </c>
-      <c r="F200">
+      <c r="F200" s="2">
         <v>8</v>
       </c>
-      <c r="G200" t="s">
+      <c r="G200" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H200" t="s">
@@ -6221,19 +6221,19 @@
       <c r="B201" s="2">
         <v>1005017</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="2">
         <v>1005</v>
       </c>
-      <c r="D201">
+      <c r="D201" s="2">
         <v>17</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="2">
         <v>166</v>
       </c>
-      <c r="F201">
+      <c r="F201" s="2">
         <v>5</v>
       </c>
-      <c r="G201" t="s">
+      <c r="G201" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H201" t="s">
@@ -6247,19 +6247,19 @@
       <c r="B202" s="2">
         <v>1005018</v>
       </c>
-      <c r="C202">
+      <c r="C202" s="2">
         <v>1005</v>
       </c>
-      <c r="D202">
+      <c r="D202" s="2">
         <v>18</v>
       </c>
-      <c r="E202">
+      <c r="E202" s="2">
         <v>186</v>
       </c>
-      <c r="F202">
+      <c r="F202" s="2">
         <v>7</v>
       </c>
-      <c r="G202" t="s">
+      <c r="G202" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H202" t="s">
@@ -6273,19 +6273,19 @@
       <c r="B203" s="2">
         <v>1005019</v>
       </c>
-      <c r="C203">
+      <c r="C203" s="2">
         <v>1005</v>
       </c>
-      <c r="D203">
+      <c r="D203" s="2">
         <v>19</v>
       </c>
-      <c r="E203">
+      <c r="E203" s="2">
         <v>209</v>
       </c>
-      <c r="F203">
+      <c r="F203" s="2">
         <v>7</v>
       </c>
-      <c r="G203" t="s">
+      <c r="G203" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H203" t="s">
@@ -6299,19 +6299,19 @@
       <c r="B204" s="2">
         <v>1005020</v>
       </c>
-      <c r="C204">
+      <c r="C204" s="2">
         <v>1005</v>
       </c>
-      <c r="D204">
+      <c r="D204" s="2">
         <v>20</v>
       </c>
-      <c r="E204">
+      <c r="E204" s="2">
         <v>235</v>
       </c>
-      <c r="F204">
+      <c r="F204" s="2">
         <v>10</v>
       </c>
-      <c r="G204" t="s">
+      <c r="G204" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H204" t="s">
@@ -6325,19 +6325,19 @@
       <c r="B205" s="2">
         <v>1005021</v>
       </c>
-      <c r="C205">
+      <c r="C205" s="2">
         <v>1005</v>
       </c>
-      <c r="D205">
+      <c r="D205" s="2">
         <v>21</v>
       </c>
-      <c r="E205">
+      <c r="E205" s="2">
         <v>215</v>
       </c>
-      <c r="F205">
+      <c r="F205" s="2">
         <v>6</v>
       </c>
-      <c r="G205" t="s">
+      <c r="G205" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H205" t="s">
@@ -6351,19 +6351,19 @@
       <c r="B206" s="2">
         <v>1005022</v>
       </c>
-      <c r="C206">
+      <c r="C206" s="2">
         <v>1005</v>
       </c>
-      <c r="D206">
-        <v>22</v>
-      </c>
-      <c r="E206">
+      <c r="D206" s="2">
+        <v>22</v>
+      </c>
+      <c r="E206" s="2">
         <v>241</v>
       </c>
-      <c r="F206">
+      <c r="F206" s="2">
         <v>9</v>
       </c>
-      <c r="G206" t="s">
+      <c r="G206" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H206" t="s">
@@ -6377,19 +6377,19 @@
       <c r="B207" s="2">
         <v>1005023</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="2">
         <v>1005</v>
       </c>
-      <c r="D207">
+      <c r="D207" s="2">
         <v>23</v>
       </c>
-      <c r="E207">
+      <c r="E207" s="2">
         <v>271</v>
       </c>
-      <c r="F207">
+      <c r="F207" s="2">
         <v>9</v>
       </c>
-      <c r="G207" t="s">
+      <c r="G207" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H207" t="s">
@@ -6403,19 +6403,19 @@
       <c r="B208" s="2">
         <v>1005024</v>
       </c>
-      <c r="C208">
+      <c r="C208" s="2">
         <v>1005</v>
       </c>
-      <c r="D208">
+      <c r="D208" s="2">
         <v>24</v>
       </c>
-      <c r="E208">
+      <c r="E208" s="2">
         <v>306</v>
       </c>
-      <c r="F208">
+      <c r="F208" s="2">
         <v>12</v>
       </c>
-      <c r="G208" t="s">
+      <c r="G208" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H208" t="s">
@@ -6429,19 +6429,19 @@
       <c r="B209" s="2">
         <v>1005025</v>
       </c>
-      <c r="C209">
+      <c r="C209" s="2">
         <v>1005</v>
       </c>
-      <c r="D209">
+      <c r="D209" s="2">
         <v>25</v>
       </c>
-      <c r="E209">
+      <c r="E209" s="2">
         <v>280</v>
       </c>
-      <c r="F209">
+      <c r="F209" s="2">
         <v>8</v>
       </c>
-      <c r="G209" t="s">
+      <c r="G209" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H209" t="s">
@@ -6455,19 +6455,19 @@
       <c r="B210" s="2">
         <v>1005026</v>
       </c>
-      <c r="C210">
+      <c r="C210" s="2">
         <v>1005</v>
       </c>
-      <c r="D210">
+      <c r="D210" s="2">
         <v>26</v>
       </c>
-      <c r="E210">
+      <c r="E210" s="2">
         <v>314</v>
       </c>
-      <c r="F210">
+      <c r="F210" s="2">
         <v>11</v>
       </c>
-      <c r="G210" t="s">
+      <c r="G210" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H210" t="s">
@@ -6481,19 +6481,19 @@
       <c r="B211" s="2">
         <v>1005027</v>
       </c>
-      <c r="C211">
+      <c r="C211" s="2">
         <v>1005</v>
       </c>
-      <c r="D211">
+      <c r="D211" s="2">
         <v>27</v>
       </c>
-      <c r="E211">
+      <c r="E211" s="2">
         <v>353</v>
       </c>
-      <c r="F211">
+      <c r="F211" s="2">
         <v>11</v>
       </c>
-      <c r="G211" t="s">
+      <c r="G211" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H211" t="s">
@@ -6507,19 +6507,19 @@
       <c r="B212" s="2">
         <v>1005028</v>
       </c>
-      <c r="C212">
+      <c r="C212" s="2">
         <v>1005</v>
       </c>
-      <c r="D212">
+      <c r="D212" s="2">
         <v>28</v>
       </c>
-      <c r="E212">
+      <c r="E212" s="2">
         <v>398</v>
       </c>
-      <c r="F212">
+      <c r="F212" s="2">
         <v>15</v>
       </c>
-      <c r="G212" t="s">
+      <c r="G212" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H212" t="s">
@@ -6533,19 +6533,19 @@
       <c r="B213" s="2">
         <v>1005029</v>
       </c>
-      <c r="C213">
+      <c r="C213" s="2">
         <v>1005</v>
       </c>
-      <c r="D213">
+      <c r="D213" s="2">
         <v>29</v>
       </c>
-      <c r="E213">
+      <c r="E213" s="2">
         <v>364</v>
       </c>
-      <c r="F213">
+      <c r="F213" s="2">
         <v>10</v>
       </c>
-      <c r="G213" t="s">
+      <c r="G213" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H213" t="s">
@@ -6559,19 +6559,19 @@
       <c r="B214" s="2">
         <v>1005030</v>
       </c>
-      <c r="C214">
+      <c r="C214" s="2">
         <v>1005</v>
       </c>
-      <c r="D214">
+      <c r="D214" s="2">
         <v>30</v>
       </c>
-      <c r="E214">
+      <c r="E214" s="2">
         <v>408</v>
       </c>
-      <c r="F214">
+      <c r="F214" s="2">
         <v>14</v>
       </c>
-      <c r="G214" t="s">
+      <c r="G214" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H214" t="s">
@@ -6585,19 +6585,19 @@
       <c r="B215" s="2">
         <v>1005031</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="2">
         <v>1005</v>
       </c>
-      <c r="D215">
+      <c r="D215" s="2">
         <v>31</v>
       </c>
-      <c r="E215">
+      <c r="E215" s="2">
         <v>459</v>
       </c>
-      <c r="F215">
+      <c r="F215" s="2">
         <v>14</v>
       </c>
-      <c r="G215" t="s">
+      <c r="G215" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H215" t="s">
@@ -6611,19 +6611,19 @@
       <c r="B216" s="2">
         <v>1005032</v>
       </c>
-      <c r="C216">
+      <c r="C216" s="2">
         <v>1005</v>
       </c>
-      <c r="D216">
+      <c r="D216" s="2">
         <v>32</v>
       </c>
-      <c r="E216">
+      <c r="E216" s="2">
         <v>517</v>
       </c>
-      <c r="F216">
+      <c r="F216" s="2">
         <v>19</v>
       </c>
-      <c r="G216" t="s">
+      <c r="G216" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H216" t="s">
@@ -6637,19 +6637,19 @@
       <c r="B217" s="2">
         <v>1005033</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="2">
         <v>1005</v>
       </c>
-      <c r="D217">
+      <c r="D217" s="2">
         <v>33</v>
       </c>
-      <c r="E217">
+      <c r="E217" s="2">
         <v>473</v>
       </c>
-      <c r="F217">
+      <c r="F217" s="2">
         <v>12</v>
       </c>
-      <c r="G217" t="s">
+      <c r="G217" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H217" t="s">
@@ -6663,19 +6663,19 @@
       <c r="B218" s="2">
         <v>1005034</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="2">
         <v>1005</v>
       </c>
-      <c r="D218">
+      <c r="D218" s="2">
         <v>34</v>
       </c>
-      <c r="E218">
+      <c r="E218" s="2">
         <v>530</v>
       </c>
-      <c r="F218">
+      <c r="F218" s="2">
         <v>18</v>
       </c>
-      <c r="G218" t="s">
+      <c r="G218" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H218" t="s">
@@ -6689,19 +6689,19 @@
       <c r="B219" s="2">
         <v>1005035</v>
       </c>
-      <c r="C219">
+      <c r="C219" s="2">
         <v>1005</v>
       </c>
-      <c r="D219">
+      <c r="D219" s="2">
         <v>35</v>
       </c>
-      <c r="E219">
+      <c r="E219" s="2">
         <v>596</v>
       </c>
-      <c r="F219">
+      <c r="F219" s="2">
         <v>18</v>
       </c>
-      <c r="G219" t="s">
+      <c r="G219" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H219" t="s">
@@ -6715,19 +6715,19 @@
       <c r="B220" s="2">
         <v>1005036</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="2">
         <v>1005</v>
       </c>
-      <c r="D220">
+      <c r="D220" s="2">
         <v>36</v>
       </c>
-      <c r="E220">
+      <c r="E220" s="2">
         <v>672</v>
       </c>
-      <c r="F220">
+      <c r="F220" s="2">
         <v>24</v>
       </c>
-      <c r="G220" t="s">
+      <c r="G220" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H220" t="s">
@@ -6741,19 +6741,19 @@
       <c r="B221" s="2">
         <v>1005037</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="2">
         <v>1005</v>
       </c>
-      <c r="D221">
+      <c r="D221" s="2">
         <v>37</v>
       </c>
-      <c r="E221">
+      <c r="E221" s="2">
         <v>615</v>
       </c>
-      <c r="F221">
+      <c r="F221" s="2">
         <v>15</v>
       </c>
-      <c r="G221" t="s">
+      <c r="G221" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H221" t="s">
@@ -6767,19 +6767,19 @@
       <c r="B222" s="2">
         <v>1005038</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="2">
         <v>1005</v>
       </c>
-      <c r="D222">
+      <c r="D222" s="2">
         <v>38</v>
       </c>
-      <c r="E222">
+      <c r="E222" s="2">
         <v>689</v>
       </c>
-      <c r="F222">
-        <v>22</v>
-      </c>
-      <c r="G222" t="s">
+      <c r="F222" s="2">
+        <v>22</v>
+      </c>
+      <c r="G222" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H222" t="s">
@@ -6793,19 +6793,19 @@
       <c r="B223" s="2">
         <v>1005039</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="2">
         <v>1005</v>
       </c>
-      <c r="D223">
+      <c r="D223" s="2">
         <v>39</v>
       </c>
-      <c r="E223">
+      <c r="E223" s="2">
         <v>775</v>
       </c>
-      <c r="F223">
-        <v>22</v>
-      </c>
-      <c r="G223" t="s">
+      <c r="F223" s="2">
+        <v>22</v>
+      </c>
+      <c r="G223" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H223" t="s">
@@ -6819,19 +6819,19 @@
       <c r="B224" s="2">
         <v>1005040</v>
       </c>
-      <c r="C224">
+      <c r="C224" s="2">
         <v>1005</v>
       </c>
-      <c r="D224">
+      <c r="D224" s="2">
         <v>40</v>
       </c>
-      <c r="E224">
+      <c r="E224" s="2">
         <v>873</v>
       </c>
-      <c r="F224">
+      <c r="F224" s="2">
         <v>30</v>
       </c>
-      <c r="G224" t="s">
+      <c r="G224" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H224" t="s">
@@ -6845,19 +6845,19 @@
       <c r="B225" s="2">
         <v>1005041</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="2">
         <v>1005</v>
       </c>
-      <c r="D225">
+      <c r="D225" s="2">
         <v>41</v>
       </c>
-      <c r="E225">
+      <c r="E225" s="2">
         <v>800</v>
       </c>
-      <c r="F225">
+      <c r="F225" s="2">
         <v>19</v>
       </c>
-      <c r="G225" t="s">
+      <c r="G225" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H225" t="s">
@@ -6871,19 +6871,19 @@
       <c r="B226" s="2">
         <v>1005042</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="2">
         <v>1005</v>
       </c>
-      <c r="D226">
+      <c r="D226" s="2">
         <v>42</v>
       </c>
-      <c r="E226">
+      <c r="E226" s="2">
         <v>896</v>
       </c>
-      <c r="F226">
+      <c r="F226" s="2">
         <v>28</v>
       </c>
-      <c r="G226" t="s">
+      <c r="G226" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H226" t="s">
@@ -6897,19 +6897,19 @@
       <c r="B227" s="2">
         <v>1005043</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="2">
         <v>1005</v>
       </c>
-      <c r="D227">
+      <c r="D227" s="2">
         <v>43</v>
       </c>
-      <c r="E227">
+      <c r="E227" s="2">
         <v>1007</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="2">
         <v>28</v>
       </c>
-      <c r="G227" t="s">
+      <c r="G227" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H227" t="s">
@@ -6923,19 +6923,19 @@
       <c r="B228" s="2">
         <v>1005044</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="2">
         <v>1005</v>
       </c>
-      <c r="D228">
+      <c r="D228" s="2">
         <v>44</v>
       </c>
-      <c r="E228">
+      <c r="E228" s="2">
         <v>1135</v>
       </c>
-      <c r="F228">
+      <c r="F228" s="2">
         <v>37</v>
       </c>
-      <c r="G228" t="s">
+      <c r="G228" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H228" t="s">
@@ -7001,16 +7001,16 @@
       <c r="B232" s="2">
         <v>2001003</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="2">
         <v>2001</v>
       </c>
-      <c r="D232">
+      <c r="D232" s="2">
         <v>3</v>
       </c>
-      <c r="E232">
+      <c r="E232" s="2">
         <v>338</v>
       </c>
-      <c r="F232">
+      <c r="F232" s="2">
         <v>16</v>
       </c>
       <c r="G232" t="s">
@@ -7027,16 +7027,16 @@
       <c r="B233" s="2">
         <v>2001004</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="2">
         <v>2001</v>
       </c>
-      <c r="D233">
+      <c r="D233" s="2">
         <v>4</v>
       </c>
-      <c r="E233">
+      <c r="E233" s="2">
         <v>439</v>
       </c>
-      <c r="F233">
+      <c r="F233" s="2">
         <v>20</v>
       </c>
       <c r="G233" t="s">
@@ -7053,16 +7053,16 @@
       <c r="B234" s="2">
         <v>2001005</v>
       </c>
-      <c r="C234">
+      <c r="C234" s="2">
         <v>2001</v>
       </c>
-      <c r="D234">
+      <c r="D234" s="2">
         <v>5</v>
       </c>
-      <c r="E234">
+      <c r="E234" s="2">
         <v>571</v>
       </c>
-      <c r="F234">
+      <c r="F234" s="2">
         <v>24</v>
       </c>
       <c r="G234" t="s">
@@ -7079,16 +7079,16 @@
       <c r="B235" s="2">
         <v>2001006</v>
       </c>
-      <c r="C235">
+      <c r="C235" s="2">
         <v>2001</v>
       </c>
-      <c r="D235">
+      <c r="D235" s="2">
         <v>6</v>
       </c>
-      <c r="E235">
+      <c r="E235" s="2">
         <v>743</v>
       </c>
-      <c r="F235">
+      <c r="F235" s="2">
         <v>31</v>
       </c>
       <c r="G235" t="s">
@@ -7105,16 +7105,16 @@
       <c r="B236" s="2">
         <v>2001007</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="2">
         <v>2001</v>
       </c>
-      <c r="D236">
+      <c r="D236" s="2">
         <v>7</v>
       </c>
-      <c r="E236">
+      <c r="E236" s="2">
         <v>965</v>
       </c>
-      <c r="F236">
+      <c r="F236" s="2">
         <v>38</v>
       </c>
       <c r="G236" t="s">
@@ -7131,16 +7131,16 @@
       <c r="B237" s="2">
         <v>2001008</v>
       </c>
-      <c r="C237">
+      <c r="C237" s="2">
         <v>2001</v>
       </c>
-      <c r="D237">
+      <c r="D237" s="2">
         <v>8</v>
       </c>
-      <c r="E237">
+      <c r="E237" s="2">
         <v>1255</v>
       </c>
-      <c r="F237">
+      <c r="F237" s="2">
         <v>48</v>
       </c>
       <c r="G237" t="s">
@@ -7157,16 +7157,16 @@
       <c r="B238" s="2">
         <v>2001009</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="2">
         <v>2001</v>
       </c>
-      <c r="D238">
+      <c r="D238" s="2">
         <v>9</v>
       </c>
-      <c r="E238">
+      <c r="E238" s="2">
         <v>1631</v>
       </c>
-      <c r="F238">
+      <c r="F238" s="2">
         <v>60</v>
       </c>
       <c r="G238" t="s">
@@ -7183,16 +7183,16 @@
       <c r="B239" s="2">
         <v>2001010</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="2">
         <v>2001</v>
       </c>
-      <c r="D239">
+      <c r="D239" s="2">
         <v>10</v>
       </c>
-      <c r="E239">
+      <c r="E239" s="2">
         <v>2121</v>
       </c>
-      <c r="F239">
+      <c r="F239" s="2">
         <v>75</v>
       </c>
       <c r="G239" t="s">
@@ -7209,16 +7209,16 @@
       <c r="B240" s="2">
         <v>2001011</v>
       </c>
-      <c r="C240">
+      <c r="C240" s="2">
         <v>2001</v>
       </c>
-      <c r="D240">
+      <c r="D240" s="2">
         <v>11</v>
       </c>
-      <c r="E240">
+      <c r="E240" s="2">
         <v>2757</v>
       </c>
-      <c r="F240">
+      <c r="F240" s="2">
         <v>93</v>
       </c>
       <c r="G240" t="s">

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14445" windowHeight="11505"/>
+    <workbookView windowWidth="13695" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -59,6 +59,12 @@
   </si>
   <si>
     <t>Icon</t>
+  </si>
+  <si>
+    <t>BaseMap</t>
+  </si>
+  <si>
+    <t>HealthBar</t>
   </si>
   <si>
     <t>MonsterEntry</t>
@@ -95,6 +101,12 @@
   </si>
   <si>
     <t>怪物icon</t>
+  </si>
+  <si>
+    <t>怪物底图</t>
+  </si>
+  <si>
+    <t>怪物血条</t>
   </si>
   <si>
     <t>怪物机制</t>
@@ -1113,7 +1125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:L240"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
@@ -1125,11 +1137,13 @@
     <col min="7" max="7" width="6.95" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.475" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.91666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.4916666666667" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.36666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.4333333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.4916666666667" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1160,72 +1174,90 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="B5" s="1">
         <v>1001001</v>
       </c>
@@ -1242,16 +1274,16 @@
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="B6" s="1">
         <v>1001002</v>
       </c>
@@ -1268,16 +1300,16 @@
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="B7" s="1">
         <v>1001003</v>
       </c>
@@ -1294,16 +1326,16 @@
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="B8" s="1">
         <v>1001004</v>
       </c>
@@ -1320,16 +1352,16 @@
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="B9" s="1">
         <v>1001005</v>
       </c>
@@ -1346,16 +1378,16 @@
         <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="B10" s="1">
         <v>1001006</v>
       </c>
@@ -1372,16 +1404,16 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="B11" s="1">
         <v>1001007</v>
       </c>
@@ -1398,16 +1430,16 @@
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="B12" s="1">
         <v>1001008</v>
       </c>
@@ -1424,16 +1456,16 @@
         <v>5</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="B13" s="2">
         <v>1001009</v>
       </c>
@@ -1450,16 +1482,16 @@
         <v>3</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="B14" s="2">
         <v>1001010</v>
       </c>
@@ -1476,16 +1508,16 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="B15" s="2">
         <v>1001011</v>
       </c>
@@ -1502,16 +1534,16 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="B16" s="2">
         <v>1001012</v>
       </c>
@@ -1528,13 +1560,13 @@
         <v>6</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -1554,13 +1586,13 @@
         <v>4</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -1580,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="2:9">
@@ -1606,13 +1638,13 @@
         <v>6</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I19" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="2:9">
@@ -1632,13 +1664,13 @@
         <v>8</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H20" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I20" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="2:9">
@@ -1658,13 +1690,13 @@
         <v>5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H21" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I21" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -1684,13 +1716,13 @@
         <v>7</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H22" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -1710,13 +1742,13 @@
         <v>7</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="2:9">
@@ -1736,13 +1768,13 @@
         <v>10</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I24" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="2:9">
@@ -1762,13 +1794,13 @@
         <v>6</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I25" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="2:9">
@@ -1788,13 +1820,13 @@
         <v>9</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I26" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="2:9">
@@ -1814,13 +1846,13 @@
         <v>9</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I27" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -1840,13 +1872,13 @@
         <v>12</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H28" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I28" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="2:9">
@@ -1866,13 +1898,13 @@
         <v>8</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H29" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I29" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="2:9">
@@ -1892,13 +1924,13 @@
         <v>11</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H30" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I30" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="2:9">
@@ -1918,13 +1950,13 @@
         <v>11</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I31" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="2:9">
@@ -1944,13 +1976,13 @@
         <v>15</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H32" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="2:9">
@@ -1970,13 +2002,13 @@
         <v>10</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I33" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -1996,13 +2028,13 @@
         <v>14</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H34" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I34" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="2:9">
@@ -2022,13 +2054,13 @@
         <v>14</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H35" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I35" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="2:9">
@@ -2048,13 +2080,13 @@
         <v>19</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H36" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I36" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="2:9">
@@ -2074,13 +2106,13 @@
         <v>12</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H37" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I37" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="2:9">
@@ -2100,13 +2132,13 @@
         <v>18</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H38" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I38" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="2:9">
@@ -2126,13 +2158,13 @@
         <v>18</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H39" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I39" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="2:9">
@@ -2152,13 +2184,13 @@
         <v>24</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H40" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I40" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="2:9">
@@ -2178,13 +2210,13 @@
         <v>15</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H41" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I41" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="2:9">
@@ -2204,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H42" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I42" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="2:9">
@@ -2230,13 +2262,13 @@
         <v>22</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H43" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I43" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="2:9">
@@ -2256,13 +2288,13 @@
         <v>30</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H44" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I44" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="2:9">
@@ -2282,13 +2314,13 @@
         <v>19</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H45" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I45" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="2:9">
@@ -2308,13 +2340,13 @@
         <v>28</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H46" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I46" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="2:9">
@@ -2334,13 +2366,13 @@
         <v>28</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H47" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I47" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="2:9">
@@ -2360,13 +2392,13 @@
         <v>37</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H48" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="2:9">
@@ -2386,13 +2418,13 @@
         <v>3</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="2:9">
@@ -2412,13 +2444,13 @@
         <v>4</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="2:9">
@@ -2438,13 +2470,13 @@
         <v>4</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="2:9">
@@ -2464,13 +2496,13 @@
         <v>5</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="2:9">
@@ -2490,13 +2522,13 @@
         <v>4</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="2:9">
@@ -2516,13 +2548,13 @@
         <v>5</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="2:9">
@@ -2542,13 +2574,13 @@
         <v>5</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="2:9">
@@ -2568,13 +2600,13 @@
         <v>6</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="2:9">
@@ -2594,13 +2626,13 @@
         <v>5</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H58" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I58" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="2:9">
@@ -2620,13 +2652,13 @@
         <v>6</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H59" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I59" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="2:9">
@@ -2646,13 +2678,13 @@
         <v>6</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H60" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="2:9">
@@ -2672,13 +2704,13 @@
         <v>8</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H61" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I61" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="2:9">
@@ -2698,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H62" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="2:9">
@@ -2724,13 +2756,13 @@
         <v>8</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H63" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I63" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="2:9">
@@ -2750,13 +2782,13 @@
         <v>8</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H64" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I64" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="2:9">
@@ -2776,13 +2808,13 @@
         <v>10</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H65" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="2:9">
@@ -2802,13 +2834,13 @@
         <v>7</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H66" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="2:9">
@@ -2828,13 +2860,13 @@
         <v>10</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="2:9">
@@ -2854,13 +2886,13 @@
         <v>10</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H68" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I68" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="2:9">
@@ -2880,13 +2912,13 @@
         <v>12</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H69" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I69" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="2:9">
@@ -2906,13 +2938,13 @@
         <v>9</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H70" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="2:9">
@@ -2932,13 +2964,13 @@
         <v>12</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H71" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="2:9">
@@ -2958,13 +2990,13 @@
         <v>12</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H72" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="2:9">
@@ -2984,13 +3016,13 @@
         <v>15</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H73" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="2:9">
@@ -3010,13 +3042,13 @@
         <v>11</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="2:9">
@@ -3036,13 +3068,13 @@
         <v>15</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H75" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I75" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="2:9">
@@ -3062,13 +3094,13 @@
         <v>15</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H76" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="2:9">
@@ -3088,13 +3120,13 @@
         <v>19</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H77" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I77" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="2:9">
@@ -3114,13 +3146,13 @@
         <v>14</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="2:9">
@@ -3140,13 +3172,13 @@
         <v>19</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H79" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="2:9">
@@ -3166,13 +3198,13 @@
         <v>19</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H80" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="2:9">
@@ -3192,13 +3224,13 @@
         <v>24</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H81" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I81" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="2:9">
@@ -3218,13 +3250,13 @@
         <v>18</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H82" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I82" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="2:9">
@@ -3244,13 +3276,13 @@
         <v>24</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H83" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I83" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="2:9">
@@ -3270,13 +3302,13 @@
         <v>24</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H84" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I84" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="2:9">
@@ -3296,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H85" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I85" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="2:9">
@@ -3322,13 +3354,13 @@
         <v>22</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H86" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="2:9">
@@ -3348,13 +3380,13 @@
         <v>30</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H87" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I87" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="2:9">
@@ -3374,13 +3406,13 @@
         <v>30</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H88" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I88" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="2:9">
@@ -3400,13 +3432,13 @@
         <v>37</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H89" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I89" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="2:9">
@@ -3426,13 +3458,13 @@
         <v>28</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H90" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I90" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="2:9">
@@ -3452,13 +3484,13 @@
         <v>37</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H91" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I91" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="2:9">
@@ -3478,13 +3510,13 @@
         <v>37</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H92" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I92" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="2:9">
@@ -3504,13 +3536,13 @@
         <v>47</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H93" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I93" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="2:9">
@@ -3530,13 +3562,13 @@
         <v>4</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="2:9">
@@ -3556,13 +3588,13 @@
         <v>5</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="2:9">
@@ -3582,13 +3614,13 @@
         <v>5</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="2:9">
@@ -3608,13 +3640,13 @@
         <v>6</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="2:9">
@@ -3634,13 +3666,13 @@
         <v>5</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="2:9">
@@ -3660,13 +3692,13 @@
         <v>6</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="2:9">
@@ -3686,13 +3718,13 @@
         <v>6</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="2:9">
@@ -3712,13 +3744,13 @@
         <v>8</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="2:9">
@@ -3738,13 +3770,13 @@
         <v>6</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H103" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I103" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="2:9">
@@ -3764,13 +3796,13 @@
         <v>8</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H104" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I104" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="2:9">
@@ -3790,13 +3822,13 @@
         <v>8</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H105" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I105" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="2:9">
@@ -3816,13 +3848,13 @@
         <v>9</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H106" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I106" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="2:9">
@@ -3842,13 +3874,13 @@
         <v>8</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H107" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I107" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="2:9">
@@ -3868,13 +3900,13 @@
         <v>10</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H108" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I108" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="2:9">
@@ -3894,13 +3926,13 @@
         <v>10</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H109" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I109" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="2:9">
@@ -3920,13 +3952,13 @@
         <v>12</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H110" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I110" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="2:9">
@@ -3946,13 +3978,13 @@
         <v>10</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H111" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I111" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="2:9">
@@ -3972,13 +4004,13 @@
         <v>12</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H112" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I112" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113" spans="2:9">
@@ -3998,13 +4030,13 @@
         <v>12</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H113" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I113" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="2:9">
@@ -4024,13 +4056,13 @@
         <v>15</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H114" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I114" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="2:9">
@@ -4050,13 +4082,13 @@
         <v>12</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H115" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I115" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="2:9">
@@ -4076,13 +4108,13 @@
         <v>15</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H116" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I116" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="2:9">
@@ -4102,13 +4134,13 @@
         <v>15</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H117" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I117" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="2:9">
@@ -4128,13 +4160,13 @@
         <v>18</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H118" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I118" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="2:9">
@@ -4154,13 +4186,13 @@
         <v>15</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H119" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I119" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="2:9">
@@ -4180,13 +4212,13 @@
         <v>19</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H120" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I120" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="2:9">
@@ -4206,13 +4238,13 @@
         <v>19</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H121" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I121" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="2:9">
@@ -4232,13 +4264,13 @@
         <v>23</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H122" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I122" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="2:9">
@@ -4258,13 +4290,13 @@
         <v>19</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H123" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I123" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="2:9">
@@ -4284,13 +4316,13 @@
         <v>24</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H124" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I124" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125" spans="2:9">
@@ -4310,13 +4342,13 @@
         <v>24</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H125" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I125" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="2:9">
@@ -4336,13 +4368,13 @@
         <v>29</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H126" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I126" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127" spans="2:9">
@@ -4362,13 +4394,13 @@
         <v>24</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H127" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I127" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" spans="2:9">
@@ -4388,13 +4420,13 @@
         <v>30</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H128" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I128" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="2:9">
@@ -4414,13 +4446,13 @@
         <v>30</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H129" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I129" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="2:9">
@@ -4440,13 +4472,13 @@
         <v>36</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H130" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I130" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131" spans="2:9">
@@ -4466,13 +4498,13 @@
         <v>30</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H131" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I131" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="132" spans="2:9">
@@ -4492,13 +4524,13 @@
         <v>37</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H132" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I132" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="2:9">
@@ -4518,13 +4550,13 @@
         <v>37</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H133" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I133" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134" spans="2:9">
@@ -4544,13 +4576,13 @@
         <v>45</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H134" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I134" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135" spans="2:9">
@@ -4570,13 +4602,13 @@
         <v>37</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H135" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I135" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136" spans="2:9">
@@ -4596,13 +4628,13 @@
         <v>47</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H136" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I136" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137" spans="2:9">
@@ -4622,13 +4654,13 @@
         <v>47</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H137" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I137" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="2:9">
@@ -4648,13 +4680,13 @@
         <v>56</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H138" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I138" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="2:9">
@@ -4674,13 +4706,13 @@
         <v>3</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="141" spans="2:9">
@@ -4700,13 +4732,13 @@
         <v>4</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="2:9">
@@ -4726,13 +4758,13 @@
         <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="143" spans="2:9">
@@ -4752,13 +4784,13 @@
         <v>5</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="144" spans="2:9">
@@ -4778,13 +4810,13 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" spans="2:9">
@@ -4804,13 +4836,13 @@
         <v>5</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="146" spans="2:9">
@@ -4830,13 +4862,13 @@
         <v>5</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147" spans="2:9">
@@ -4856,13 +4888,13 @@
         <v>6</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="148" spans="2:9">
@@ -4882,13 +4914,13 @@
         <v>5</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H148" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I148" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="149" spans="2:9">
@@ -4908,13 +4940,13 @@
         <v>6</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H149" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I149" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="150" spans="2:9">
@@ -4934,13 +4966,13 @@
         <v>6</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H150" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I150" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="151" spans="2:9">
@@ -4960,13 +4992,13 @@
         <v>8</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H151" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I151" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="152" spans="2:9">
@@ -4986,13 +5018,13 @@
         <v>6</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H152" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I152" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="153" spans="2:9">
@@ -5012,13 +5044,13 @@
         <v>8</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H153" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I153" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="154" spans="2:9">
@@ -5038,13 +5070,13 @@
         <v>8</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H154" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I154" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="155" spans="2:9">
@@ -5064,13 +5096,13 @@
         <v>10</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H155" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I155" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" spans="2:9">
@@ -5090,13 +5122,13 @@
         <v>7</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H156" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I156" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="157" spans="2:9">
@@ -5116,13 +5148,13 @@
         <v>10</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H157" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I157" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="158" spans="2:9">
@@ -5142,13 +5174,13 @@
         <v>10</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H158" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I158" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" spans="2:9">
@@ -5168,13 +5200,13 @@
         <v>12</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H159" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I159" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" spans="2:9">
@@ -5194,13 +5226,13 @@
         <v>9</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H160" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I160" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="161" spans="2:9">
@@ -5220,13 +5252,13 @@
         <v>12</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H161" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I161" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="162" spans="2:9">
@@ -5246,13 +5278,13 @@
         <v>12</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H162" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I162" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="163" spans="2:9">
@@ -5272,13 +5304,13 @@
         <v>15</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H163" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I163" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="164" spans="2:9">
@@ -5298,13 +5330,13 @@
         <v>11</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H164" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I164" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="2:9">
@@ -5324,13 +5356,13 @@
         <v>15</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H165" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I165" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="166" spans="2:9">
@@ -5350,13 +5382,13 @@
         <v>15</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H166" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I166" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="167" spans="2:9">
@@ -5376,13 +5408,13 @@
         <v>19</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H167" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I167" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" spans="2:9">
@@ -5402,13 +5434,13 @@
         <v>14</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H168" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I168" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="2:9">
@@ -5428,13 +5460,13 @@
         <v>19</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H169" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I169" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="2:9">
@@ -5454,13 +5486,13 @@
         <v>19</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H170" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I170" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="171" spans="2:9">
@@ -5480,13 +5512,13 @@
         <v>24</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H171" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I171" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="172" spans="2:9">
@@ -5506,13 +5538,13 @@
         <v>18</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H172" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I172" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="2:9">
@@ -5532,13 +5564,13 @@
         <v>24</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H173" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I173" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174" spans="2:9">
@@ -5558,13 +5590,13 @@
         <v>24</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H174" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I174" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="2:9">
@@ -5584,13 +5616,13 @@
         <v>30</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H175" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I175" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="176" spans="2:9">
@@ -5610,13 +5642,13 @@
         <v>22</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H176" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I176" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="177" spans="2:9">
@@ -5636,13 +5668,13 @@
         <v>30</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H177" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I177" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178" spans="2:9">
@@ -5662,13 +5694,13 @@
         <v>30</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H178" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I178" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="179" spans="2:9">
@@ -5688,13 +5720,13 @@
         <v>37</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H179" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I179" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="2:9">
@@ -5714,13 +5746,13 @@
         <v>28</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H180" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I180" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="2:9">
@@ -5740,13 +5772,13 @@
         <v>37</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H181" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I181" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="182" spans="2:9">
@@ -5766,13 +5798,13 @@
         <v>37</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H182" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I182" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="183" spans="2:9">
@@ -5792,13 +5824,13 @@
         <v>47</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H183" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I183" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="185" spans="2:9">
@@ -5818,13 +5850,13 @@
         <v>2</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="186" spans="2:9">
@@ -5844,13 +5876,13 @@
         <v>3</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="187" spans="2:9">
@@ -5870,13 +5902,13 @@
         <v>3</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="188" spans="2:9">
@@ -5896,13 +5928,13 @@
         <v>4</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="189" spans="2:9">
@@ -5922,13 +5954,13 @@
         <v>3</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="190" spans="2:9">
@@ -5948,13 +5980,13 @@
         <v>4</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="191" spans="2:9">
@@ -5974,13 +6006,13 @@
         <v>4</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="192" spans="2:9">
@@ -6000,13 +6032,13 @@
         <v>5</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193" spans="2:9">
@@ -6026,13 +6058,13 @@
         <v>3</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H193" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I193" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="194" spans="2:9">
@@ -6052,13 +6084,13 @@
         <v>5</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H194" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I194" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="195" spans="2:9">
@@ -6078,13 +6110,13 @@
         <v>5</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H195" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I195" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="196" spans="2:9">
@@ -6104,13 +6136,13 @@
         <v>6</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H196" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I196" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="197" spans="2:9">
@@ -6130,13 +6162,13 @@
         <v>4</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H197" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I197" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="198" spans="2:9">
@@ -6156,13 +6188,13 @@
         <v>6</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H198" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I198" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199" spans="2:9">
@@ -6182,13 +6214,13 @@
         <v>6</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H199" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I199" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="200" spans="2:9">
@@ -6208,13 +6240,13 @@
         <v>8</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H200" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I200" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="201" spans="2:9">
@@ -6234,13 +6266,13 @@
         <v>5</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H201" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I201" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="202" spans="2:9">
@@ -6260,13 +6292,13 @@
         <v>7</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H202" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I202" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="203" spans="2:9">
@@ -6286,13 +6318,13 @@
         <v>7</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H203" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I203" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="204" spans="2:9">
@@ -6312,13 +6344,13 @@
         <v>10</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H204" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I204" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="205" spans="2:9">
@@ -6338,13 +6370,13 @@
         <v>6</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H205" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I205" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="206" spans="2:9">
@@ -6364,13 +6396,13 @@
         <v>9</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H206" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I206" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="207" spans="2:9">
@@ -6390,13 +6422,13 @@
         <v>9</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H207" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I207" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="208" spans="2:9">
@@ -6416,13 +6448,13 @@
         <v>12</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H208" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I208" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="209" spans="2:9">
@@ -6442,13 +6474,13 @@
         <v>8</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H209" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I209" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="210" spans="2:9">
@@ -6468,13 +6500,13 @@
         <v>11</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H210" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I210" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="211" spans="2:9">
@@ -6494,13 +6526,13 @@
         <v>11</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H211" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I211" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="212" spans="2:9">
@@ -6520,13 +6552,13 @@
         <v>15</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H212" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I212" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="213" spans="2:9">
@@ -6546,13 +6578,13 @@
         <v>10</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H213" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I213" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="214" spans="2:9">
@@ -6572,13 +6604,13 @@
         <v>14</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H214" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I214" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="215" spans="2:9">
@@ -6598,13 +6630,13 @@
         <v>14</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H215" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I215" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="216" spans="2:9">
@@ -6624,13 +6656,13 @@
         <v>19</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H216" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I216" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="217" spans="2:9">
@@ -6650,13 +6682,13 @@
         <v>12</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H217" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I217" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="218" spans="2:9">
@@ -6676,13 +6708,13 @@
         <v>18</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H218" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I218" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="219" spans="2:9">
@@ -6702,13 +6734,13 @@
         <v>18</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H219" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I219" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="220" spans="2:9">
@@ -6728,13 +6760,13 @@
         <v>24</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H220" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I220" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="221" spans="2:9">
@@ -6754,13 +6786,13 @@
         <v>15</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H221" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I221" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="222" spans="2:9">
@@ -6780,13 +6812,13 @@
         <v>22</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H222" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I222" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="223" spans="2:9">
@@ -6806,13 +6838,13 @@
         <v>22</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H223" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I223" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="224" spans="2:9">
@@ -6832,13 +6864,13 @@
         <v>30</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H224" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I224" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="225" spans="2:9">
@@ -6858,13 +6890,13 @@
         <v>19</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H225" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I225" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="226" spans="2:9">
@@ -6884,13 +6916,13 @@
         <v>28</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H226" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I226" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="227" spans="2:9">
@@ -6910,13 +6942,13 @@
         <v>28</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H227" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I227" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="228" spans="2:9">
@@ -6936,13 +6968,13 @@
         <v>37</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H228" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I228" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="230" spans="2:9">
@@ -6962,13 +6994,13 @@
         <v>10</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="231" spans="2:9">
@@ -6988,13 +7020,13 @@
         <v>13</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="232" spans="2:9">
@@ -7014,13 +7046,13 @@
         <v>16</v>
       </c>
       <c r="G232" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H232" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I232" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="233" spans="2:9">
@@ -7040,13 +7072,13 @@
         <v>20</v>
       </c>
       <c r="G233" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H233" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I233" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="234" spans="2:9">
@@ -7066,13 +7098,13 @@
         <v>24</v>
       </c>
       <c r="G234" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H234" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I234" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="235" spans="2:9">
@@ -7092,13 +7124,13 @@
         <v>31</v>
       </c>
       <c r="G235" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H235" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I235" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="236" spans="2:9">
@@ -7118,13 +7150,13 @@
         <v>38</v>
       </c>
       <c r="G236" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H236" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I236" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="237" spans="2:9">
@@ -7144,13 +7176,13 @@
         <v>48</v>
       </c>
       <c r="G237" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H237" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I237" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="238" spans="2:9">
@@ -7170,13 +7202,13 @@
         <v>60</v>
       </c>
       <c r="G238" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H238" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I238" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="239" spans="2:9">
@@ -7196,13 +7228,13 @@
         <v>75</v>
       </c>
       <c r="G239" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H239" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I239" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="240" spans="2:9">
@@ -7222,13 +7254,13 @@
         <v>93</v>
       </c>
       <c r="G240" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H240" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I240" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13695" windowHeight="9555"/>
+    <workbookView windowWidth="16245" windowHeight="7590"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>enemy1</t>
+  </si>
+  <si>
+    <t>PurpleMonsterBaseFrame</t>
+  </si>
+  <si>
+    <t>PurpleMonsterBaseFrameBox</t>
   </si>
   <si>
     <t>狼哥</t>
@@ -1268,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>55</v>
+        <v>262</v>
       </c>
       <c r="F5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>26</v>
@@ -1281,6 +1287,12 @@
       </c>
       <c r="I5" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1294,10 +1306,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>62</v>
+        <v>559</v>
       </c>
       <c r="F6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>26</v>
@@ -1307,6 +1319,12 @@
       </c>
       <c r="I6" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1320,10 +1338,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>69</v>
+        <v>1195</v>
       </c>
       <c r="F7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>26</v>
@@ -1333,6 +1351,12 @@
       </c>
       <c r="I7" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1346,10 +1370,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>78</v>
+        <v>2663</v>
       </c>
       <c r="F8" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>26</v>
@@ -1359,6 +1383,12 @@
       </c>
       <c r="I8" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1372,10 +1402,10 @@
         <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="F9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>26</v>
@@ -1385,6 +1415,12 @@
       </c>
       <c r="I9" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1398,10 +1434,10 @@
         <v>6</v>
       </c>
       <c r="E10" s="1">
-        <v>80</v>
+        <v>650</v>
       </c>
       <c r="F10" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>26</v>
@@ -1411,6 +1447,12 @@
       </c>
       <c r="I10" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1424,10 +1466,10 @@
         <v>7</v>
       </c>
       <c r="E11" s="1">
-        <v>90</v>
+        <v>1513</v>
       </c>
       <c r="F11" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>26</v>
@@ -1437,6 +1479,12 @@
       </c>
       <c r="I11" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1450,10 +1498,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="1">
-        <v>102</v>
+        <v>2849</v>
       </c>
       <c r="F12" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>26</v>
@@ -1463,6 +1511,12 @@
       </c>
       <c r="I12" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1476,7 +1530,7 @@
         <v>9</v>
       </c>
       <c r="E13" s="2">
-        <v>93</v>
+        <v>298</v>
       </c>
       <c r="F13" s="2">
         <v>3</v>
@@ -1489,6 +1543,12 @@
       </c>
       <c r="I13" t="s">
         <v>28</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1502,10 +1562,10 @@
         <v>10</v>
       </c>
       <c r="E14" s="2">
-        <v>104</v>
+        <v>744</v>
       </c>
       <c r="F14" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>26</v>
@@ -1515,6 +1575,12 @@
       </c>
       <c r="I14" t="s">
         <v>28</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1528,10 +1594,10 @@
         <v>11</v>
       </c>
       <c r="E15" s="2">
-        <v>117</v>
+        <v>1884</v>
       </c>
       <c r="F15" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>26</v>
@@ -1541,6 +1607,12 @@
       </c>
       <c r="I15" t="s">
         <v>28</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1554,10 +1626,10 @@
         <v>12</v>
       </c>
       <c r="E16" s="2">
-        <v>132</v>
+        <v>3036</v>
       </c>
       <c r="F16" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>26</v>
@@ -1568,8 +1640,14 @@
       <c r="I16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="2:9">
+      <c r="J16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
       <c r="B17" s="2">
         <v>1001013</v>
       </c>
@@ -1580,10 +1658,10 @@
         <v>13</v>
       </c>
       <c r="E17" s="2">
-        <v>121</v>
+        <v>317</v>
       </c>
       <c r="F17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>26</v>
@@ -1594,8 +1672,14 @@
       <c r="I17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="2:9">
+      <c r="J17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
       <c r="B18" s="2">
         <v>1001014</v>
       </c>
@@ -1606,10 +1690,10 @@
         <v>14</v>
       </c>
       <c r="E18" s="2">
-        <v>135</v>
+        <v>853</v>
       </c>
       <c r="F18" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>26</v>
@@ -1620,8 +1704,14 @@
       <c r="I18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="2:9">
+      <c r="J18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
       <c r="B19" s="2">
         <v>1001015</v>
       </c>
@@ -1632,10 +1722,10 @@
         <v>15</v>
       </c>
       <c r="E19" s="2">
-        <v>152</v>
+        <v>2315</v>
       </c>
       <c r="F19" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>26</v>
@@ -1646,8 +1736,14 @@
       <c r="I19" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="2:9">
+      <c r="J19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
       <c r="B20" s="2">
         <v>1001016</v>
       </c>
@@ -1658,10 +1754,10 @@
         <v>16</v>
       </c>
       <c r="E20" s="2">
-        <v>172</v>
+        <v>3222</v>
       </c>
       <c r="F20" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>26</v>
@@ -1672,8 +1768,14 @@
       <c r="I20" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="2:9">
+      <c r="J20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
       <c r="B21" s="2">
         <v>1001017</v>
       </c>
@@ -1684,10 +1786,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2">
-        <v>157</v>
+        <v>335</v>
       </c>
       <c r="F21" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>26</v>
@@ -1698,8 +1800,14 @@
       <c r="I21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="2:9">
+      <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11">
       <c r="B22" s="2">
         <v>1001018</v>
       </c>
@@ -1710,10 +1818,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2">
-        <v>176</v>
+        <v>972</v>
       </c>
       <c r="F22" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>26</v>
@@ -1724,8 +1832,14 @@
       <c r="I22" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="2:9">
+      <c r="J22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
       <c r="B23" s="2">
         <v>1001019</v>
       </c>
@@ -1736,10 +1850,10 @@
         <v>19</v>
       </c>
       <c r="E23" s="2">
-        <v>198</v>
+        <v>2828</v>
       </c>
       <c r="F23" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>26</v>
@@ -1750,8 +1864,14 @@
       <c r="I23" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="2:9">
+      <c r="J23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
       <c r="B24" s="2">
         <v>1001020</v>
       </c>
@@ -1762,10 +1882,10 @@
         <v>20</v>
       </c>
       <c r="E24" s="2">
-        <v>223</v>
+        <v>3409</v>
       </c>
       <c r="F24" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>26</v>
@@ -1776,8 +1896,14 @@
       <c r="I24" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="2:9">
+      <c r="J24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11">
       <c r="B25" s="2">
         <v>1001021</v>
       </c>
@@ -1788,10 +1914,10 @@
         <v>21</v>
       </c>
       <c r="E25" s="2">
-        <v>204</v>
+        <v>353</v>
       </c>
       <c r="F25" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>26</v>
@@ -1802,8 +1928,14 @@
       <c r="I25" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="2:9">
+      <c r="J25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11">
       <c r="B26" s="2">
         <v>1001022</v>
       </c>
@@ -1814,10 +1946,10 @@
         <v>22</v>
       </c>
       <c r="E26" s="2">
-        <v>229</v>
+        <v>1094</v>
       </c>
       <c r="F26" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>26</v>
@@ -1828,8 +1960,14 @@
       <c r="I26" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="27" spans="2:9">
+      <c r="J26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11">
       <c r="B27" s="2">
         <v>1001023</v>
       </c>
@@ -1840,10 +1978,10 @@
         <v>23</v>
       </c>
       <c r="E27" s="2">
-        <v>257</v>
+        <v>3414</v>
       </c>
       <c r="F27" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>26</v>
@@ -1854,8 +1992,14 @@
       <c r="I27" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="28" spans="2:9">
+      <c r="J27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
       <c r="B28" s="2">
         <v>1001024</v>
       </c>
@@ -1866,10 +2010,10 @@
         <v>24</v>
       </c>
       <c r="E28" s="2">
-        <v>290</v>
+        <v>3595</v>
       </c>
       <c r="F28" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>26</v>
@@ -1880,8 +2024,14 @@
       <c r="I28" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="2:9">
+      <c r="J28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
       <c r="B29" s="2">
         <v>1001025</v>
       </c>
@@ -1892,10 +2042,10 @@
         <v>25</v>
       </c>
       <c r="E29" s="2">
-        <v>265</v>
+        <v>372</v>
       </c>
       <c r="F29" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>26</v>
@@ -1906,8 +2056,14 @@
       <c r="I29" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="2:9">
+      <c r="J29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
       <c r="B30" s="2">
         <v>1001026</v>
       </c>
@@ -1918,10 +2074,10 @@
         <v>26</v>
       </c>
       <c r="E30" s="2">
-        <v>297</v>
+        <v>1233</v>
       </c>
       <c r="F30" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>26</v>
@@ -1932,8 +2088,14 @@
       <c r="I30" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="2:9">
+      <c r="J30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
       <c r="B31" s="2">
         <v>1001027</v>
       </c>
@@ -1944,10 +2106,10 @@
         <v>27</v>
       </c>
       <c r="E31" s="2">
-        <v>334</v>
+        <v>3781</v>
       </c>
       <c r="F31" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>26</v>
@@ -1958,8 +2120,14 @@
       <c r="I31" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="2:9">
+      <c r="J31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
       <c r="B32" s="2">
         <v>1001028</v>
       </c>
@@ -1970,10 +2138,10 @@
         <v>28</v>
       </c>
       <c r="E32" s="2">
-        <v>377</v>
+        <v>3781</v>
       </c>
       <c r="F32" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>26</v>
@@ -1984,8 +2152,14 @@
       <c r="I32" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="33" spans="2:9">
+      <c r="J32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
       <c r="B33" s="2">
         <v>1001029</v>
       </c>
@@ -1996,10 +2170,10 @@
         <v>29</v>
       </c>
       <c r="E33" s="2">
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="F33" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>26</v>
@@ -2010,8 +2184,14 @@
       <c r="I33" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="34" spans="2:9">
+      <c r="J33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
       <c r="B34" s="2">
         <v>1001030</v>
       </c>
@@ -2022,10 +2202,10 @@
         <v>30</v>
       </c>
       <c r="E34" s="2">
-        <v>387</v>
+        <v>1374</v>
       </c>
       <c r="F34" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>26</v>
@@ -2036,8 +2216,14 @@
       <c r="I34" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="35" spans="2:9">
+      <c r="J34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
       <c r="B35" s="2">
         <v>1001031</v>
       </c>
@@ -2048,10 +2234,10 @@
         <v>31</v>
       </c>
       <c r="E35" s="2">
-        <v>435</v>
+        <v>3968</v>
       </c>
       <c r="F35" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>26</v>
@@ -2062,8 +2248,14 @@
       <c r="I35" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="36" spans="2:9">
+      <c r="J35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
       <c r="B36" s="2">
         <v>1001032</v>
       </c>
@@ -2074,10 +2266,10 @@
         <v>32</v>
       </c>
       <c r="E36" s="2">
-        <v>490</v>
+        <v>3968</v>
       </c>
       <c r="F36" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>26</v>
@@ -2088,8 +2280,14 @@
       <c r="I36" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="37" spans="2:9">
+      <c r="J36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
       <c r="B37" s="2">
         <v>1001033</v>
       </c>
@@ -2100,10 +2298,10 @@
         <v>33</v>
       </c>
       <c r="E37" s="2">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="F37" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>26</v>
@@ -2114,8 +2312,14 @@
       <c r="I37" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="38" spans="2:9">
+      <c r="J37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
       <c r="B38" s="2">
         <v>1001034</v>
       </c>
@@ -2126,10 +2330,10 @@
         <v>34</v>
       </c>
       <c r="E38" s="2">
-        <v>502</v>
+        <v>1536</v>
       </c>
       <c r="F38" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>26</v>
@@ -2140,8 +2344,14 @@
       <c r="I38" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="39" spans="2:9">
+      <c r="J38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
       <c r="B39" s="2">
         <v>1001035</v>
       </c>
@@ -2152,10 +2362,10 @@
         <v>35</v>
       </c>
       <c r="E39" s="2">
-        <v>565</v>
+        <v>4154</v>
       </c>
       <c r="F39" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>26</v>
@@ -2166,8 +2376,14 @@
       <c r="I39" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="40" spans="2:9">
+      <c r="J39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
       <c r="B40" s="2">
         <v>1001036</v>
       </c>
@@ -2178,10 +2394,10 @@
         <v>36</v>
       </c>
       <c r="E40" s="2">
-        <v>637</v>
+        <v>4154</v>
       </c>
       <c r="F40" s="2">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>26</v>
@@ -2192,8 +2408,14 @@
       <c r="I40" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="41" spans="2:9">
+      <c r="J40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
       <c r="B41" s="2">
         <v>1001037</v>
       </c>
@@ -2204,10 +2426,10 @@
         <v>37</v>
       </c>
       <c r="E41" s="2">
-        <v>583</v>
+        <v>427</v>
       </c>
       <c r="F41" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>26</v>
@@ -2218,8 +2440,14 @@
       <c r="I41" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="42" spans="2:9">
+      <c r="J41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
       <c r="B42" s="2">
         <v>1001038</v>
       </c>
@@ -2230,10 +2458,10 @@
         <v>38</v>
       </c>
       <c r="E42" s="2">
-        <v>653</v>
+        <v>1699</v>
       </c>
       <c r="F42" s="2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>26</v>
@@ -2244,8 +2472,14 @@
       <c r="I42" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="43" spans="2:9">
+      <c r="J42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
       <c r="B43" s="2">
         <v>1001039</v>
       </c>
@@ -2256,10 +2490,10 @@
         <v>39</v>
       </c>
       <c r="E43" s="2">
-        <v>735</v>
+        <v>4341</v>
       </c>
       <c r="F43" s="2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>26</v>
@@ -2270,8 +2504,14 @@
       <c r="I43" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="44" spans="2:9">
+      <c r="J43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
       <c r="B44" s="2">
         <v>1001040</v>
       </c>
@@ -2282,10 +2522,10 @@
         <v>40</v>
       </c>
       <c r="E44" s="2">
-        <v>828</v>
+        <v>4341</v>
       </c>
       <c r="F44" s="2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>26</v>
@@ -2296,8 +2536,14 @@
       <c r="I44" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="45" spans="2:9">
+      <c r="J44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
       <c r="B45" s="2">
         <v>1001041</v>
       </c>
@@ -2308,10 +2554,10 @@
         <v>41</v>
       </c>
       <c r="E45" s="2">
-        <v>758</v>
+        <v>445</v>
       </c>
       <c r="F45" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>26</v>
@@ -2322,8 +2568,14 @@
       <c r="I45" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="46" spans="2:9">
+      <c r="J45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
       <c r="B46" s="2">
         <v>1001042</v>
       </c>
@@ -2334,10 +2586,10 @@
         <v>42</v>
       </c>
       <c r="E46" s="2">
-        <v>849</v>
+        <v>1896</v>
       </c>
       <c r="F46" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>26</v>
@@ -2348,8 +2600,14 @@
       <c r="I46" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="47" spans="2:9">
+      <c r="J46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
       <c r="B47" s="2">
         <v>1001043</v>
       </c>
@@ -2360,10 +2618,10 @@
         <v>43</v>
       </c>
       <c r="E47" s="2">
-        <v>955</v>
+        <v>4527</v>
       </c>
       <c r="F47" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>26</v>
@@ -2374,8 +2632,14 @@
       <c r="I47" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="48" spans="2:9">
+      <c r="J47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11">
       <c r="B48" s="2">
         <v>1001044</v>
       </c>
@@ -2386,10 +2650,10 @@
         <v>44</v>
       </c>
       <c r="E48" s="2">
-        <v>1077</v>
+        <v>4527</v>
       </c>
       <c r="F48" s="2">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>26</v>
@@ -2400,8 +2664,14 @@
       <c r="I48" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="50" spans="2:9">
+      <c r="J48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
       <c r="B50" s="1">
         <v>1002001</v>
       </c>
@@ -2412,22 +2682,28 @@
         <v>1</v>
       </c>
       <c r="E50" s="1">
-        <v>50</v>
+        <v>238</v>
       </c>
       <c r="F50" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
       <c r="B51" s="1">
         <v>1002002</v>
       </c>
@@ -2438,22 +2714,28 @@
         <v>2</v>
       </c>
       <c r="E51" s="1">
-        <v>56</v>
+        <v>508</v>
       </c>
       <c r="F51" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52" s="1">
         <v>1002003</v>
       </c>
@@ -2464,22 +2746,28 @@
         <v>3</v>
       </c>
       <c r="E52" s="1">
-        <v>63</v>
+        <v>1087</v>
       </c>
       <c r="F52" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
       <c r="B53" s="1">
         <v>1002004</v>
       </c>
@@ -2490,22 +2778,28 @@
         <v>4</v>
       </c>
       <c r="E53" s="1">
-        <v>71</v>
+        <v>2421</v>
       </c>
       <c r="F53" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
       <c r="B54" s="1">
         <v>1002005</v>
       </c>
@@ -2516,22 +2810,28 @@
         <v>5</v>
       </c>
       <c r="E54" s="1">
-        <v>65</v>
+        <v>255</v>
       </c>
       <c r="F54" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55" s="1">
         <v>1002006</v>
       </c>
@@ -2542,22 +2842,28 @@
         <v>6</v>
       </c>
       <c r="E55" s="1">
-        <v>73</v>
+        <v>591</v>
       </c>
       <c r="F55" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56" s="1">
         <v>1002007</v>
       </c>
@@ -2568,22 +2874,28 @@
         <v>7</v>
       </c>
       <c r="E56" s="1">
-        <v>82</v>
+        <v>1375</v>
       </c>
       <c r="F56" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57" s="1">
         <v>1002008</v>
       </c>
@@ -2594,22 +2906,28 @@
         <v>8</v>
       </c>
       <c r="E57" s="1">
-        <v>92</v>
+        <v>2590</v>
       </c>
       <c r="F57" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
       <c r="B58" s="2">
         <v>1002009</v>
       </c>
@@ -2620,22 +2938,28 @@
         <v>9</v>
       </c>
       <c r="E58" s="2">
-        <v>85</v>
+        <v>271</v>
       </c>
       <c r="F58" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H58" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" s="2">
         <v>1002010</v>
       </c>
@@ -2646,22 +2970,28 @@
         <v>10</v>
       </c>
       <c r="E59" s="2">
-        <v>95</v>
+        <v>676</v>
       </c>
       <c r="F59" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H59" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I59" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
       <c r="B60" s="2">
         <v>1002011</v>
       </c>
@@ -2672,22 +3002,28 @@
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>106</v>
+        <v>1713</v>
       </c>
       <c r="F60" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H60" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I60" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
       <c r="B61" s="2">
         <v>1002012</v>
       </c>
@@ -2698,22 +3034,28 @@
         <v>12</v>
       </c>
       <c r="E61" s="2">
-        <v>120</v>
+        <v>2760</v>
       </c>
       <c r="F61" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H61" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I61" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
       <c r="B62" s="2">
         <v>1002013</v>
       </c>
@@ -2724,22 +3066,28 @@
         <v>13</v>
       </c>
       <c r="E62" s="2">
-        <v>110</v>
+        <v>288</v>
       </c>
       <c r="F62" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H62" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I62" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
       <c r="B63" s="2">
         <v>1002014</v>
       </c>
@@ -2750,22 +3098,28 @@
         <v>14</v>
       </c>
       <c r="E63" s="2">
-        <v>123</v>
+        <v>776</v>
       </c>
       <c r="F63" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H63" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I63" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
       <c r="B64" s="2">
         <v>1002015</v>
       </c>
@@ -2776,22 +3130,28 @@
         <v>15</v>
       </c>
       <c r="E64" s="2">
-        <v>138</v>
+        <v>2105</v>
       </c>
       <c r="F64" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H64" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I64" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
       <c r="B65" s="2">
         <v>1002016</v>
       </c>
@@ -2802,22 +3162,28 @@
         <v>16</v>
       </c>
       <c r="E65" s="2">
-        <v>156</v>
+        <v>2929</v>
       </c>
       <c r="F65" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H65" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I65" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
       <c r="B66" s="2">
         <v>1002017</v>
       </c>
@@ -2828,22 +3194,28 @@
         <v>17</v>
       </c>
       <c r="E66" s="2">
-        <v>143</v>
+        <v>305</v>
       </c>
       <c r="F66" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H66" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I66" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
       <c r="B67" s="2">
         <v>1002018</v>
       </c>
@@ -2854,22 +3226,28 @@
         <v>18</v>
       </c>
       <c r="E67" s="2">
-        <v>160</v>
+        <v>884</v>
       </c>
       <c r="F67" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H67" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I67" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
       <c r="B68" s="2">
         <v>1002019</v>
       </c>
@@ -2880,22 +3258,28 @@
         <v>19</v>
       </c>
       <c r="E68" s="2">
-        <v>180</v>
+        <v>2571</v>
       </c>
       <c r="F68" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H68" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I68" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11">
       <c r="B69" s="2">
         <v>1002020</v>
       </c>
@@ -2906,22 +3290,28 @@
         <v>20</v>
       </c>
       <c r="E69" s="2">
-        <v>203</v>
+        <v>3099</v>
       </c>
       <c r="F69" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H69" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I69" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
       <c r="B70" s="2">
         <v>1002021</v>
       </c>
@@ -2932,22 +3322,28 @@
         <v>21</v>
       </c>
       <c r="E70" s="2">
-        <v>186</v>
+        <v>321</v>
       </c>
       <c r="F70" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H70" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I70" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
       <c r="B71" s="2">
         <v>1002022</v>
       </c>
@@ -2958,22 +3354,28 @@
         <v>22</v>
       </c>
       <c r="E71" s="2">
-        <v>208</v>
+        <v>994</v>
       </c>
       <c r="F71" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H71" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I71" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
       <c r="B72" s="2">
         <v>1002023</v>
       </c>
@@ -2984,22 +3386,28 @@
         <v>23</v>
       </c>
       <c r="E72" s="2">
-        <v>234</v>
+        <v>3104</v>
       </c>
       <c r="F72" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H72" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I72" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
       <c r="B73" s="2">
         <v>1002024</v>
       </c>
@@ -3010,22 +3418,28 @@
         <v>24</v>
       </c>
       <c r="E73" s="2">
-        <v>264</v>
+        <v>3268</v>
       </c>
       <c r="F73" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H73" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I73" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
       <c r="B74" s="2">
         <v>1002025</v>
       </c>
@@ -3036,22 +3450,28 @@
         <v>25</v>
       </c>
       <c r="E74" s="2">
-        <v>241</v>
+        <v>338</v>
       </c>
       <c r="F74" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H74" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I74" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11">
       <c r="B75" s="2">
         <v>1002026</v>
       </c>
@@ -3062,22 +3482,28 @@
         <v>26</v>
       </c>
       <c r="E75" s="2">
-        <v>270</v>
+        <v>1121</v>
       </c>
       <c r="F75" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H75" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I75" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
       <c r="B76" s="2">
         <v>1002027</v>
       </c>
@@ -3088,22 +3514,28 @@
         <v>27</v>
       </c>
       <c r="E76" s="2">
-        <v>304</v>
+        <v>3438</v>
       </c>
       <c r="F76" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H76" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I76" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
       <c r="B77" s="2">
         <v>1002028</v>
       </c>
@@ -3114,22 +3546,28 @@
         <v>28</v>
       </c>
       <c r="E77" s="2">
-        <v>343</v>
+        <v>3438</v>
       </c>
       <c r="F77" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H77" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I77" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
       <c r="B78" s="2">
         <v>1002029</v>
       </c>
@@ -3140,22 +3578,28 @@
         <v>29</v>
       </c>
       <c r="E78" s="2">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="F78" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I78" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
       <c r="B79" s="2">
         <v>1002030</v>
       </c>
@@ -3166,22 +3610,28 @@
         <v>30</v>
       </c>
       <c r="E79" s="2">
-        <v>351</v>
+        <v>1249</v>
       </c>
       <c r="F79" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H79" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I79" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
       <c r="B80" s="2">
         <v>1002031</v>
       </c>
@@ -3192,22 +3642,28 @@
         <v>31</v>
       </c>
       <c r="E80" s="2">
-        <v>395</v>
+        <v>3607</v>
       </c>
       <c r="F80" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H80" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I80" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
       <c r="B81" s="2">
         <v>1002032</v>
       </c>
@@ -3218,22 +3674,28 @@
         <v>32</v>
       </c>
       <c r="E81" s="2">
-        <v>446</v>
+        <v>3607</v>
       </c>
       <c r="F81" s="2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H81" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I81" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
       <c r="B82" s="2">
         <v>1002033</v>
       </c>
@@ -3244,22 +3706,28 @@
         <v>33</v>
       </c>
       <c r="E82" s="2">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="F82" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H82" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I82" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="83" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
       <c r="B83" s="2">
         <v>1002034</v>
       </c>
@@ -3270,22 +3738,28 @@
         <v>34</v>
       </c>
       <c r="E83" s="2">
-        <v>457</v>
+        <v>1396</v>
       </c>
       <c r="F83" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H83" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I83" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
       <c r="B84" s="2">
         <v>1002035</v>
       </c>
@@ -3296,22 +3770,28 @@
         <v>35</v>
       </c>
       <c r="E84" s="2">
-        <v>514</v>
+        <v>3777</v>
       </c>
       <c r="F84" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H84" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I84" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
       <c r="B85" s="2">
         <v>1002036</v>
       </c>
@@ -3322,22 +3802,28 @@
         <v>36</v>
       </c>
       <c r="E85" s="2">
-        <v>579</v>
+        <v>3777</v>
       </c>
       <c r="F85" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H85" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I85" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
       <c r="B86" s="2">
         <v>1002037</v>
       </c>
@@ -3348,22 +3834,28 @@
         <v>37</v>
       </c>
       <c r="E86" s="2">
-        <v>530</v>
+        <v>388</v>
       </c>
       <c r="F86" s="2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H86" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
       <c r="B87" s="2">
         <v>1002038</v>
       </c>
@@ -3374,22 +3866,28 @@
         <v>38</v>
       </c>
       <c r="E87" s="2">
-        <v>594</v>
+        <v>1544</v>
       </c>
       <c r="F87" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H87" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I87" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
       <c r="B88" s="2">
         <v>1002039</v>
       </c>
@@ -3400,22 +3898,28 @@
         <v>39</v>
       </c>
       <c r="E88" s="2">
-        <v>668</v>
+        <v>3946</v>
       </c>
       <c r="F88" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H88" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I88" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
       <c r="B89" s="2">
         <v>1002040</v>
       </c>
@@ -3426,22 +3930,28 @@
         <v>40</v>
       </c>
       <c r="E89" s="2">
-        <v>753</v>
+        <v>3946</v>
       </c>
       <c r="F89" s="2">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H89" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
       <c r="B90" s="2">
         <v>1002041</v>
       </c>
@@ -3452,22 +3962,28 @@
         <v>41</v>
       </c>
       <c r="E90" s="2">
-        <v>689</v>
+        <v>405</v>
       </c>
       <c r="F90" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H90" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I90" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
       <c r="B91" s="2">
         <v>1002042</v>
       </c>
@@ -3478,22 +3994,28 @@
         <v>42</v>
       </c>
       <c r="E91" s="2">
-        <v>772</v>
+        <v>1723</v>
       </c>
       <c r="F91" s="2">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H91" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I91" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
       <c r="B92" s="2">
         <v>1002043</v>
       </c>
@@ -3504,22 +4026,28 @@
         <v>43</v>
       </c>
       <c r="E92" s="2">
-        <v>869</v>
+        <v>4115</v>
       </c>
       <c r="F92" s="2">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H92" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I92" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
       <c r="B93" s="2">
         <v>1002044</v>
       </c>
@@ -3530,22 +4058,28 @@
         <v>44</v>
       </c>
       <c r="E93" s="2">
-        <v>979</v>
+        <v>4115</v>
       </c>
       <c r="F93" s="2">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H93" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I93" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="95" spans="2:9">
+        <v>32</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
       <c r="B95" s="1">
         <v>1003001</v>
       </c>
@@ -3556,22 +4090,28 @@
         <v>1</v>
       </c>
       <c r="E95" s="1">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="F95" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
       <c r="B96" s="1">
         <v>1003002</v>
       </c>
@@ -3582,22 +4122,28 @@
         <v>2</v>
       </c>
       <c r="E96" s="1">
-        <v>54</v>
+        <v>488</v>
       </c>
       <c r="F96" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11">
       <c r="B97" s="1">
         <v>1003003</v>
       </c>
@@ -3608,22 +4154,28 @@
         <v>3</v>
       </c>
       <c r="E97" s="1">
-        <v>60</v>
+        <v>1043</v>
       </c>
       <c r="F97" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11">
       <c r="B98" s="1">
         <v>1003004</v>
       </c>
@@ -3634,22 +4186,28 @@
         <v>4</v>
       </c>
       <c r="E98" s="1">
-        <v>68</v>
+        <v>2324</v>
       </c>
       <c r="F98" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
       <c r="B99" s="1">
         <v>1003005</v>
       </c>
@@ -3660,22 +4218,28 @@
         <v>5</v>
       </c>
       <c r="E99" s="1">
-        <v>62</v>
+        <v>244</v>
       </c>
       <c r="F99" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11">
       <c r="B100" s="1">
         <v>1003006</v>
       </c>
@@ -3686,22 +4250,28 @@
         <v>6</v>
       </c>
       <c r="E100" s="1">
-        <v>70</v>
+        <v>567</v>
       </c>
       <c r="F100" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="101" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
       <c r="B101" s="1">
         <v>1003007</v>
       </c>
@@ -3712,22 +4282,28 @@
         <v>7</v>
       </c>
       <c r="E101" s="1">
-        <v>79</v>
+        <v>1320</v>
       </c>
       <c r="F101" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
       <c r="B102" s="1">
         <v>1003008</v>
       </c>
@@ -3738,22 +4314,28 @@
         <v>8</v>
       </c>
       <c r="E102" s="1">
-        <v>89</v>
+        <v>2487</v>
       </c>
       <c r="F102" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="103" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
       <c r="B103" s="2">
         <v>1003009</v>
       </c>
@@ -3764,22 +4346,28 @@
         <v>9</v>
       </c>
       <c r="E103" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
       <c r="F103" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H103" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I103" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
       <c r="B104" s="2">
         <v>1003010</v>
       </c>
@@ -3790,22 +4378,28 @@
         <v>10</v>
       </c>
       <c r="E104" s="2">
-        <v>91</v>
+        <v>649</v>
       </c>
       <c r="F104" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H104" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I104" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
       <c r="B105" s="2">
         <v>1003011</v>
       </c>
@@ -3816,22 +4410,28 @@
         <v>11</v>
       </c>
       <c r="E105" s="2">
-        <v>102</v>
+        <v>1644</v>
       </c>
       <c r="F105" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H105" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I105" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="106" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
       <c r="B106" s="2">
         <v>1003012</v>
       </c>
@@ -3842,22 +4442,28 @@
         <v>12</v>
       </c>
       <c r="E106" s="2">
-        <v>115</v>
+        <v>2649</v>
       </c>
       <c r="F106" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I106" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
       <c r="B107" s="2">
         <v>1003013</v>
       </c>
@@ -3868,22 +4474,28 @@
         <v>13</v>
       </c>
       <c r="E107" s="2">
-        <v>105</v>
+        <v>276</v>
       </c>
       <c r="F107" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H107" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="108" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11">
       <c r="B108" s="2">
         <v>1003014</v>
       </c>
@@ -3894,22 +4506,28 @@
         <v>14</v>
       </c>
       <c r="E108" s="2">
-        <v>118</v>
+        <v>745</v>
       </c>
       <c r="F108" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H108" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I108" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="109" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
       <c r="B109" s="2">
         <v>1003015</v>
       </c>
@@ -3920,22 +4538,28 @@
         <v>15</v>
       </c>
       <c r="E109" s="2">
-        <v>133</v>
+        <v>2021</v>
       </c>
       <c r="F109" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H109" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I109" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="110" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11">
       <c r="B110" s="2">
         <v>1003016</v>
       </c>
@@ -3946,22 +4570,28 @@
         <v>16</v>
       </c>
       <c r="E110" s="2">
-        <v>150</v>
+        <v>2812</v>
       </c>
       <c r="F110" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H110" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I110" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11">
       <c r="B111" s="2">
         <v>1003017</v>
       </c>
@@ -3972,22 +4602,28 @@
         <v>17</v>
       </c>
       <c r="E111" s="2">
-        <v>137</v>
+        <v>292</v>
       </c>
       <c r="F111" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H111" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I111" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11">
       <c r="B112" s="2">
         <v>1003018</v>
       </c>
@@ -3998,22 +4634,28 @@
         <v>18</v>
       </c>
       <c r="E112" s="2">
-        <v>154</v>
+        <v>848</v>
       </c>
       <c r="F112" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H112" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I112" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="113" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11">
       <c r="B113" s="2">
         <v>1003019</v>
       </c>
@@ -4024,22 +4666,28 @@
         <v>19</v>
       </c>
       <c r="E113" s="2">
-        <v>173</v>
+        <v>2468</v>
       </c>
       <c r="F113" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H113" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I113" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="114" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="2:11">
       <c r="B114" s="2">
         <v>1003020</v>
       </c>
@@ -4050,22 +4698,28 @@
         <v>20</v>
       </c>
       <c r="E114" s="2">
-        <v>195</v>
+        <v>2975</v>
       </c>
       <c r="F114" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H114" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I114" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="115" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11">
       <c r="B115" s="2">
         <v>1003021</v>
       </c>
@@ -4076,22 +4730,28 @@
         <v>21</v>
       </c>
       <c r="E115" s="2">
-        <v>178</v>
+        <v>308</v>
       </c>
       <c r="F115" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H115" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I115" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="116" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="2:11">
       <c r="B116" s="2">
         <v>1003022</v>
       </c>
@@ -4102,22 +4762,28 @@
         <v>22</v>
       </c>
       <c r="E116" s="2">
-        <v>200</v>
+        <v>954</v>
       </c>
       <c r="F116" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H116" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I116" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="117" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" spans="2:11">
       <c r="B117" s="2">
         <v>1003023</v>
       </c>
@@ -4128,22 +4794,28 @@
         <v>23</v>
       </c>
       <c r="E117" s="2">
-        <v>225</v>
+        <v>2980</v>
       </c>
       <c r="F117" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H117" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I117" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="118" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="2:11">
       <c r="B118" s="2">
         <v>1003024</v>
       </c>
@@ -4154,22 +4826,28 @@
         <v>24</v>
       </c>
       <c r="E118" s="2">
-        <v>253</v>
+        <v>3137</v>
       </c>
       <c r="F118" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H118" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I118" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="119" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="119" spans="2:11">
       <c r="B119" s="2">
         <v>1003025</v>
       </c>
@@ -4180,22 +4858,28 @@
         <v>25</v>
       </c>
       <c r="E119" s="2">
-        <v>232</v>
+        <v>324</v>
       </c>
       <c r="F119" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H119" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I119" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="120" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="120" spans="2:11">
       <c r="B120" s="2">
         <v>1003026</v>
       </c>
@@ -4206,22 +4890,28 @@
         <v>26</v>
       </c>
       <c r="E120" s="2">
-        <v>259</v>
+        <v>1076</v>
       </c>
       <c r="F120" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I120" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="121" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="121" spans="2:11">
       <c r="B121" s="2">
         <v>1003027</v>
       </c>
@@ -4232,22 +4922,28 @@
         <v>27</v>
       </c>
       <c r="E121" s="2">
-        <v>292</v>
+        <v>3300</v>
       </c>
       <c r="F121" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I121" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="122" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122" spans="2:11">
       <c r="B122" s="2">
         <v>1003028</v>
       </c>
@@ -4258,22 +4954,28 @@
         <v>28</v>
       </c>
       <c r="E122" s="2">
-        <v>329</v>
+        <v>3300</v>
       </c>
       <c r="F122" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H122" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I122" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="123" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11">
       <c r="B123" s="2">
         <v>1003029</v>
       </c>
@@ -4284,22 +4986,28 @@
         <v>29</v>
       </c>
       <c r="E123" s="2">
-        <v>301</v>
+        <v>340</v>
       </c>
       <c r="F123" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H123" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I123" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="124" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="2:11">
       <c r="B124" s="2">
         <v>1003030</v>
       </c>
@@ -4310,22 +5018,28 @@
         <v>30</v>
       </c>
       <c r="E124" s="2">
-        <v>337</v>
+        <v>1199</v>
       </c>
       <c r="F124" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H124" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I124" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="125" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125" spans="2:11">
       <c r="B125" s="2">
         <v>1003031</v>
       </c>
@@ -4336,22 +5050,28 @@
         <v>31</v>
       </c>
       <c r="E125" s="2">
-        <v>380</v>
+        <v>3463</v>
       </c>
       <c r="F125" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H125" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I125" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="126" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126" spans="2:11">
       <c r="B126" s="2">
         <v>1003032</v>
       </c>
@@ -4362,22 +5082,28 @@
         <v>32</v>
       </c>
       <c r="E126" s="2">
-        <v>428</v>
+        <v>3463</v>
       </c>
       <c r="F126" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H126" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I126" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="127" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="2:11">
       <c r="B127" s="2">
         <v>1003033</v>
       </c>
@@ -4388,22 +5114,28 @@
         <v>33</v>
       </c>
       <c r="E127" s="2">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="F127" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H127" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I127" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="128" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="2:11">
       <c r="B128" s="2">
         <v>1003034</v>
       </c>
@@ -4414,22 +5146,28 @@
         <v>34</v>
       </c>
       <c r="E128" s="2">
-        <v>439</v>
+        <v>1340</v>
       </c>
       <c r="F128" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H128" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I128" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="129" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="2:11">
       <c r="B129" s="2">
         <v>1003035</v>
       </c>
@@ -4440,22 +5178,28 @@
         <v>35</v>
       </c>
       <c r="E129" s="2">
-        <v>493</v>
+        <v>3626</v>
       </c>
       <c r="F129" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H129" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I129" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="130" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="2:11">
       <c r="B130" s="2">
         <v>1003036</v>
       </c>
@@ -4466,22 +5210,28 @@
         <v>36</v>
       </c>
       <c r="E130" s="2">
-        <v>556</v>
+        <v>3626</v>
       </c>
       <c r="F130" s="2">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H130" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I130" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="131" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="131" spans="2:11">
       <c r="B131" s="2">
         <v>1003037</v>
       </c>
@@ -4492,22 +5242,28 @@
         <v>37</v>
       </c>
       <c r="E131" s="2">
-        <v>509</v>
+        <v>372</v>
       </c>
       <c r="F131" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H131" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I131" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="132" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" spans="2:11">
       <c r="B132" s="2">
         <v>1003038</v>
       </c>
@@ -4518,22 +5274,28 @@
         <v>38</v>
       </c>
       <c r="E132" s="2">
-        <v>570</v>
+        <v>1483</v>
       </c>
       <c r="F132" s="2">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H132" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I132" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="133" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="2:11">
       <c r="B133" s="2">
         <v>1003039</v>
       </c>
@@ -4544,22 +5306,28 @@
         <v>39</v>
       </c>
       <c r="E133" s="2">
-        <v>641</v>
+        <v>3788</v>
       </c>
       <c r="F133" s="2">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H133" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I133" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="134" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="134" spans="2:11">
       <c r="B134" s="2">
         <v>1003040</v>
       </c>
@@ -4570,22 +5338,28 @@
         <v>40</v>
       </c>
       <c r="E134" s="2">
-        <v>723</v>
+        <v>3788</v>
       </c>
       <c r="F134" s="2">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H134" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I134" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="135" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135" spans="2:11">
       <c r="B135" s="2">
         <v>1003041</v>
       </c>
@@ -4596,22 +5370,28 @@
         <v>41</v>
       </c>
       <c r="E135" s="2">
-        <v>662</v>
+        <v>388</v>
       </c>
       <c r="F135" s="2">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H135" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I135" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="136" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136" spans="2:11">
       <c r="B136" s="2">
         <v>1003042</v>
       </c>
@@ -4622,22 +5402,28 @@
         <v>42</v>
       </c>
       <c r="E136" s="2">
-        <v>741</v>
+        <v>1654</v>
       </c>
       <c r="F136" s="2">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H136" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I136" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="137" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="137" spans="2:11">
       <c r="B137" s="2">
         <v>1003043</v>
       </c>
@@ -4648,22 +5434,28 @@
         <v>43</v>
       </c>
       <c r="E137" s="2">
-        <v>834</v>
+        <v>3951</v>
       </c>
       <c r="F137" s="2">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H137" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I137" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="138" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="2:11">
       <c r="B138" s="2">
         <v>1003044</v>
       </c>
@@ -4674,22 +5466,28 @@
         <v>44</v>
       </c>
       <c r="E138" s="2">
-        <v>940</v>
+        <v>3951</v>
       </c>
       <c r="F138" s="2">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H138" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I138" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="140" spans="2:9">
+        <v>34</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140" spans="2:11">
       <c r="B140" s="1">
         <v>1004001</v>
       </c>
@@ -4700,22 +5498,28 @@
         <v>1</v>
       </c>
       <c r="E140" s="1">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="F140" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="141" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141" spans="2:11">
       <c r="B141" s="1">
         <v>1004002</v>
       </c>
@@ -4726,22 +5530,28 @@
         <v>2</v>
       </c>
       <c r="E141" s="1">
-        <v>47</v>
+        <v>427</v>
       </c>
       <c r="F141" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="142" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" spans="2:11">
       <c r="B142" s="1">
         <v>1004003</v>
       </c>
@@ -4752,22 +5562,28 @@
         <v>3</v>
       </c>
       <c r="E142" s="1">
-        <v>53</v>
+        <v>913</v>
       </c>
       <c r="F142" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="143" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="2:11">
       <c r="B143" s="1">
         <v>1004004</v>
       </c>
@@ -4778,22 +5594,28 @@
         <v>4</v>
       </c>
       <c r="E143" s="1">
-        <v>60</v>
+        <v>2034</v>
       </c>
       <c r="F143" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="144" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="144" spans="2:11">
       <c r="B144" s="1">
         <v>1004005</v>
       </c>
@@ -4804,22 +5626,28 @@
         <v>5</v>
       </c>
       <c r="E144" s="1">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="F144" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="145" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="145" spans="2:11">
       <c r="B145" s="1">
         <v>1004006</v>
       </c>
@@ -4830,22 +5658,28 @@
         <v>6</v>
       </c>
       <c r="E145" s="1">
-        <v>61</v>
+        <v>496</v>
       </c>
       <c r="F145" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="146" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="146" spans="2:11">
       <c r="B146" s="1">
         <v>1004007</v>
       </c>
@@ -4856,22 +5690,28 @@
         <v>7</v>
       </c>
       <c r="E146" s="1">
-        <v>69</v>
+        <v>1155</v>
       </c>
       <c r="F146" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="147" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="147" spans="2:11">
       <c r="B147" s="1">
         <v>1004008</v>
       </c>
@@ -4882,22 +5722,28 @@
         <v>8</v>
       </c>
       <c r="E147" s="1">
-        <v>78</v>
+        <v>2176</v>
       </c>
       <c r="F147" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="148" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="148" spans="2:11">
       <c r="B148" s="2">
         <v>1004009</v>
       </c>
@@ -4908,22 +5754,28 @@
         <v>9</v>
       </c>
       <c r="E148" s="2">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="F148" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H148" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I148" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="149" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="149" spans="2:11">
       <c r="B149" s="2">
         <v>1004010</v>
       </c>
@@ -4934,22 +5786,28 @@
         <v>10</v>
       </c>
       <c r="E149" s="2">
-        <v>79</v>
+        <v>568</v>
       </c>
       <c r="F149" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H149" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I149" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="150" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="150" spans="2:11">
       <c r="B150" s="2">
         <v>1004011</v>
       </c>
@@ -4960,22 +5818,28 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>89</v>
+        <v>1439</v>
       </c>
       <c r="F150" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H150" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I150" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="151" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151" spans="2:11">
       <c r="B151" s="2">
         <v>1004012</v>
       </c>
@@ -4986,22 +5850,28 @@
         <v>12</v>
       </c>
       <c r="E151" s="2">
-        <v>101</v>
+        <v>2318</v>
       </c>
       <c r="F151" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H151" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I151" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="152" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152" spans="2:11">
       <c r="B152" s="2">
         <v>1004013</v>
       </c>
@@ -5012,22 +5882,28 @@
         <v>13</v>
       </c>
       <c r="E152" s="2">
-        <v>92</v>
+        <v>242</v>
       </c>
       <c r="F152" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H152" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I152" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="153" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153" spans="2:11">
       <c r="B153" s="2">
         <v>1004014</v>
       </c>
@@ -5038,22 +5914,28 @@
         <v>14</v>
       </c>
       <c r="E153" s="2">
-        <v>103</v>
+        <v>651</v>
       </c>
       <c r="F153" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H153" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I153" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="154" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="2:11">
       <c r="B154" s="2">
         <v>1004015</v>
       </c>
@@ -5064,22 +5946,28 @@
         <v>15</v>
       </c>
       <c r="E154" s="2">
-        <v>116</v>
+        <v>1768</v>
       </c>
       <c r="F154" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H154" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I154" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="155" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="155" spans="2:11">
       <c r="B155" s="2">
         <v>1004016</v>
       </c>
@@ -5090,22 +5978,28 @@
         <v>16</v>
       </c>
       <c r="E155" s="2">
-        <v>131</v>
+        <v>2461</v>
       </c>
       <c r="F155" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H155" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I155" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="156" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="156" spans="2:11">
       <c r="B156" s="2">
         <v>1004017</v>
       </c>
@@ -5116,22 +6010,28 @@
         <v>17</v>
       </c>
       <c r="E156" s="2">
-        <v>120</v>
+        <v>256</v>
       </c>
       <c r="F156" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H156" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I156" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="157" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="157" spans="2:11">
       <c r="B157" s="2">
         <v>1004018</v>
       </c>
@@ -5142,22 +6042,28 @@
         <v>18</v>
       </c>
       <c r="E157" s="2">
-        <v>134</v>
+        <v>742</v>
       </c>
       <c r="F157" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H157" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I157" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="158" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="158" spans="2:11">
       <c r="B158" s="2">
         <v>1004019</v>
       </c>
@@ -5168,22 +6074,28 @@
         <v>19</v>
       </c>
       <c r="E158" s="2">
-        <v>151</v>
+        <v>2160</v>
       </c>
       <c r="F158" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H158" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I158" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="159" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="159" spans="2:11">
       <c r="B159" s="2">
         <v>1004020</v>
       </c>
@@ -5194,22 +6106,28 @@
         <v>20</v>
       </c>
       <c r="E159" s="2">
-        <v>170</v>
+        <v>2603</v>
       </c>
       <c r="F159" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H159" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I159" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="160" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160" spans="2:11">
       <c r="B160" s="2">
         <v>1004021</v>
       </c>
@@ -5220,22 +6138,28 @@
         <v>21</v>
       </c>
       <c r="E160" s="2">
-        <v>156</v>
+        <v>270</v>
       </c>
       <c r="F160" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H160" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I160" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="161" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11">
       <c r="B161" s="2">
         <v>1004022</v>
       </c>
@@ -5246,22 +6170,28 @@
         <v>22</v>
       </c>
       <c r="E161" s="2">
-        <v>175</v>
+        <v>835</v>
       </c>
       <c r="F161" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H161" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I161" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="162" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11">
       <c r="B162" s="2">
         <v>1004023</v>
       </c>
@@ -5272,22 +6202,28 @@
         <v>23</v>
       </c>
       <c r="E162" s="2">
-        <v>196</v>
+        <v>2607</v>
       </c>
       <c r="F162" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H162" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I162" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="163" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11">
       <c r="B163" s="2">
         <v>1004024</v>
       </c>
@@ -5298,22 +6234,28 @@
         <v>24</v>
       </c>
       <c r="E163" s="2">
-        <v>221</v>
+        <v>2745</v>
       </c>
       <c r="F163" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H163" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I163" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="164" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11">
       <c r="B164" s="2">
         <v>1004025</v>
       </c>
@@ -5324,22 +6266,28 @@
         <v>25</v>
       </c>
       <c r="E164" s="2">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="F164" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H164" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I164" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="165" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="165" spans="2:11">
       <c r="B165" s="2">
         <v>1004026</v>
       </c>
@@ -5350,22 +6298,28 @@
         <v>26</v>
       </c>
       <c r="E165" s="2">
-        <v>227</v>
+        <v>942</v>
       </c>
       <c r="F165" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H165" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I165" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="166" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K165" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="166" spans="2:11">
       <c r="B166" s="2">
         <v>1004027</v>
       </c>
@@ -5376,22 +6330,28 @@
         <v>27</v>
       </c>
       <c r="E166" s="2">
-        <v>255</v>
+        <v>2888</v>
       </c>
       <c r="F166" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H166" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I166" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="167" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K166" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="2:11">
       <c r="B167" s="2">
         <v>1004028</v>
       </c>
@@ -5402,22 +6362,28 @@
         <v>28</v>
       </c>
       <c r="E167" s="2">
-        <v>288</v>
+        <v>2888</v>
       </c>
       <c r="F167" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H167" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I167" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="168" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K167" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="168" spans="2:11">
       <c r="B168" s="2">
         <v>1004029</v>
       </c>
@@ -5428,22 +6394,28 @@
         <v>29</v>
       </c>
       <c r="E168" s="2">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="F168" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H168" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I168" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="169" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K168" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="2:11">
       <c r="B169" s="2">
         <v>1004030</v>
       </c>
@@ -5454,22 +6426,28 @@
         <v>30</v>
       </c>
       <c r="E169" s="2">
-        <v>295</v>
+        <v>1050</v>
       </c>
       <c r="F169" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H169" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I169" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="170" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K169" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="170" spans="2:11">
       <c r="B170" s="2">
         <v>1004031</v>
       </c>
@@ -5480,22 +6458,28 @@
         <v>31</v>
       </c>
       <c r="E170" s="2">
-        <v>332</v>
+        <v>3030</v>
       </c>
       <c r="F170" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H170" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I170" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="171" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K170" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="171" spans="2:11">
       <c r="B171" s="2">
         <v>1004032</v>
       </c>
@@ -5506,22 +6490,28 @@
         <v>32</v>
       </c>
       <c r="E171" s="2">
-        <v>374</v>
+        <v>3030</v>
       </c>
       <c r="F171" s="2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H171" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I171" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="172" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K171" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" spans="2:11">
       <c r="B172" s="2">
         <v>1004033</v>
       </c>
@@ -5532,22 +6522,28 @@
         <v>33</v>
       </c>
       <c r="E172" s="2">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="F172" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H172" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I172" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="173" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J172" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K172" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173" spans="2:11">
       <c r="B173" s="2">
         <v>1004034</v>
       </c>
@@ -5558,22 +6554,28 @@
         <v>34</v>
       </c>
       <c r="E173" s="2">
-        <v>384</v>
+        <v>1173</v>
       </c>
       <c r="F173" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H173" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I173" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="174" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K173" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="174" spans="2:11">
       <c r="B174" s="2">
         <v>1004035</v>
       </c>
@@ -5584,22 +6586,28 @@
         <v>35</v>
       </c>
       <c r="E174" s="2">
-        <v>432</v>
+        <v>3172</v>
       </c>
       <c r="F174" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H174" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I174" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="175" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K174" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175" spans="2:11">
       <c r="B175" s="2">
         <v>1004036</v>
       </c>
@@ -5610,22 +6618,28 @@
         <v>36</v>
       </c>
       <c r="E175" s="2">
-        <v>487</v>
+        <v>3172</v>
       </c>
       <c r="F175" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H175" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I175" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="176" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K175" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="176" spans="2:11">
       <c r="B176" s="2">
         <v>1004037</v>
       </c>
@@ -5636,22 +6650,28 @@
         <v>37</v>
       </c>
       <c r="E176" s="2">
-        <v>445</v>
+        <v>326</v>
       </c>
       <c r="F176" s="2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H176" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I176" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="177" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K176" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177" spans="2:11">
       <c r="B177" s="2">
         <v>1004038</v>
       </c>
@@ -5662,22 +6682,28 @@
         <v>38</v>
       </c>
       <c r="E177" s="2">
-        <v>499</v>
+        <v>1297</v>
       </c>
       <c r="F177" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H177" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I177" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="178" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K177" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178" spans="2:11">
       <c r="B178" s="2">
         <v>1004039</v>
       </c>
@@ -5688,22 +6714,28 @@
         <v>39</v>
       </c>
       <c r="E178" s="2">
-        <v>561</v>
+        <v>3315</v>
       </c>
       <c r="F178" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H178" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I178" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="179" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K178" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="179" spans="2:11">
       <c r="B179" s="2">
         <v>1004040</v>
       </c>
@@ -5714,22 +6746,28 @@
         <v>40</v>
       </c>
       <c r="E179" s="2">
-        <v>632</v>
+        <v>3315</v>
       </c>
       <c r="F179" s="2">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H179" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I179" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="180" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K179" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180" spans="2:11">
       <c r="B180" s="2">
         <v>1004041</v>
       </c>
@@ -5740,22 +6778,28 @@
         <v>41</v>
       </c>
       <c r="E180" s="2">
-        <v>579</v>
+        <v>340</v>
       </c>
       <c r="F180" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H180" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I180" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="181" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K180" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="181" spans="2:11">
       <c r="B181" s="2">
         <v>1004042</v>
       </c>
@@ -5766,22 +6810,28 @@
         <v>42</v>
       </c>
       <c r="E181" s="2">
-        <v>648</v>
+        <v>1448</v>
       </c>
       <c r="F181" s="2">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H181" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I181" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="182" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="182" spans="2:11">
       <c r="B182" s="2">
         <v>1004043</v>
       </c>
@@ -5792,22 +6842,28 @@
         <v>43</v>
       </c>
       <c r="E182" s="2">
-        <v>730</v>
+        <v>3457</v>
       </c>
       <c r="F182" s="2">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H182" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I182" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="183" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K182" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="183" spans="2:11">
       <c r="B183" s="2">
         <v>1004044</v>
       </c>
@@ -5818,22 +6874,28 @@
         <v>44</v>
       </c>
       <c r="E183" s="2">
-        <v>822</v>
+        <v>3457</v>
       </c>
       <c r="F183" s="2">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H183" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I183" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="185" spans="2:9">
+        <v>36</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K183" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="185" spans="2:11">
       <c r="B185" s="1">
         <v>1005001</v>
       </c>
@@ -5844,22 +6906,28 @@
         <v>1</v>
       </c>
       <c r="E185" s="1">
-        <v>58</v>
+        <v>276</v>
       </c>
       <c r="F185" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="186" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J185" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K185" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="186" spans="2:11">
       <c r="B186" s="1">
         <v>1005002</v>
       </c>
@@ -5870,22 +6938,28 @@
         <v>2</v>
       </c>
       <c r="E186" s="1">
-        <v>65</v>
+        <v>589</v>
       </c>
       <c r="F186" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="187" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K186" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="187" spans="2:11">
       <c r="B187" s="1">
         <v>1005003</v>
       </c>
@@ -5896,22 +6970,28 @@
         <v>3</v>
       </c>
       <c r="E187" s="1">
-        <v>73</v>
+        <v>1261</v>
       </c>
       <c r="F187" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="188" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J187" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K187" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="188" spans="2:11">
       <c r="B188" s="1">
         <v>1005004</v>
       </c>
@@ -5922,22 +7002,28 @@
         <v>4</v>
       </c>
       <c r="E188" s="1">
-        <v>82</v>
+        <v>2808</v>
       </c>
       <c r="F188" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="189" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="189" spans="2:11">
       <c r="B189" s="1">
         <v>1005005</v>
       </c>
@@ -5948,22 +7034,28 @@
         <v>5</v>
       </c>
       <c r="E189" s="1">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="F189" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="190" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J189" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K189" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="190" spans="2:11">
       <c r="B190" s="1">
         <v>1005006</v>
       </c>
@@ -5974,22 +7066,28 @@
         <v>6</v>
       </c>
       <c r="E190" s="1">
-        <v>84</v>
+        <v>685</v>
       </c>
       <c r="F190" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="191" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J190" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K190" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="191" spans="2:11">
       <c r="B191" s="1">
         <v>1005007</v>
       </c>
@@ -6000,22 +7098,28 @@
         <v>7</v>
       </c>
       <c r="E191" s="1">
-        <v>95</v>
+        <v>1595</v>
       </c>
       <c r="F191" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="192" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K191" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="192" spans="2:11">
       <c r="B192" s="1">
         <v>1005008</v>
       </c>
@@ -6026,22 +7130,28 @@
         <v>8</v>
       </c>
       <c r="E192" s="1">
-        <v>107</v>
+        <v>3005</v>
       </c>
       <c r="F192" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="193" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J192" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K192" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="193" spans="2:11">
       <c r="B193" s="2">
         <v>1005009</v>
       </c>
@@ -6052,7 +7162,7 @@
         <v>9</v>
       </c>
       <c r="E193" s="2">
-        <v>98</v>
+        <v>315</v>
       </c>
       <c r="F193" s="2">
         <v>3</v>
@@ -6061,13 +7171,19 @@
         <v>26</v>
       </c>
       <c r="H193" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I193" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="194" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K193" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="194" spans="2:11">
       <c r="B194" s="2">
         <v>1005010</v>
       </c>
@@ -6078,22 +7194,28 @@
         <v>10</v>
       </c>
       <c r="E194" s="2">
-        <v>110</v>
+        <v>785</v>
       </c>
       <c r="F194" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H194" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I194" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="195" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K194" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="195" spans="2:11">
       <c r="B195" s="2">
         <v>1005011</v>
       </c>
@@ -6104,22 +7226,28 @@
         <v>11</v>
       </c>
       <c r="E195" s="2">
-        <v>124</v>
+        <v>1987</v>
       </c>
       <c r="F195" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H195" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I195" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="196" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J195" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K195" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="196" spans="2:11">
       <c r="B196" s="2">
         <v>1005012</v>
       </c>
@@ -6130,22 +7258,28 @@
         <v>12</v>
       </c>
       <c r="E196" s="2">
-        <v>139</v>
+        <v>3201</v>
       </c>
       <c r="F196" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H196" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I196" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="197" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J196" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K196" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="197" spans="2:11">
       <c r="B197" s="2">
         <v>1005013</v>
       </c>
@@ -6156,22 +7290,28 @@
         <v>13</v>
       </c>
       <c r="E197" s="2">
-        <v>127</v>
+        <v>334</v>
       </c>
       <c r="F197" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H197" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I197" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="198" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K197" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="198" spans="2:11">
       <c r="B198" s="2">
         <v>1005014</v>
       </c>
@@ -6182,22 +7322,28 @@
         <v>14</v>
       </c>
       <c r="E198" s="2">
-        <v>143</v>
+        <v>900</v>
       </c>
       <c r="F198" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H198" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I198" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="199" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J198" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K198" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="199" spans="2:11">
       <c r="B199" s="2">
         <v>1005015</v>
       </c>
@@ -6208,22 +7354,28 @@
         <v>15</v>
       </c>
       <c r="E199" s="2">
-        <v>161</v>
+        <v>2442</v>
       </c>
       <c r="F199" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H199" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I199" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="200" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K199" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200" spans="2:11">
       <c r="B200" s="2">
         <v>1005016</v>
       </c>
@@ -6234,22 +7386,28 @@
         <v>16</v>
       </c>
       <c r="E200" s="2">
-        <v>181</v>
+        <v>3398</v>
       </c>
       <c r="F200" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H200" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I200" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="201" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K200" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="201" spans="2:11">
       <c r="B201" s="2">
         <v>1005017</v>
       </c>
@@ -6260,22 +7418,28 @@
         <v>17</v>
       </c>
       <c r="E201" s="2">
-        <v>166</v>
+        <v>353</v>
       </c>
       <c r="F201" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H201" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I201" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="202" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K201" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="202" spans="2:11">
       <c r="B202" s="2">
         <v>1005018</v>
       </c>
@@ -6286,22 +7450,28 @@
         <v>18</v>
       </c>
       <c r="E202" s="2">
-        <v>186</v>
+        <v>1025</v>
       </c>
       <c r="F202" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H202" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I202" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="203" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K202" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="203" spans="2:11">
       <c r="B203" s="2">
         <v>1005019</v>
       </c>
@@ -6312,22 +7482,28 @@
         <v>19</v>
       </c>
       <c r="E203" s="2">
-        <v>209</v>
+        <v>2982</v>
       </c>
       <c r="F203" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H203" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I203" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="204" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J203" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K203" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="204" spans="2:11">
       <c r="B204" s="2">
         <v>1005020</v>
       </c>
@@ -6338,22 +7514,28 @@
         <v>20</v>
       </c>
       <c r="E204" s="2">
-        <v>235</v>
+        <v>3595</v>
       </c>
       <c r="F204" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H204" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I204" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="205" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J204" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K204" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="205" spans="2:11">
       <c r="B205" s="2">
         <v>1005021</v>
       </c>
@@ -6364,22 +7546,28 @@
         <v>21</v>
       </c>
       <c r="E205" s="2">
-        <v>215</v>
+        <v>373</v>
       </c>
       <c r="F205" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H205" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I205" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="206" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K205" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="2:11">
       <c r="B206" s="2">
         <v>1005022</v>
       </c>
@@ -6390,22 +7578,28 @@
         <v>22</v>
       </c>
       <c r="E206" s="2">
-        <v>241</v>
+        <v>1153</v>
       </c>
       <c r="F206" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H206" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I206" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="207" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K206" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="207" spans="2:11">
       <c r="B207" s="2">
         <v>1005023</v>
       </c>
@@ -6416,22 +7610,28 @@
         <v>23</v>
       </c>
       <c r="E207" s="2">
-        <v>271</v>
+        <v>3600</v>
       </c>
       <c r="F207" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H207" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I207" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="208" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J207" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K207" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="208" spans="2:11">
       <c r="B208" s="2">
         <v>1005024</v>
       </c>
@@ -6442,22 +7642,28 @@
         <v>24</v>
       </c>
       <c r="E208" s="2">
-        <v>306</v>
+        <v>3791</v>
       </c>
       <c r="F208" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H208" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I208" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="209" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J208" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K208" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="209" spans="2:11">
       <c r="B209" s="2">
         <v>1005025</v>
       </c>
@@ -6468,22 +7674,28 @@
         <v>25</v>
       </c>
       <c r="E209" s="2">
-        <v>280</v>
+        <v>392</v>
       </c>
       <c r="F209" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H209" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I209" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="210" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J209" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K209" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="210" spans="2:11">
       <c r="B210" s="2">
         <v>1005026</v>
       </c>
@@ -6494,22 +7706,28 @@
         <v>26</v>
       </c>
       <c r="E210" s="2">
-        <v>314</v>
+        <v>1300</v>
       </c>
       <c r="F210" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H210" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I210" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="211" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J210" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K210" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" spans="2:11">
       <c r="B211" s="2">
         <v>1005027</v>
       </c>
@@ -6520,22 +7738,28 @@
         <v>27</v>
       </c>
       <c r="E211" s="2">
-        <v>353</v>
+        <v>3988</v>
       </c>
       <c r="F211" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H211" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I211" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="212" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J211" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K211" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="212" spans="2:11">
       <c r="B212" s="2">
         <v>1005028</v>
       </c>
@@ -6546,22 +7770,28 @@
         <v>28</v>
       </c>
       <c r="E212" s="2">
-        <v>398</v>
+        <v>3988</v>
       </c>
       <c r="F212" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H212" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I212" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="213" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K212" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="213" spans="2:11">
       <c r="B213" s="2">
         <v>1005029</v>
       </c>
@@ -6572,22 +7802,28 @@
         <v>29</v>
       </c>
       <c r="E213" s="2">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="F213" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H213" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I213" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="214" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K213" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="214" spans="2:11">
       <c r="B214" s="2">
         <v>1005030</v>
       </c>
@@ -6598,22 +7834,28 @@
         <v>30</v>
       </c>
       <c r="E214" s="2">
-        <v>408</v>
+        <v>1449</v>
       </c>
       <c r="F214" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H214" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I214" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="215" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J214" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K214" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="215" spans="2:11">
       <c r="B215" s="2">
         <v>1005031</v>
       </c>
@@ -6624,22 +7866,28 @@
         <v>31</v>
       </c>
       <c r="E215" s="2">
-        <v>459</v>
+        <v>4184</v>
       </c>
       <c r="F215" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H215" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I215" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="216" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J215" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K215" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="216" spans="2:11">
       <c r="B216" s="2">
         <v>1005032</v>
       </c>
@@ -6650,22 +7898,28 @@
         <v>32</v>
       </c>
       <c r="E216" s="2">
-        <v>517</v>
+        <v>4184</v>
       </c>
       <c r="F216" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H216" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I216" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="217" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J216" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K216" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="217" spans="2:11">
       <c r="B217" s="2">
         <v>1005033</v>
       </c>
@@ -6676,22 +7930,28 @@
         <v>33</v>
       </c>
       <c r="E217" s="2">
-        <v>473</v>
+        <v>431</v>
       </c>
       <c r="F217" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H217" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I217" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="218" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J217" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K217" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="218" spans="2:11">
       <c r="B218" s="2">
         <v>1005034</v>
       </c>
@@ -6702,22 +7962,28 @@
         <v>34</v>
       </c>
       <c r="E218" s="2">
-        <v>530</v>
+        <v>1620</v>
       </c>
       <c r="F218" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H218" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I218" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="219" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J218" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K218" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="219" spans="2:11">
       <c r="B219" s="2">
         <v>1005035</v>
       </c>
@@ -6728,22 +7994,28 @@
         <v>35</v>
       </c>
       <c r="E219" s="2">
-        <v>596</v>
+        <v>4381</v>
       </c>
       <c r="F219" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H219" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I219" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="220" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J219" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K219" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="220" spans="2:11">
       <c r="B220" s="2">
         <v>1005036</v>
       </c>
@@ -6754,22 +8026,28 @@
         <v>36</v>
       </c>
       <c r="E220" s="2">
-        <v>672</v>
+        <v>4381</v>
       </c>
       <c r="F220" s="2">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H220" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I220" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="221" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K220" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="221" spans="2:11">
       <c r="B221" s="2">
         <v>1005037</v>
       </c>
@@ -6780,22 +8058,28 @@
         <v>37</v>
       </c>
       <c r="E221" s="2">
-        <v>615</v>
+        <v>450</v>
       </c>
       <c r="F221" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H221" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I221" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="222" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222" spans="2:11">
       <c r="B222" s="2">
         <v>1005038</v>
       </c>
@@ -6806,22 +8090,28 @@
         <v>38</v>
       </c>
       <c r="E222" s="2">
-        <v>689</v>
+        <v>1791</v>
       </c>
       <c r="F222" s="2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H222" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I222" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="223" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J222" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K222" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="223" spans="2:11">
       <c r="B223" s="2">
         <v>1005039</v>
       </c>
@@ -6832,22 +8122,28 @@
         <v>39</v>
       </c>
       <c r="E223" s="2">
-        <v>775</v>
+        <v>4577</v>
       </c>
       <c r="F223" s="2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H223" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I223" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="224" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J223" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K223" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="224" spans="2:11">
       <c r="B224" s="2">
         <v>1005040</v>
       </c>
@@ -6858,22 +8154,28 @@
         <v>40</v>
       </c>
       <c r="E224" s="2">
-        <v>873</v>
+        <v>4577</v>
       </c>
       <c r="F224" s="2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H224" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I224" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="225" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J224" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K224" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="225" spans="2:11">
       <c r="B225" s="2">
         <v>1005041</v>
       </c>
@@ -6884,22 +8186,28 @@
         <v>41</v>
       </c>
       <c r="E225" s="2">
-        <v>800</v>
+        <v>469</v>
       </c>
       <c r="F225" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H225" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I225" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="226" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J225" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K225" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="226" spans="2:11">
       <c r="B226" s="2">
         <v>1005042</v>
       </c>
@@ -6910,22 +8218,28 @@
         <v>42</v>
       </c>
       <c r="E226" s="2">
-        <v>896</v>
+        <v>1999</v>
       </c>
       <c r="F226" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H226" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I226" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="227" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K226" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="227" spans="2:11">
       <c r="B227" s="2">
         <v>1005043</v>
       </c>
@@ -6936,22 +8250,28 @@
         <v>43</v>
       </c>
       <c r="E227" s="2">
-        <v>1007</v>
+        <v>4774</v>
       </c>
       <c r="F227" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H227" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I227" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="228" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="228" spans="2:11">
       <c r="B228" s="2">
         <v>1005044</v>
       </c>
@@ -6962,22 +8282,28 @@
         <v>44</v>
       </c>
       <c r="E228" s="2">
-        <v>1135</v>
+        <v>4774</v>
       </c>
       <c r="F228" s="2">
+        <v>8</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H228" t="s">
         <v>37</v>
       </c>
-      <c r="G228" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H228" t="s">
-        <v>35</v>
-      </c>
       <c r="I228" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="230" spans="2:9">
+        <v>38</v>
+      </c>
+      <c r="J228" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K228" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="230" spans="2:11">
       <c r="B230" s="1">
         <v>2001001</v>
       </c>
@@ -6988,22 +8314,28 @@
         <v>1</v>
       </c>
       <c r="E230" s="1">
-        <v>200</v>
+        <v>8120</v>
       </c>
       <c r="F230" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="231" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J230" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K230" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="231" spans="2:11">
       <c r="B231" s="1">
         <v>2001002</v>
       </c>
@@ -7014,22 +8346,28 @@
         <v>2</v>
       </c>
       <c r="E231" s="1">
-        <v>260</v>
+        <v>8526</v>
       </c>
       <c r="F231" s="1">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="232" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J231" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K231" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="232" spans="2:11">
       <c r="B232" s="2">
         <v>2001003</v>
       </c>
@@ -7040,22 +8378,28 @@
         <v>3</v>
       </c>
       <c r="E232" s="2">
-        <v>338</v>
+        <v>8932</v>
       </c>
       <c r="F232" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G232" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H232" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I232" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="233" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J232" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K232" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="233" spans="2:11">
       <c r="B233" s="2">
         <v>2001004</v>
       </c>
@@ -7066,22 +8410,28 @@
         <v>4</v>
       </c>
       <c r="E233" s="2">
-        <v>439</v>
+        <v>9338</v>
       </c>
       <c r="F233" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G233" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H233" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I233" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="234" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K233" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="234" spans="2:11">
       <c r="B234" s="2">
         <v>2001005</v>
       </c>
@@ -7092,22 +8442,28 @@
         <v>5</v>
       </c>
       <c r="E234" s="2">
-        <v>571</v>
+        <v>9744</v>
       </c>
       <c r="F234" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G234" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H234" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I234" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="235" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K234" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="235" spans="2:11">
       <c r="B235" s="2">
         <v>2001006</v>
       </c>
@@ -7118,22 +8474,28 @@
         <v>6</v>
       </c>
       <c r="E235" s="2">
-        <v>743</v>
+        <v>10150</v>
       </c>
       <c r="F235" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G235" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H235" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I235" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="236" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K235" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="236" spans="2:11">
       <c r="B236" s="2">
         <v>2001007</v>
       </c>
@@ -7144,22 +8506,28 @@
         <v>7</v>
       </c>
       <c r="E236" s="2">
-        <v>965</v>
+        <v>10556</v>
       </c>
       <c r="F236" s="2">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G236" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H236" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I236" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="237" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J236" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K236" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="237" spans="2:11">
       <c r="B237" s="2">
         <v>2001008</v>
       </c>
@@ -7170,22 +8538,28 @@
         <v>8</v>
       </c>
       <c r="E237" s="2">
-        <v>1255</v>
+        <v>10962</v>
       </c>
       <c r="F237" s="2">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="G237" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H237" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I237" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="238" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J237" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K237" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="238" spans="2:11">
       <c r="B238" s="2">
         <v>2001009</v>
       </c>
@@ -7196,22 +8570,28 @@
         <v>9</v>
       </c>
       <c r="E238" s="2">
-        <v>1631</v>
+        <v>11368</v>
       </c>
       <c r="F238" s="2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G238" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H238" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I238" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="239" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J238" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K238" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="239" spans="2:11">
       <c r="B239" s="2">
         <v>2001010</v>
       </c>
@@ -7222,22 +8602,28 @@
         <v>10</v>
       </c>
       <c r="E239" s="2">
-        <v>2121</v>
+        <v>11774</v>
       </c>
       <c r="F239" s="2">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="G239" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H239" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I239" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="240" spans="2:9">
+        <v>41</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K239" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="240" spans="2:11">
       <c r="B240" s="2">
         <v>2001011</v>
       </c>
@@ -7248,19 +8634,25 @@
         <v>11</v>
       </c>
       <c r="E240" s="2">
-        <v>2757</v>
+        <v>12180</v>
       </c>
       <c r="F240" s="2">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="G240" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H240" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I240" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K240" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16245" windowHeight="7590"/>
+    <workbookView windowWidth="16380" windowHeight="7635"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -121,10 +121,10 @@
     <t>enemy1</t>
   </si>
   <si>
-    <t>PurpleMonsterBaseFrame</t>
+    <t>KhakiMonsterBaseFrame</t>
   </si>
   <si>
-    <t>PurpleMonsterBaseFrameBox</t>
+    <t>KhakiMonsterBaseFrameBox</t>
   </si>
   <si>
     <t>狼哥</t>
@@ -139,6 +139,12 @@
     <t>enemy3</t>
   </si>
   <si>
+    <t>PurpleMonsterBaseFrame</t>
+  </si>
+  <si>
+    <t>PurpleMonsterBaseFrameBox</t>
+  </si>
+  <si>
     <t>小蜜蜂</t>
   </si>
   <si>
@@ -149,6 +155,12 @@
   </si>
   <si>
     <t>enemy5</t>
+  </si>
+  <si>
+    <t>RedMonsterBaseFrame</t>
+  </si>
+  <si>
+    <t>RedMonsterBaseFrameBox</t>
   </si>
   <si>
     <t>Boss</t>
@@ -1131,7 +1143,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L240"/>
+  <dimension ref="A1:L273"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
@@ -4105,10 +4117,10 @@
         <v>34</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="2:11">
@@ -4137,10 +4149,10 @@
         <v>34</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="2:11">
@@ -4169,10 +4181,10 @@
         <v>34</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="2:11">
@@ -4201,10 +4213,10 @@
         <v>34</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="2:11">
@@ -4233,10 +4245,10 @@
         <v>34</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="2:11">
@@ -4265,10 +4277,10 @@
         <v>34</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="2:11">
@@ -4297,10 +4309,10 @@
         <v>34</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="2:11">
@@ -4329,10 +4341,10 @@
         <v>34</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="2:11">
@@ -4361,10 +4373,10 @@
         <v>34</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104" spans="2:11">
@@ -4393,10 +4405,10 @@
         <v>34</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="2:11">
@@ -4425,10 +4437,10 @@
         <v>34</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="106" spans="2:11">
@@ -4457,10 +4469,10 @@
         <v>34</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107" spans="2:11">
@@ -4489,10 +4501,10 @@
         <v>34</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108" spans="2:11">
@@ -4521,10 +4533,10 @@
         <v>34</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109" spans="2:11">
@@ -4553,10 +4565,10 @@
         <v>34</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110" spans="2:11">
@@ -4585,10 +4597,10 @@
         <v>34</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111" spans="2:11">
@@ -4617,10 +4629,10 @@
         <v>34</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -4649,10 +4661,10 @@
         <v>34</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -4681,10 +4693,10 @@
         <v>34</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -4713,10 +4725,10 @@
         <v>34</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -4745,10 +4757,10 @@
         <v>34</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -4777,10 +4789,10 @@
         <v>34</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -4809,10 +4821,10 @@
         <v>34</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -4841,10 +4853,10 @@
         <v>34</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -4873,10 +4885,10 @@
         <v>34</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -4905,10 +4917,10 @@
         <v>34</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -4937,10 +4949,10 @@
         <v>34</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -4969,10 +4981,10 @@
         <v>34</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -5001,10 +5013,10 @@
         <v>34</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -5033,10 +5045,10 @@
         <v>34</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -5065,10 +5077,10 @@
         <v>34</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -5097,10 +5109,10 @@
         <v>34</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -5129,10 +5141,10 @@
         <v>34</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -5161,10 +5173,10 @@
         <v>34</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -5193,10 +5205,10 @@
         <v>34</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -5225,10 +5237,10 @@
         <v>34</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -5257,10 +5269,10 @@
         <v>34</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -5289,10 +5301,10 @@
         <v>34</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -5321,10 +5333,10 @@
         <v>34</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -5353,10 +5365,10 @@
         <v>34</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -5385,10 +5397,10 @@
         <v>34</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -5417,10 +5429,10 @@
         <v>34</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -5449,10 +5461,10 @@
         <v>34</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -5481,10 +5493,10 @@
         <v>34</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -5507,16 +5519,16 @@
         <v>26</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -5539,16 +5551,16 @@
         <v>26</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -5571,16 +5583,16 @@
         <v>26</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -5603,16 +5615,16 @@
         <v>26</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="144" spans="2:11">
@@ -5635,16 +5647,16 @@
         <v>26</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="145" spans="2:11">
@@ -5667,16 +5679,16 @@
         <v>26</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="146" spans="2:11">
@@ -5699,16 +5711,16 @@
         <v>26</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="147" spans="2:11">
@@ -5731,16 +5743,16 @@
         <v>26</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="148" spans="2:11">
@@ -5763,16 +5775,16 @@
         <v>26</v>
       </c>
       <c r="H148" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I148" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="149" spans="2:11">
@@ -5795,16 +5807,16 @@
         <v>26</v>
       </c>
       <c r="H149" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I149" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -5827,16 +5839,16 @@
         <v>26</v>
       </c>
       <c r="H150" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I150" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -5859,16 +5871,16 @@
         <v>26</v>
       </c>
       <c r="H151" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I151" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -5891,16 +5903,16 @@
         <v>26</v>
       </c>
       <c r="H152" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I152" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -5923,16 +5935,16 @@
         <v>26</v>
       </c>
       <c r="H153" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I153" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -5955,16 +5967,16 @@
         <v>26</v>
       </c>
       <c r="H154" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I154" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -5987,16 +5999,16 @@
         <v>26</v>
       </c>
       <c r="H155" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I155" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -6019,16 +6031,16 @@
         <v>26</v>
       </c>
       <c r="H156" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I156" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -6051,16 +6063,16 @@
         <v>26</v>
       </c>
       <c r="H157" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I157" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -6083,16 +6095,16 @@
         <v>26</v>
       </c>
       <c r="H158" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I158" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="159" spans="2:11">
@@ -6115,16 +6127,16 @@
         <v>26</v>
       </c>
       <c r="H159" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I159" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="160" spans="2:11">
@@ -6147,16 +6159,16 @@
         <v>26</v>
       </c>
       <c r="H160" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I160" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="161" spans="2:11">
@@ -6179,16 +6191,16 @@
         <v>26</v>
       </c>
       <c r="H161" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I161" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="162" spans="2:11">
@@ -6211,16 +6223,16 @@
         <v>26</v>
       </c>
       <c r="H162" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I162" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="163" spans="2:11">
@@ -6243,16 +6255,16 @@
         <v>26</v>
       </c>
       <c r="H163" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I163" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="164" spans="2:11">
@@ -6275,16 +6287,16 @@
         <v>26</v>
       </c>
       <c r="H164" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I164" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="165" spans="2:11">
@@ -6307,16 +6319,16 @@
         <v>26</v>
       </c>
       <c r="H165" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I165" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K165" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="166" spans="2:11">
@@ -6339,16 +6351,16 @@
         <v>26</v>
       </c>
       <c r="H166" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I166" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="167" spans="2:11">
@@ -6371,16 +6383,16 @@
         <v>26</v>
       </c>
       <c r="H167" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I167" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="168" spans="2:11">
@@ -6403,16 +6415,16 @@
         <v>26</v>
       </c>
       <c r="H168" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I168" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="169" spans="2:11">
@@ -6435,16 +6447,16 @@
         <v>26</v>
       </c>
       <c r="H169" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I169" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="170" spans="2:11">
@@ -6467,16 +6479,16 @@
         <v>26</v>
       </c>
       <c r="H170" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I170" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="171" spans="2:11">
@@ -6499,16 +6511,16 @@
         <v>26</v>
       </c>
       <c r="H171" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I171" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="172" spans="2:11">
@@ -6531,16 +6543,16 @@
         <v>26</v>
       </c>
       <c r="H172" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I172" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="173" spans="2:11">
@@ -6563,16 +6575,16 @@
         <v>26</v>
       </c>
       <c r="H173" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I173" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="174" spans="2:11">
@@ -6595,16 +6607,16 @@
         <v>26</v>
       </c>
       <c r="H174" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I174" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="175" spans="2:11">
@@ -6627,16 +6639,16 @@
         <v>26</v>
       </c>
       <c r="H175" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I175" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="176" spans="2:11">
@@ -6659,16 +6671,16 @@
         <v>26</v>
       </c>
       <c r="H176" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I176" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="177" spans="2:11">
@@ -6691,16 +6703,16 @@
         <v>26</v>
       </c>
       <c r="H177" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I177" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="178" spans="2:11">
@@ -6723,16 +6735,16 @@
         <v>26</v>
       </c>
       <c r="H178" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I178" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="179" spans="2:11">
@@ -6755,16 +6767,16 @@
         <v>26</v>
       </c>
       <c r="H179" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I179" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="180" spans="2:11">
@@ -6787,16 +6799,16 @@
         <v>26</v>
       </c>
       <c r="H180" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I180" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="181" spans="2:11">
@@ -6819,16 +6831,16 @@
         <v>26</v>
       </c>
       <c r="H181" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I181" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K181" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="182" spans="2:11">
@@ -6851,16 +6863,16 @@
         <v>26</v>
       </c>
       <c r="H182" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I182" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="183" spans="2:11">
@@ -6883,16 +6895,16 @@
         <v>26</v>
       </c>
       <c r="H183" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I183" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="185" spans="2:11">
@@ -6915,16 +6927,16 @@
         <v>26</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K185" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="186" spans="2:11">
@@ -6947,16 +6959,16 @@
         <v>26</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K186" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="187" spans="2:11">
@@ -6979,16 +6991,16 @@
         <v>26</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K187" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="188" spans="2:11">
@@ -7011,16 +7023,16 @@
         <v>26</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K188" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="189" spans="2:11">
@@ -7043,16 +7055,16 @@
         <v>26</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K189" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190" spans="2:11">
@@ -7075,16 +7087,16 @@
         <v>26</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="191" spans="2:11">
@@ -7107,16 +7119,16 @@
         <v>26</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="192" spans="2:11">
@@ -7139,16 +7151,16 @@
         <v>26</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="193" spans="2:11">
@@ -7171,16 +7183,16 @@
         <v>26</v>
       </c>
       <c r="H193" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I193" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="194" spans="2:11">
@@ -7203,16 +7215,16 @@
         <v>26</v>
       </c>
       <c r="H194" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I194" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="195" spans="2:11">
@@ -7235,16 +7247,16 @@
         <v>26</v>
       </c>
       <c r="H195" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I195" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K195" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="196" spans="2:11">
@@ -7267,16 +7279,16 @@
         <v>26</v>
       </c>
       <c r="H196" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I196" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="197" spans="2:11">
@@ -7299,16 +7311,16 @@
         <v>26</v>
       </c>
       <c r="H197" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I197" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="198" spans="2:11">
@@ -7331,16 +7343,16 @@
         <v>26</v>
       </c>
       <c r="H198" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I198" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="199" spans="2:11">
@@ -7363,16 +7375,16 @@
         <v>26</v>
       </c>
       <c r="H199" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I199" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="200" spans="2:11">
@@ -7395,16 +7407,16 @@
         <v>26</v>
       </c>
       <c r="H200" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I200" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="201" spans="2:11">
@@ -7427,16 +7439,16 @@
         <v>26</v>
       </c>
       <c r="H201" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I201" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="202" spans="2:11">
@@ -7459,16 +7471,16 @@
         <v>26</v>
       </c>
       <c r="H202" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I202" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="203" spans="2:11">
@@ -7491,16 +7503,16 @@
         <v>26</v>
       </c>
       <c r="H203" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I203" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="204" spans="2:11">
@@ -7523,16 +7535,16 @@
         <v>26</v>
       </c>
       <c r="H204" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I204" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K204" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="205" spans="2:11">
@@ -7555,16 +7567,16 @@
         <v>26</v>
       </c>
       <c r="H205" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I205" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="206" spans="2:11">
@@ -7587,16 +7599,16 @@
         <v>26</v>
       </c>
       <c r="H206" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I206" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K206" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="207" spans="2:11">
@@ -7619,16 +7631,16 @@
         <v>26</v>
       </c>
       <c r="H207" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I207" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K207" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="208" spans="2:11">
@@ -7651,16 +7663,16 @@
         <v>26</v>
       </c>
       <c r="H208" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I208" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="209" spans="2:11">
@@ -7683,16 +7695,16 @@
         <v>26</v>
       </c>
       <c r="H209" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I209" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="210" spans="2:11">
@@ -7715,16 +7727,16 @@
         <v>26</v>
       </c>
       <c r="H210" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I210" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K210" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="211" spans="2:11">
@@ -7747,16 +7759,16 @@
         <v>26</v>
       </c>
       <c r="H211" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I211" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="212" spans="2:11">
@@ -7779,16 +7791,16 @@
         <v>26</v>
       </c>
       <c r="H212" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I212" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="213" spans="2:11">
@@ -7811,16 +7823,16 @@
         <v>26</v>
       </c>
       <c r="H213" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I213" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="214" spans="2:11">
@@ -7843,16 +7855,16 @@
         <v>26</v>
       </c>
       <c r="H214" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I214" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="215" spans="2:11">
@@ -7875,16 +7887,16 @@
         <v>26</v>
       </c>
       <c r="H215" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I215" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="216" spans="2:11">
@@ -7907,16 +7919,16 @@
         <v>26</v>
       </c>
       <c r="H216" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I216" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="217" spans="2:11">
@@ -7939,16 +7951,16 @@
         <v>26</v>
       </c>
       <c r="H217" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I217" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="218" spans="2:11">
@@ -7971,16 +7983,16 @@
         <v>26</v>
       </c>
       <c r="H218" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I218" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K218" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="219" spans="2:11">
@@ -8003,16 +8015,16 @@
         <v>26</v>
       </c>
       <c r="H219" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I219" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="2:11">
@@ -8035,16 +8047,16 @@
         <v>26</v>
       </c>
       <c r="H220" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I220" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K220" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="2:11">
@@ -8067,16 +8079,16 @@
         <v>26</v>
       </c>
       <c r="H221" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I221" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="222" spans="2:11">
@@ -8099,16 +8111,16 @@
         <v>26</v>
       </c>
       <c r="H222" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I222" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K222" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="223" spans="2:11">
@@ -8131,16 +8143,16 @@
         <v>26</v>
       </c>
       <c r="H223" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I223" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="224" spans="2:11">
@@ -8163,16 +8175,16 @@
         <v>26</v>
       </c>
       <c r="H224" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I224" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="225" spans="2:11">
@@ -8195,16 +8207,16 @@
         <v>26</v>
       </c>
       <c r="H225" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I225" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="226" spans="2:11">
@@ -8227,16 +8239,16 @@
         <v>26</v>
       </c>
       <c r="H226" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I226" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K226" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="227" spans="2:11">
@@ -8259,16 +8271,16 @@
         <v>26</v>
       </c>
       <c r="H227" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I227" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="228" spans="2:11">
@@ -8291,16 +8303,16 @@
         <v>26</v>
       </c>
       <c r="H228" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I228" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="230" spans="2:11">
@@ -8320,19 +8332,19 @@
         <v>4</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I230" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J230" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J230" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K230" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="231" spans="2:11">
@@ -8352,19 +8364,19 @@
         <v>6</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I231" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J231" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J231" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K231" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="232" spans="2:11">
@@ -8384,19 +8396,19 @@
         <v>8</v>
       </c>
       <c r="G232" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H232" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I232" t="s">
+        <v>45</v>
+      </c>
+      <c r="J232" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J232" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K232" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="233" spans="2:11">
@@ -8416,19 +8428,19 @@
         <v>10</v>
       </c>
       <c r="G233" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H233" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I233" t="s">
+        <v>45</v>
+      </c>
+      <c r="J233" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J233" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K233" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="234" spans="2:11">
@@ -8448,19 +8460,19 @@
         <v>12</v>
       </c>
       <c r="G234" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H234" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I234" t="s">
+        <v>45</v>
+      </c>
+      <c r="J234" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J234" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K234" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="235" spans="2:11">
@@ -8480,19 +8492,19 @@
         <v>14</v>
       </c>
       <c r="G235" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H235" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I235" t="s">
+        <v>45</v>
+      </c>
+      <c r="J235" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J235" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K235" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="236" spans="2:11">
@@ -8512,19 +8524,19 @@
         <v>16</v>
       </c>
       <c r="G236" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H236" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I236" t="s">
+        <v>45</v>
+      </c>
+      <c r="J236" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J236" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K236" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="237" spans="2:11">
@@ -8544,19 +8556,19 @@
         <v>18</v>
       </c>
       <c r="G237" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H237" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I237" t="s">
+        <v>45</v>
+      </c>
+      <c r="J237" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J237" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K237" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="238" spans="2:11">
@@ -8576,19 +8588,19 @@
         <v>20</v>
       </c>
       <c r="G238" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H238" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I238" t="s">
+        <v>45</v>
+      </c>
+      <c r="J238" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J238" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K238" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="239" spans="2:11">
@@ -8608,19 +8620,19 @@
         <v>22</v>
       </c>
       <c r="G239" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H239" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I239" t="s">
+        <v>45</v>
+      </c>
+      <c r="J239" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J239" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K239" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="240" spans="2:11">
@@ -8640,20 +8652,152 @@
         <v>24</v>
       </c>
       <c r="G240" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H240" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I240" t="s">
+        <v>45</v>
+      </c>
+      <c r="J240" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J240" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="K240" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="241" spans="10:11">
+      <c r="J241"/>
+      <c r="K241"/>
+    </row>
+    <row r="242" spans="10:11">
+      <c r="J242"/>
+      <c r="K242"/>
+    </row>
+    <row r="243" spans="10:11">
+      <c r="J243"/>
+      <c r="K243"/>
+    </row>
+    <row r="244" spans="10:11">
+      <c r="J244"/>
+      <c r="K244"/>
+    </row>
+    <row r="245" spans="10:11">
+      <c r="J245"/>
+      <c r="K245"/>
+    </row>
+    <row r="246" spans="10:11">
+      <c r="J246"/>
+      <c r="K246"/>
+    </row>
+    <row r="247" spans="10:11">
+      <c r="J247"/>
+      <c r="K247"/>
+    </row>
+    <row r="248" spans="10:11">
+      <c r="J248"/>
+      <c r="K248"/>
+    </row>
+    <row r="249" spans="10:11">
+      <c r="J249"/>
+      <c r="K249"/>
+    </row>
+    <row r="250" spans="10:11">
+      <c r="J250"/>
+      <c r="K250"/>
+    </row>
+    <row r="251" spans="10:11">
+      <c r="J251"/>
+      <c r="K251"/>
+    </row>
+    <row r="252" spans="10:11">
+      <c r="J252"/>
+      <c r="K252"/>
+    </row>
+    <row r="253" spans="10:11">
+      <c r="J253"/>
+      <c r="K253"/>
+    </row>
+    <row r="254" spans="10:11">
+      <c r="J254"/>
+      <c r="K254"/>
+    </row>
+    <row r="255" spans="10:11">
+      <c r="J255"/>
+      <c r="K255"/>
+    </row>
+    <row r="256" spans="10:11">
+      <c r="J256"/>
+      <c r="K256"/>
+    </row>
+    <row r="257" spans="10:11">
+      <c r="J257"/>
+      <c r="K257"/>
+    </row>
+    <row r="258" spans="10:11">
+      <c r="J258"/>
+      <c r="K258"/>
+    </row>
+    <row r="259" spans="10:11">
+      <c r="J259"/>
+      <c r="K259"/>
+    </row>
+    <row r="260" spans="10:11">
+      <c r="J260"/>
+      <c r="K260"/>
+    </row>
+    <row r="261" spans="10:11">
+      <c r="J261"/>
+      <c r="K261"/>
+    </row>
+    <row r="262" spans="10:11">
+      <c r="J262"/>
+      <c r="K262"/>
+    </row>
+    <row r="263" spans="10:11">
+      <c r="J263"/>
+      <c r="K263"/>
+    </row>
+    <row r="264" spans="10:11">
+      <c r="J264"/>
+      <c r="K264"/>
+    </row>
+    <row r="265" spans="10:11">
+      <c r="J265"/>
+      <c r="K265"/>
+    </row>
+    <row r="266" spans="10:11">
+      <c r="J266"/>
+      <c r="K266"/>
+    </row>
+    <row r="267" spans="10:11">
+      <c r="J267"/>
+      <c r="K267"/>
+    </row>
+    <row r="268" spans="10:11">
+      <c r="J268"/>
+      <c r="K268"/>
+    </row>
+    <row r="269" spans="10:11">
+      <c r="J269"/>
+      <c r="K269"/>
+    </row>
+    <row r="270" spans="10:11">
+      <c r="J270"/>
+      <c r="K270"/>
+    </row>
+    <row r="271" spans="10:11">
+      <c r="J271"/>
+      <c r="K271"/>
+    </row>
+    <row r="272" spans="10:11">
+      <c r="J272"/>
+      <c r="K272"/>
+    </row>
+    <row r="273" spans="10:11">
+      <c r="J273"/>
+      <c r="K273"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16380" windowHeight="7635"/>
+    <workbookView windowWidth="17145" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
   </si>
   <si>
     <t>Icon</t>
@@ -100,6 +103,9 @@
     <t>怪物名字</t>
   </si>
   <si>
+    <t>怪物介绍</t>
+  </si>
+  <si>
     <t>怪物icon</t>
   </si>
   <si>
@@ -118,6 +124,9 @@
     <t>屎莱姆</t>
   </si>
   <si>
+    <t>黏糊糊的,身板脆弱</t>
+  </si>
+  <si>
     <t>enemy1</t>
   </si>
   <si>
@@ -130,10 +139,16 @@
     <t>狼哥</t>
   </si>
   <si>
+    <t>喜欢看电影,最爱看港片[赌神]</t>
+  </si>
+  <si>
     <t>enemy2</t>
   </si>
   <si>
     <t>蛙弟</t>
+  </si>
+  <si>
+    <t>经常被忽视,喜欢打翻身仗</t>
   </si>
   <si>
     <t>enemy3</t>
@@ -148,10 +163,16 @@
     <t>小蜜蜂</t>
   </si>
   <si>
+    <t>虽然杀伤力不强,但声音惹人烦</t>
+  </si>
+  <si>
     <t>enemy4</t>
   </si>
   <si>
     <t>蘑菇人</t>
+  </si>
+  <si>
+    <t>身体强壮,但行动颇为缓慢</t>
   </si>
   <si>
     <t>enemy5</t>
@@ -167,6 +188,9 @@
   </si>
   <si>
     <t>大眼仔</t>
+  </si>
+  <si>
+    <t>首领之一,颇具杀伤力</t>
   </si>
   <si>
     <t>enemy6</t>
@@ -1143,10 +1167,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L273"/>
+  <dimension ref="A1:M273"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.03333333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="6.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="4.55833333333333" style="1" customWidth="1"/>
@@ -1154,14 +1178,14 @@
     <col min="6" max="6" width="5.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.95" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.475" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.91666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.36666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.4333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.4916666666667" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="9" max="10" width="8.91666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.36666666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.4333333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.4916666666667" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1198,84 +1222,93 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5" s="1">
         <v>1001001</v>
       </c>
@@ -1292,22 +1325,25 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6" s="1">
         <v>1001002</v>
       </c>
@@ -1324,22 +1360,25 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7" s="1">
         <v>1001003</v>
       </c>
@@ -1356,22 +1395,25 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="B8" s="1">
         <v>1001004</v>
       </c>
@@ -1388,22 +1430,25 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="B9" s="1">
         <v>1001005</v>
       </c>
@@ -1420,22 +1465,25 @@
         <v>2</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="B10" s="1">
         <v>1001006</v>
       </c>
@@ -1452,22 +1500,25 @@
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="B11" s="1">
         <v>1001007</v>
       </c>
@@ -1484,22 +1535,25 @@
         <v>2</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="B12" s="1">
         <v>1001008</v>
       </c>
@@ -1516,22 +1570,25 @@
         <v>2</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="B13" s="2">
         <v>1001009</v>
       </c>
@@ -1548,22 +1605,25 @@
         <v>3</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" t="s">
+        <v>31</v>
+      </c>
       <c r="K13" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="B14" s="2">
         <v>1001010</v>
       </c>
@@ -1580,22 +1640,25 @@
         <v>3</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" t="s">
+        <v>31</v>
+      </c>
       <c r="K14" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="B15" s="2">
         <v>1001011</v>
       </c>
@@ -1612,22 +1675,25 @@
         <v>3</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
       <c r="K15" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>32</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="B16" s="2">
         <v>1001012</v>
       </c>
@@ -1644,22 +1710,25 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" t="s">
+        <v>31</v>
+      </c>
       <c r="K16" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
       <c r="B17" s="2">
         <v>1001013</v>
       </c>
@@ -1676,22 +1745,25 @@
         <v>3</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" t="s">
+        <v>31</v>
+      </c>
       <c r="K17" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12">
       <c r="B18" s="2">
         <v>1001014</v>
       </c>
@@ -1708,22 +1780,25 @@
         <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" t="s">
+        <v>31</v>
+      </c>
       <c r="K18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
       <c r="B19" s="2">
         <v>1001015</v>
       </c>
@@ -1740,22 +1815,25 @@
         <v>3</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" t="s">
+        <v>31</v>
+      </c>
       <c r="K19" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
       <c r="B20" s="2">
         <v>1001016</v>
       </c>
@@ -1772,22 +1850,25 @@
         <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" t="s">
+        <v>31</v>
+      </c>
       <c r="K20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
       <c r="B21" s="2">
         <v>1001017</v>
       </c>
@@ -1804,22 +1885,25 @@
         <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" t="s">
+        <v>31</v>
+      </c>
       <c r="K21" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
       <c r="B22" s="2">
         <v>1001018</v>
       </c>
@@ -1836,22 +1920,25 @@
         <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" t="s">
+        <v>31</v>
+      </c>
       <c r="K22" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12">
       <c r="B23" s="2">
         <v>1001019</v>
       </c>
@@ -1868,22 +1955,25 @@
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H23" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" t="s">
+        <v>31</v>
+      </c>
       <c r="K23" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
       <c r="B24" s="2">
         <v>1001020</v>
       </c>
@@ -1900,22 +1990,25 @@
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I24" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
       <c r="K24" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
       <c r="B25" s="2">
         <v>1001021</v>
       </c>
@@ -1932,22 +2025,25 @@
         <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
-      </c>
-      <c r="I25" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
       <c r="K25" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
       <c r="B26" s="2">
         <v>1001022</v>
       </c>
@@ -1964,22 +2060,25 @@
         <v>5</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H26" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J26" t="s">
+        <v>31</v>
+      </c>
       <c r="K26" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12">
       <c r="B27" s="2">
         <v>1001023</v>
       </c>
@@ -1996,22 +2095,25 @@
         <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H27" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J27" t="s">
+        <v>31</v>
+      </c>
       <c r="K27" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
       <c r="B28" s="2">
         <v>1001024</v>
       </c>
@@ -2028,22 +2130,25 @@
         <v>5</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H28" t="s">
-        <v>27</v>
-      </c>
-      <c r="I28" t="s">
-        <v>28</v>
-      </c>
-      <c r="J28" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J28" t="s">
+        <v>31</v>
+      </c>
       <c r="K28" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12">
       <c r="B29" s="2">
         <v>1001025</v>
       </c>
@@ -2060,22 +2165,25 @@
         <v>5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H29" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29" t="s">
-        <v>28</v>
-      </c>
-      <c r="J29" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J29" t="s">
+        <v>31</v>
+      </c>
       <c r="K29" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12">
       <c r="B30" s="2">
         <v>1001026</v>
       </c>
@@ -2092,22 +2200,25 @@
         <v>5</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
-      </c>
-      <c r="I30" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J30" t="s">
+        <v>31</v>
+      </c>
       <c r="K30" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12">
       <c r="B31" s="2">
         <v>1001027</v>
       </c>
@@ -2124,22 +2235,25 @@
         <v>5</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31" t="s">
-        <v>28</v>
-      </c>
-      <c r="J31" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J31" t="s">
+        <v>31</v>
+      </c>
       <c r="K31" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12">
       <c r="B32" s="2">
         <v>1001028</v>
       </c>
@@ -2156,22 +2270,25 @@
         <v>5</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
-      </c>
-      <c r="I32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J32" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J32" t="s">
+        <v>31</v>
+      </c>
       <c r="K32" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
       <c r="B33" s="2">
         <v>1001029</v>
       </c>
@@ -2188,22 +2305,25 @@
         <v>6</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" t="s">
-        <v>28</v>
-      </c>
-      <c r="J33" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
       <c r="K33" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
       <c r="B34" s="2">
         <v>1001030</v>
       </c>
@@ -2220,22 +2340,25 @@
         <v>6</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H34" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" t="s">
-        <v>28</v>
-      </c>
-      <c r="J34" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J34" t="s">
+        <v>31</v>
+      </c>
       <c r="K34" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
       <c r="B35" s="2">
         <v>1001031</v>
       </c>
@@ -2252,22 +2375,25 @@
         <v>6</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H35" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J35" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" t="s">
+        <v>31</v>
+      </c>
       <c r="K35" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
       <c r="B36" s="2">
         <v>1001032</v>
       </c>
@@ -2284,22 +2410,25 @@
         <v>6</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
-      </c>
-      <c r="I36" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" t="s">
+        <v>31</v>
+      </c>
       <c r="K36" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
       <c r="B37" s="2">
         <v>1001033</v>
       </c>
@@ -2316,22 +2445,25 @@
         <v>7</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H37" t="s">
-        <v>27</v>
-      </c>
-      <c r="I37" t="s">
-        <v>28</v>
-      </c>
-      <c r="J37" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" t="s">
+        <v>31</v>
+      </c>
       <c r="K37" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
       <c r="B38" s="2">
         <v>1001034</v>
       </c>
@@ -2348,22 +2480,25 @@
         <v>7</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H38" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" t="s">
-        <v>28</v>
-      </c>
-      <c r="J38" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" t="s">
+        <v>31</v>
+      </c>
       <c r="K38" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
       <c r="B39" s="2">
         <v>1001035</v>
       </c>
@@ -2380,22 +2515,25 @@
         <v>7</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H39" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39" t="s">
-        <v>28</v>
-      </c>
-      <c r="J39" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J39" t="s">
+        <v>31</v>
+      </c>
       <c r="K39" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12">
       <c r="B40" s="2">
         <v>1001036</v>
       </c>
@@ -2412,22 +2550,25 @@
         <v>7</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H40" t="s">
-        <v>27</v>
-      </c>
-      <c r="I40" t="s">
-        <v>28</v>
-      </c>
-      <c r="J40" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J40" t="s">
+        <v>31</v>
+      </c>
       <c r="K40" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12">
       <c r="B41" s="2">
         <v>1001037</v>
       </c>
@@ -2444,22 +2585,25 @@
         <v>7</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H41" t="s">
-        <v>27</v>
-      </c>
-      <c r="I41" t="s">
-        <v>28</v>
-      </c>
-      <c r="J41" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J41" t="s">
+        <v>31</v>
+      </c>
       <c r="K41" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12">
       <c r="B42" s="2">
         <v>1001038</v>
       </c>
@@ -2476,22 +2620,25 @@
         <v>7</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H42" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" t="s">
-        <v>28</v>
-      </c>
-      <c r="J42" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J42" t="s">
+        <v>31</v>
+      </c>
       <c r="K42" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12">
       <c r="B43" s="2">
         <v>1001039</v>
       </c>
@@ -2508,22 +2655,25 @@
         <v>7</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H43" t="s">
-        <v>27</v>
-      </c>
-      <c r="I43" t="s">
-        <v>28</v>
-      </c>
-      <c r="J43" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J43" t="s">
+        <v>31</v>
+      </c>
       <c r="K43" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12">
       <c r="B44" s="2">
         <v>1001040</v>
       </c>
@@ -2540,22 +2690,25 @@
         <v>7</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H44" t="s">
-        <v>27</v>
-      </c>
-      <c r="I44" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J44" t="s">
+        <v>31</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
       <c r="B45" s="2">
         <v>1001041</v>
       </c>
@@ -2572,22 +2725,25 @@
         <v>8</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H45" t="s">
-        <v>27</v>
-      </c>
-      <c r="I45" t="s">
-        <v>28</v>
-      </c>
-      <c r="J45" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J45" t="s">
+        <v>31</v>
+      </c>
       <c r="K45" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12">
       <c r="B46" s="2">
         <v>1001042</v>
       </c>
@@ -2604,22 +2760,25 @@
         <v>8</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H46" t="s">
-        <v>27</v>
-      </c>
-      <c r="I46" t="s">
-        <v>28</v>
-      </c>
-      <c r="J46" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I46" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J46" t="s">
+        <v>31</v>
+      </c>
       <c r="K46" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12">
       <c r="B47" s="2">
         <v>1001043</v>
       </c>
@@ -2636,22 +2795,25 @@
         <v>8</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H47" t="s">
-        <v>27</v>
-      </c>
-      <c r="I47" t="s">
-        <v>28</v>
-      </c>
-      <c r="J47" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J47" t="s">
+        <v>31</v>
+      </c>
       <c r="K47" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12">
       <c r="B48" s="2">
         <v>1001044</v>
       </c>
@@ -2668,22 +2830,25 @@
         <v>8</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H48" t="s">
-        <v>27</v>
-      </c>
-      <c r="I48" t="s">
-        <v>28</v>
-      </c>
-      <c r="J48" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="I48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J48" t="s">
+        <v>31</v>
+      </c>
       <c r="K48" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
+        <v>32</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12">
       <c r="B50" s="1">
         <v>1002001</v>
       </c>
@@ -2700,22 +2865,25 @@
         <v>2</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
+      <c r="L50" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12">
       <c r="B51" s="1">
         <v>1002002</v>
       </c>
@@ -2732,22 +2900,25 @@
         <v>2</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
+      <c r="L51" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12">
       <c r="B52" s="1">
         <v>1002003</v>
       </c>
@@ -2764,22 +2935,25 @@
         <v>2</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
+      <c r="L52" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12">
       <c r="B53" s="1">
         <v>1002004</v>
       </c>
@@ -2796,22 +2970,25 @@
         <v>2</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
+      <c r="L53" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12">
       <c r="B54" s="1">
         <v>1002005</v>
       </c>
@@ -2828,22 +3005,25 @@
         <v>3</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
+      <c r="L54" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12">
       <c r="B55" s="1">
         <v>1002006</v>
       </c>
@@ -2860,22 +3040,25 @@
         <v>3</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
+      <c r="L55" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12">
       <c r="B56" s="1">
         <v>1002007</v>
       </c>
@@ -2892,22 +3075,25 @@
         <v>3</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
+      <c r="L56" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12">
       <c r="B57" s="1">
         <v>1002008</v>
       </c>
@@ -2924,22 +3110,25 @@
         <v>3</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
+      <c r="L57" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12">
       <c r="B58" s="2">
         <v>1002009</v>
       </c>
@@ -2956,22 +3145,25 @@
         <v>4</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H58" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" t="s">
+        <v>34</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J58" t="s">
+        <v>36</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
+      <c r="L58" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12">
       <c r="B59" s="2">
         <v>1002010</v>
       </c>
@@ -2988,22 +3180,25 @@
         <v>4</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H59" t="s">
-        <v>31</v>
-      </c>
-      <c r="I59" t="s">
+        <v>34</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J59" t="s">
+        <v>36</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
+      <c r="L59" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12">
       <c r="B60" s="2">
         <v>1002011</v>
       </c>
@@ -3020,22 +3215,25 @@
         <v>4</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H60" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" t="s">
+        <v>34</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J60" t="s">
+        <v>36</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
+      <c r="L60" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12">
       <c r="B61" s="2">
         <v>1002012</v>
       </c>
@@ -3052,22 +3250,25 @@
         <v>4</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H61" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" t="s">
+        <v>34</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J61" t="s">
+        <v>36</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
+      <c r="L61" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12">
       <c r="B62" s="2">
         <v>1002013</v>
       </c>
@@ -3084,22 +3285,25 @@
         <v>5</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H62" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62" t="s">
+        <v>34</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J62" t="s">
+        <v>36</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
+      <c r="L62" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12">
       <c r="B63" s="2">
         <v>1002014</v>
       </c>
@@ -3116,22 +3320,25 @@
         <v>5</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H63" t="s">
-        <v>31</v>
-      </c>
-      <c r="I63" t="s">
+        <v>34</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J63" t="s">
+        <v>36</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
+      <c r="L63" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12">
       <c r="B64" s="2">
         <v>1002015</v>
       </c>
@@ -3148,22 +3355,25 @@
         <v>5</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" t="s">
+        <v>34</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J64" t="s">
+        <v>36</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
+      <c r="L64" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12">
       <c r="B65" s="2">
         <v>1002016</v>
       </c>
@@ -3180,22 +3390,25 @@
         <v>5</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H65" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" t="s">
+        <v>34</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J65" t="s">
+        <v>36</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
+      <c r="L65" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12">
       <c r="B66" s="2">
         <v>1002017</v>
       </c>
@@ -3212,22 +3425,25 @@
         <v>6</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" t="s">
+        <v>34</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J66" t="s">
+        <v>36</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
+      <c r="L66" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12">
       <c r="B67" s="2">
         <v>1002018</v>
       </c>
@@ -3244,22 +3460,25 @@
         <v>6</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H67" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" t="s">
+        <v>34</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J67" t="s">
+        <v>36</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
+      <c r="L67" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12">
       <c r="B68" s="2">
         <v>1002019</v>
       </c>
@@ -3276,22 +3495,25 @@
         <v>6</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H68" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" t="s">
+        <v>34</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J68" t="s">
+        <v>36</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
+      <c r="L68" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12">
       <c r="B69" s="2">
         <v>1002020</v>
       </c>
@@ -3308,22 +3530,25 @@
         <v>6</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H69" t="s">
-        <v>31</v>
-      </c>
-      <c r="I69" t="s">
+        <v>34</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J69" t="s">
+        <v>36</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
+      <c r="L69" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12">
       <c r="B70" s="2">
         <v>1002021</v>
       </c>
@@ -3340,22 +3565,25 @@
         <v>7</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H70" t="s">
-        <v>31</v>
-      </c>
-      <c r="I70" t="s">
+        <v>34</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J70" t="s">
+        <v>36</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11">
+      <c r="L70" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12">
       <c r="B71" s="2">
         <v>1002022</v>
       </c>
@@ -3372,22 +3600,25 @@
         <v>7</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H71" t="s">
-        <v>31</v>
-      </c>
-      <c r="I71" t="s">
+        <v>34</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J71" t="s">
+        <v>36</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
+      <c r="L71" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12">
       <c r="B72" s="2">
         <v>1002023</v>
       </c>
@@ -3404,22 +3635,25 @@
         <v>7</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H72" t="s">
-        <v>31</v>
-      </c>
-      <c r="I72" t="s">
+        <v>34</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J72" t="s">
+        <v>36</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
+      <c r="L72" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12">
       <c r="B73" s="2">
         <v>1002024</v>
       </c>
@@ -3436,22 +3670,25 @@
         <v>7</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H73" t="s">
-        <v>31</v>
-      </c>
-      <c r="I73" t="s">
+        <v>34</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J73" t="s">
+        <v>36</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
+      <c r="L73" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12">
       <c r="B74" s="2">
         <v>1002025</v>
       </c>
@@ -3468,22 +3705,25 @@
         <v>8</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
-      </c>
-      <c r="I74" t="s">
+        <v>34</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J74" t="s">
+        <v>36</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
+      <c r="L74" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12">
       <c r="B75" s="2">
         <v>1002026</v>
       </c>
@@ -3500,22 +3740,25 @@
         <v>8</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
-      </c>
-      <c r="I75" t="s">
+        <v>34</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J75" t="s">
+        <v>36</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
+      <c r="L75" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12">
       <c r="B76" s="2">
         <v>1002027</v>
       </c>
@@ -3532,22 +3775,25 @@
         <v>8</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H76" t="s">
-        <v>31</v>
-      </c>
-      <c r="I76" t="s">
+        <v>34</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J76" t="s">
+        <v>36</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J76" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
+      <c r="L76" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12">
       <c r="B77" s="2">
         <v>1002028</v>
       </c>
@@ -3564,22 +3810,25 @@
         <v>8</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H77" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" t="s">
+        <v>34</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J77" t="s">
+        <v>36</v>
+      </c>
+      <c r="K77" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
+      <c r="L77" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12">
       <c r="B78" s="2">
         <v>1002029</v>
       </c>
@@ -3596,22 +3845,25 @@
         <v>9</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
-      </c>
-      <c r="I78" t="s">
+        <v>34</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J78" t="s">
+        <v>36</v>
+      </c>
+      <c r="K78" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
+      <c r="L78" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12">
       <c r="B79" s="2">
         <v>1002030</v>
       </c>
@@ -3628,22 +3880,25 @@
         <v>9</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H79" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" t="s">
+        <v>34</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J79" t="s">
+        <v>36</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
+      <c r="L79" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12">
       <c r="B80" s="2">
         <v>1002031</v>
       </c>
@@ -3660,22 +3915,25 @@
         <v>9</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H80" t="s">
-        <v>31</v>
-      </c>
-      <c r="I80" t="s">
+        <v>34</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J80" t="s">
+        <v>36</v>
+      </c>
+      <c r="K80" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
+      <c r="L80" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12">
       <c r="B81" s="2">
         <v>1002032</v>
       </c>
@@ -3692,22 +3950,25 @@
         <v>9</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H81" t="s">
-        <v>31</v>
-      </c>
-      <c r="I81" t="s">
+        <v>34</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J81" t="s">
+        <v>36</v>
+      </c>
+      <c r="K81" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
+      <c r="L81" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12">
       <c r="B82" s="2">
         <v>1002033</v>
       </c>
@@ -3724,22 +3985,25 @@
         <v>10</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H82" t="s">
-        <v>31</v>
-      </c>
-      <c r="I82" t="s">
+        <v>34</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J82" t="s">
+        <v>36</v>
+      </c>
+      <c r="K82" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
+      <c r="L82" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12">
       <c r="B83" s="2">
         <v>1002034</v>
       </c>
@@ -3756,22 +4020,25 @@
         <v>10</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H83" t="s">
-        <v>31</v>
-      </c>
-      <c r="I83" t="s">
+        <v>34</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J83" t="s">
+        <v>36</v>
+      </c>
+      <c r="K83" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
+      <c r="L83" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12">
       <c r="B84" s="2">
         <v>1002035</v>
       </c>
@@ -3788,22 +4055,25 @@
         <v>10</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H84" t="s">
-        <v>31</v>
-      </c>
-      <c r="I84" t="s">
+        <v>34</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J84" t="s">
+        <v>36</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
+      <c r="L84" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12">
       <c r="B85" s="2">
         <v>1002036</v>
       </c>
@@ -3820,22 +4090,25 @@
         <v>10</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H85" t="s">
-        <v>31</v>
-      </c>
-      <c r="I85" t="s">
+        <v>34</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J85" t="s">
+        <v>36</v>
+      </c>
+      <c r="K85" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
+      <c r="L85" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12">
       <c r="B86" s="2">
         <v>1002037</v>
       </c>
@@ -3852,22 +4125,25 @@
         <v>11</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H86" t="s">
-        <v>31</v>
-      </c>
-      <c r="I86" t="s">
+        <v>34</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J86" t="s">
+        <v>36</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
+      <c r="L86" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12">
       <c r="B87" s="2">
         <v>1002038</v>
       </c>
@@ -3884,22 +4160,25 @@
         <v>11</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H87" t="s">
-        <v>31</v>
-      </c>
-      <c r="I87" t="s">
+        <v>34</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J87" t="s">
+        <v>36</v>
+      </c>
+      <c r="K87" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11">
+      <c r="L87" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="88" spans="2:12">
       <c r="B88" s="2">
         <v>1002039</v>
       </c>
@@ -3916,22 +4195,25 @@
         <v>11</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H88" t="s">
-        <v>31</v>
-      </c>
-      <c r="I88" t="s">
+        <v>34</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J88" t="s">
+        <v>36</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
+      <c r="L88" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12">
       <c r="B89" s="2">
         <v>1002040</v>
       </c>
@@ -3948,22 +4230,25 @@
         <v>11</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
-      </c>
-      <c r="I89" t="s">
+        <v>34</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J89" t="s">
+        <v>36</v>
+      </c>
+      <c r="K89" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
+      <c r="L89" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12">
       <c r="B90" s="2">
         <v>1002041</v>
       </c>
@@ -3980,22 +4265,25 @@
         <v>12</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H90" t="s">
-        <v>31</v>
-      </c>
-      <c r="I90" t="s">
+        <v>34</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J90" t="s">
+        <v>36</v>
+      </c>
+      <c r="K90" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J90" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
+      <c r="L90" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12">
       <c r="B91" s="2">
         <v>1002042</v>
       </c>
@@ -4012,22 +4300,25 @@
         <v>12</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
-      </c>
-      <c r="I91" t="s">
+        <v>34</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J91" t="s">
+        <v>36</v>
+      </c>
+      <c r="K91" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J91" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
+      <c r="L91" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" spans="2:12">
       <c r="B92" s="2">
         <v>1002043</v>
       </c>
@@ -4044,22 +4335,25 @@
         <v>12</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H92" t="s">
-        <v>31</v>
-      </c>
-      <c r="I92" t="s">
+        <v>34</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J92" t="s">
+        <v>36</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J92" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
+      <c r="L92" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93" spans="2:12">
       <c r="B93" s="2">
         <v>1002044</v>
       </c>
@@ -4076,22 +4370,25 @@
         <v>12</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H93" t="s">
-        <v>31</v>
-      </c>
-      <c r="I93" t="s">
+        <v>34</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J93" t="s">
+        <v>36</v>
+      </c>
+      <c r="K93" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J93" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11">
+      <c r="L93" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12">
       <c r="B95" s="1">
         <v>1003001</v>
       </c>
@@ -4108,22 +4405,25 @@
         <v>3</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="96" spans="2:12">
       <c r="B96" s="1">
         <v>1003002</v>
       </c>
@@ -4140,22 +4440,25 @@
         <v>3</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="97" spans="2:12">
       <c r="B97" s="1">
         <v>1003003</v>
       </c>
@@ -4172,22 +4475,25 @@
         <v>3</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="2:12">
       <c r="B98" s="1">
         <v>1003004</v>
       </c>
@@ -4204,22 +4510,25 @@
         <v>3</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="2:12">
       <c r="B99" s="1">
         <v>1003005</v>
       </c>
@@ -4236,22 +4545,25 @@
         <v>4</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12">
       <c r="B100" s="1">
         <v>1003006</v>
       </c>
@@ -4268,22 +4580,25 @@
         <v>4</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101" spans="2:12">
       <c r="B101" s="1">
         <v>1003007</v>
       </c>
@@ -4300,22 +4615,25 @@
         <v>4</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="102" spans="2:12">
       <c r="B102" s="1">
         <v>1003008</v>
       </c>
@@ -4332,22 +4650,25 @@
         <v>4</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="103" spans="2:12">
       <c r="B103" s="2">
         <v>1003009</v>
       </c>
@@ -4364,22 +4685,25 @@
         <v>5</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H103" t="s">
-        <v>33</v>
-      </c>
-      <c r="I103" t="s">
-        <v>34</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J103" t="s">
+        <v>39</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12">
       <c r="B104" s="2">
         <v>1003010</v>
       </c>
@@ -4396,22 +4720,25 @@
         <v>5</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H104" t="s">
-        <v>33</v>
-      </c>
-      <c r="I104" t="s">
-        <v>34</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J104" t="s">
+        <v>39</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12">
       <c r="B105" s="2">
         <v>1003011</v>
       </c>
@@ -4428,22 +4755,25 @@
         <v>5</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H105" t="s">
-        <v>33</v>
-      </c>
-      <c r="I105" t="s">
-        <v>34</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J105" t="s">
+        <v>39</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="106" spans="2:12">
       <c r="B106" s="2">
         <v>1003012</v>
       </c>
@@ -4460,22 +4790,25 @@
         <v>5</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H106" t="s">
-        <v>33</v>
-      </c>
-      <c r="I106" t="s">
-        <v>34</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J106" t="s">
+        <v>39</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="107" spans="2:12">
       <c r="B107" s="2">
         <v>1003013</v>
       </c>
@@ -4492,22 +4825,25 @@
         <v>7</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H107" t="s">
-        <v>33</v>
-      </c>
-      <c r="I107" t="s">
-        <v>34</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J107" t="s">
+        <v>39</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="2:12">
       <c r="B108" s="2">
         <v>1003014</v>
       </c>
@@ -4524,22 +4860,25 @@
         <v>7</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H108" t="s">
-        <v>33</v>
-      </c>
-      <c r="I108" t="s">
-        <v>34</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J108" t="s">
+        <v>39</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="109" spans="2:12">
       <c r="B109" s="2">
         <v>1003015</v>
       </c>
@@ -4556,22 +4895,25 @@
         <v>7</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H109" t="s">
-        <v>33</v>
-      </c>
-      <c r="I109" t="s">
-        <v>34</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J109" t="s">
+        <v>39</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110" spans="2:12">
       <c r="B110" s="2">
         <v>1003016</v>
       </c>
@@ -4588,22 +4930,25 @@
         <v>7</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H110" t="s">
-        <v>33</v>
-      </c>
-      <c r="I110" t="s">
-        <v>34</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J110" t="s">
+        <v>39</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="111" spans="2:12">
       <c r="B111" s="2">
         <v>1003017</v>
       </c>
@@ -4620,22 +4965,25 @@
         <v>8</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H111" t="s">
-        <v>33</v>
-      </c>
-      <c r="I111" t="s">
-        <v>34</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J111" t="s">
+        <v>39</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12">
       <c r="B112" s="2">
         <v>1003018</v>
       </c>
@@ -4652,22 +5000,25 @@
         <v>8</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H112" t="s">
-        <v>33</v>
-      </c>
-      <c r="I112" t="s">
-        <v>34</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J112" t="s">
+        <v>39</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="113" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12">
       <c r="B113" s="2">
         <v>1003019</v>
       </c>
@@ -4684,22 +5035,25 @@
         <v>8</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H113" t="s">
-        <v>33</v>
-      </c>
-      <c r="I113" t="s">
-        <v>34</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J113" t="s">
+        <v>39</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="114" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12">
       <c r="B114" s="2">
         <v>1003020</v>
       </c>
@@ -4716,22 +5070,25 @@
         <v>8</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H114" t="s">
-        <v>33</v>
-      </c>
-      <c r="I114" t="s">
-        <v>34</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J114" t="s">
+        <v>39</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="115" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="115" spans="2:12">
       <c r="B115" s="2">
         <v>1003021</v>
       </c>
@@ -4748,22 +5105,25 @@
         <v>9</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H115" t="s">
-        <v>33</v>
-      </c>
-      <c r="I115" t="s">
-        <v>34</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J115" t="s">
+        <v>39</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="116" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116" spans="2:12">
       <c r="B116" s="2">
         <v>1003022</v>
       </c>
@@ -4780,22 +5140,25 @@
         <v>9</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H116" t="s">
-        <v>33</v>
-      </c>
-      <c r="I116" t="s">
-        <v>34</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J116" t="s">
+        <v>39</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="117" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="117" spans="2:12">
       <c r="B117" s="2">
         <v>1003023</v>
       </c>
@@ -4812,22 +5175,25 @@
         <v>9</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H117" t="s">
-        <v>33</v>
-      </c>
-      <c r="I117" t="s">
-        <v>34</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J117" t="s">
+        <v>39</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="118" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="118" spans="2:12">
       <c r="B118" s="2">
         <v>1003024</v>
       </c>
@@ -4844,22 +5210,25 @@
         <v>9</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H118" t="s">
-        <v>33</v>
-      </c>
-      <c r="I118" t="s">
-        <v>34</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J118" t="s">
+        <v>39</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="119" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="119" spans="2:12">
       <c r="B119" s="2">
         <v>1003025</v>
       </c>
@@ -4876,22 +5245,25 @@
         <v>11</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H119" t="s">
-        <v>33</v>
-      </c>
-      <c r="I119" t="s">
-        <v>34</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J119" t="s">
+        <v>39</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="120" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="120" spans="2:12">
       <c r="B120" s="2">
         <v>1003026</v>
       </c>
@@ -4908,22 +5280,25 @@
         <v>11</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H120" t="s">
-        <v>33</v>
-      </c>
-      <c r="I120" t="s">
-        <v>34</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J120" t="s">
+        <v>39</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="121" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="121" spans="2:12">
       <c r="B121" s="2">
         <v>1003027</v>
       </c>
@@ -4940,22 +5315,25 @@
         <v>11</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H121" t="s">
-        <v>33</v>
-      </c>
-      <c r="I121" t="s">
-        <v>34</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J121" t="s">
+        <v>39</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="122" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="122" spans="2:12">
       <c r="B122" s="2">
         <v>1003028</v>
       </c>
@@ -4972,22 +5350,25 @@
         <v>11</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H122" t="s">
-        <v>33</v>
-      </c>
-      <c r="I122" t="s">
-        <v>34</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J122" t="s">
+        <v>39</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="123" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="123" spans="2:12">
       <c r="B123" s="2">
         <v>1003029</v>
       </c>
@@ -5004,22 +5385,25 @@
         <v>12</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H123" t="s">
-        <v>33</v>
-      </c>
-      <c r="I123" t="s">
-        <v>34</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J123" t="s">
+        <v>39</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="124" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="124" spans="2:12">
       <c r="B124" s="2">
         <v>1003030</v>
       </c>
@@ -5036,22 +5420,25 @@
         <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H124" t="s">
-        <v>33</v>
-      </c>
-      <c r="I124" t="s">
-        <v>34</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J124" t="s">
+        <v>39</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="125" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="125" spans="2:12">
       <c r="B125" s="2">
         <v>1003031</v>
       </c>
@@ -5068,22 +5455,25 @@
         <v>12</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H125" t="s">
-        <v>33</v>
-      </c>
-      <c r="I125" t="s">
-        <v>34</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J125" t="s">
+        <v>39</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="126" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="126" spans="2:12">
       <c r="B126" s="2">
         <v>1003032</v>
       </c>
@@ -5100,22 +5490,25 @@
         <v>12</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H126" t="s">
-        <v>33</v>
-      </c>
-      <c r="I126" t="s">
-        <v>34</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J126" t="s">
+        <v>39</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="127" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="127" spans="2:12">
       <c r="B127" s="2">
         <v>1003033</v>
       </c>
@@ -5132,22 +5525,25 @@
         <v>13</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H127" t="s">
-        <v>33</v>
-      </c>
-      <c r="I127" t="s">
-        <v>34</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J127" t="s">
+        <v>39</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="128" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="128" spans="2:12">
       <c r="B128" s="2">
         <v>1003034</v>
       </c>
@@ -5164,22 +5560,25 @@
         <v>13</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H128" t="s">
-        <v>33</v>
-      </c>
-      <c r="I128" t="s">
-        <v>34</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J128" t="s">
+        <v>39</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="129" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="129" spans="2:12">
       <c r="B129" s="2">
         <v>1003035</v>
       </c>
@@ -5196,22 +5595,25 @@
         <v>13</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H129" t="s">
-        <v>33</v>
-      </c>
-      <c r="I129" t="s">
-        <v>34</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J129" t="s">
+        <v>39</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="130" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="130" spans="2:12">
       <c r="B130" s="2">
         <v>1003036</v>
       </c>
@@ -5228,22 +5630,25 @@
         <v>13</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H130" t="s">
-        <v>33</v>
-      </c>
-      <c r="I130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J130" t="s">
+        <v>39</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="131" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="131" spans="2:12">
       <c r="B131" s="2">
         <v>1003037</v>
       </c>
@@ -5260,22 +5665,25 @@
         <v>15</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H131" t="s">
-        <v>33</v>
-      </c>
-      <c r="I131" t="s">
-        <v>34</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J131" t="s">
+        <v>39</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="132" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="132" spans="2:12">
       <c r="B132" s="2">
         <v>1003038</v>
       </c>
@@ -5292,22 +5700,25 @@
         <v>15</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H132" t="s">
-        <v>33</v>
-      </c>
-      <c r="I132" t="s">
-        <v>34</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J132" t="s">
+        <v>39</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="133" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="133" spans="2:12">
       <c r="B133" s="2">
         <v>1003039</v>
       </c>
@@ -5324,22 +5735,25 @@
         <v>15</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H133" t="s">
-        <v>33</v>
-      </c>
-      <c r="I133" t="s">
-        <v>34</v>
-      </c>
-      <c r="J133" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J133" t="s">
+        <v>39</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="134" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="134" spans="2:12">
       <c r="B134" s="2">
         <v>1003040</v>
       </c>
@@ -5356,22 +5770,25 @@
         <v>15</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H134" t="s">
-        <v>33</v>
-      </c>
-      <c r="I134" t="s">
-        <v>34</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J134" t="s">
+        <v>39</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="135" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="135" spans="2:12">
       <c r="B135" s="2">
         <v>1003041</v>
       </c>
@@ -5388,22 +5805,25 @@
         <v>16</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H135" t="s">
-        <v>33</v>
-      </c>
-      <c r="I135" t="s">
-        <v>34</v>
-      </c>
-      <c r="J135" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J135" t="s">
+        <v>39</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="136" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="136" spans="2:12">
       <c r="B136" s="2">
         <v>1003042</v>
       </c>
@@ -5420,22 +5840,25 @@
         <v>16</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H136" t="s">
-        <v>33</v>
-      </c>
-      <c r="I136" t="s">
-        <v>34</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J136" t="s">
+        <v>39</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="137" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="137" spans="2:12">
       <c r="B137" s="2">
         <v>1003043</v>
       </c>
@@ -5452,22 +5875,25 @@
         <v>16</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H137" t="s">
-        <v>33</v>
-      </c>
-      <c r="I137" t="s">
-        <v>34</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J137" t="s">
+        <v>39</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="138" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="138" spans="2:12">
       <c r="B138" s="2">
         <v>1003044</v>
       </c>
@@ -5484,22 +5910,25 @@
         <v>16</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H138" t="s">
-        <v>33</v>
-      </c>
-      <c r="I138" t="s">
-        <v>34</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J138" t="s">
+        <v>39</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="140" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="140" spans="2:12">
       <c r="B140" s="1">
         <v>1004001</v>
       </c>
@@ -5516,22 +5945,25 @@
         <v>2</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="141" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="141" spans="2:12">
       <c r="B141" s="1">
         <v>1004002</v>
       </c>
@@ -5548,22 +5980,25 @@
         <v>2</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="142" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="142" spans="2:12">
       <c r="B142" s="1">
         <v>1004003</v>
       </c>
@@ -5580,22 +6015,25 @@
         <v>2</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="143" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="143" spans="2:12">
       <c r="B143" s="1">
         <v>1004004</v>
       </c>
@@ -5612,22 +6050,25 @@
         <v>2</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="144" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L143" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="144" spans="2:12">
       <c r="B144" s="1">
         <v>1004005</v>
       </c>
@@ -5644,22 +6085,25 @@
         <v>3</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="145" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="145" spans="2:12">
       <c r="B145" s="1">
         <v>1004006</v>
       </c>
@@ -5676,22 +6120,25 @@
         <v>3</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="146" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="146" spans="2:12">
       <c r="B146" s="1">
         <v>1004007</v>
       </c>
@@ -5708,22 +6155,25 @@
         <v>3</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="147" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="147" spans="2:12">
       <c r="B147" s="1">
         <v>1004008</v>
       </c>
@@ -5740,22 +6190,25 @@
         <v>3</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="148" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="148" spans="2:12">
       <c r="B148" s="2">
         <v>1004009</v>
       </c>
@@ -5772,22 +6225,25 @@
         <v>4</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H148" t="s">
-        <v>37</v>
-      </c>
-      <c r="I148" t="s">
-        <v>38</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" t="s">
+        <v>44</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="149" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="149" spans="2:12">
       <c r="B149" s="2">
         <v>1004010</v>
       </c>
@@ -5804,22 +6260,25 @@
         <v>4</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H149" t="s">
-        <v>37</v>
-      </c>
-      <c r="I149" t="s">
-        <v>38</v>
-      </c>
-      <c r="J149" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J149" t="s">
+        <v>44</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="150" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="150" spans="2:12">
       <c r="B150" s="2">
         <v>1004011</v>
       </c>
@@ -5836,22 +6295,25 @@
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H150" t="s">
-        <v>37</v>
-      </c>
-      <c r="I150" t="s">
-        <v>38</v>
-      </c>
-      <c r="J150" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J150" t="s">
+        <v>44</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="151" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="151" spans="2:12">
       <c r="B151" s="2">
         <v>1004012</v>
       </c>
@@ -5868,22 +6330,25 @@
         <v>4</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H151" t="s">
-        <v>37</v>
-      </c>
-      <c r="I151" t="s">
-        <v>38</v>
-      </c>
-      <c r="J151" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J151" t="s">
+        <v>44</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="152" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="152" spans="2:12">
       <c r="B152" s="2">
         <v>1004013</v>
       </c>
@@ -5900,22 +6365,25 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H152" t="s">
-        <v>37</v>
-      </c>
-      <c r="I152" t="s">
-        <v>38</v>
-      </c>
-      <c r="J152" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J152" t="s">
+        <v>44</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="153" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="153" spans="2:12">
       <c r="B153" s="2">
         <v>1004014</v>
       </c>
@@ -5932,22 +6400,25 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H153" t="s">
-        <v>37</v>
-      </c>
-      <c r="I153" t="s">
-        <v>38</v>
-      </c>
-      <c r="J153" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J153" t="s">
+        <v>44</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="154" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="154" spans="2:12">
       <c r="B154" s="2">
         <v>1004015</v>
       </c>
@@ -5964,22 +6435,25 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H154" t="s">
-        <v>37</v>
-      </c>
-      <c r="I154" t="s">
-        <v>38</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" t="s">
+        <v>44</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="155" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L154" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="155" spans="2:12">
       <c r="B155" s="2">
         <v>1004016</v>
       </c>
@@ -5996,22 +6470,25 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H155" t="s">
-        <v>37</v>
-      </c>
-      <c r="I155" t="s">
-        <v>38</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J155" t="s">
+        <v>44</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="156" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L155" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="156" spans="2:12">
       <c r="B156" s="2">
         <v>1004017</v>
       </c>
@@ -6028,22 +6505,25 @@
         <v>6</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H156" t="s">
-        <v>37</v>
-      </c>
-      <c r="I156" t="s">
-        <v>38</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J156" t="s">
+        <v>44</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="157" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L156" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="157" spans="2:12">
       <c r="B157" s="2">
         <v>1004018</v>
       </c>
@@ -6060,22 +6540,25 @@
         <v>6</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H157" t="s">
-        <v>37</v>
-      </c>
-      <c r="I157" t="s">
-        <v>38</v>
-      </c>
-      <c r="J157" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J157" t="s">
+        <v>44</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="158" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L157" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="158" spans="2:12">
       <c r="B158" s="2">
         <v>1004019</v>
       </c>
@@ -6092,22 +6575,25 @@
         <v>6</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H158" t="s">
-        <v>37</v>
-      </c>
-      <c r="I158" t="s">
-        <v>38</v>
-      </c>
-      <c r="J158" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J158" t="s">
+        <v>44</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="159" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L158" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="159" spans="2:12">
       <c r="B159" s="2">
         <v>1004020</v>
       </c>
@@ -6124,22 +6610,25 @@
         <v>6</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H159" t="s">
-        <v>37</v>
-      </c>
-      <c r="I159" t="s">
-        <v>38</v>
-      </c>
-      <c r="J159" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J159" t="s">
+        <v>44</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="160" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L159" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="160" spans="2:12">
       <c r="B160" s="2">
         <v>1004021</v>
       </c>
@@ -6156,22 +6645,25 @@
         <v>7</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H160" t="s">
-        <v>37</v>
-      </c>
-      <c r="I160" t="s">
-        <v>38</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" t="s">
+        <v>44</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="161" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L160" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="161" spans="2:12">
       <c r="B161" s="2">
         <v>1004022</v>
       </c>
@@ -6188,22 +6680,25 @@
         <v>7</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H161" t="s">
-        <v>37</v>
-      </c>
-      <c r="I161" t="s">
-        <v>38</v>
-      </c>
-      <c r="J161" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J161" t="s">
+        <v>44</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="162" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L161" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="162" spans="2:12">
       <c r="B162" s="2">
         <v>1004023</v>
       </c>
@@ -6220,22 +6715,25 @@
         <v>7</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H162" t="s">
-        <v>37</v>
-      </c>
-      <c r="I162" t="s">
-        <v>38</v>
-      </c>
-      <c r="J162" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J162" t="s">
+        <v>44</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="163" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L162" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="163" spans="2:12">
       <c r="B163" s="2">
         <v>1004024</v>
       </c>
@@ -6252,22 +6750,25 @@
         <v>7</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H163" t="s">
-        <v>37</v>
-      </c>
-      <c r="I163" t="s">
-        <v>38</v>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J163" t="s">
+        <v>44</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="164" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="164" spans="2:12">
       <c r="B164" s="2">
         <v>1004025</v>
       </c>
@@ -6284,22 +6785,25 @@
         <v>8</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H164" t="s">
-        <v>37</v>
-      </c>
-      <c r="I164" t="s">
-        <v>38</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J164" t="s">
+        <v>44</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="165" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L164" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="165" spans="2:12">
       <c r="B165" s="2">
         <v>1004026</v>
       </c>
@@ -6316,22 +6820,25 @@
         <v>8</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H165" t="s">
-        <v>37</v>
-      </c>
-      <c r="I165" t="s">
-        <v>38</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J165" t="s">
+        <v>44</v>
       </c>
       <c r="K165" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="166" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L165" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="166" spans="2:12">
       <c r="B166" s="2">
         <v>1004027</v>
       </c>
@@ -6348,22 +6855,25 @@
         <v>8</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H166" t="s">
-        <v>37</v>
-      </c>
-      <c r="I166" t="s">
-        <v>38</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J166" t="s">
+        <v>44</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="167" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L166" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="167" spans="2:12">
       <c r="B167" s="2">
         <v>1004028</v>
       </c>
@@ -6380,22 +6890,25 @@
         <v>8</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H167" t="s">
-        <v>37</v>
-      </c>
-      <c r="I167" t="s">
-        <v>38</v>
-      </c>
-      <c r="J167" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J167" t="s">
+        <v>44</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="168" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L167" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="168" spans="2:12">
       <c r="B168" s="2">
         <v>1004029</v>
       </c>
@@ -6412,22 +6925,25 @@
         <v>9</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H168" t="s">
-        <v>37</v>
-      </c>
-      <c r="I168" t="s">
-        <v>38</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J168" t="s">
+        <v>44</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="169" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L168" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="169" spans="2:12">
       <c r="B169" s="2">
         <v>1004030</v>
       </c>
@@ -6444,22 +6960,25 @@
         <v>9</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H169" t="s">
-        <v>37</v>
-      </c>
-      <c r="I169" t="s">
-        <v>38</v>
-      </c>
-      <c r="J169" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J169" t="s">
+        <v>44</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="170" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L169" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="170" spans="2:12">
       <c r="B170" s="2">
         <v>1004031</v>
       </c>
@@ -6476,22 +6995,25 @@
         <v>9</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H170" t="s">
-        <v>37</v>
-      </c>
-      <c r="I170" t="s">
-        <v>38</v>
-      </c>
-      <c r="J170" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J170" t="s">
+        <v>44</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="171" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L170" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="171" spans="2:12">
       <c r="B171" s="2">
         <v>1004032</v>
       </c>
@@ -6508,22 +7030,25 @@
         <v>9</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H171" t="s">
-        <v>37</v>
-      </c>
-      <c r="I171" t="s">
-        <v>38</v>
-      </c>
-      <c r="J171" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J171" t="s">
+        <v>44</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="172" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L171" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="172" spans="2:12">
       <c r="B172" s="2">
         <v>1004033</v>
       </c>
@@ -6540,22 +7065,25 @@
         <v>10</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H172" t="s">
-        <v>37</v>
-      </c>
-      <c r="I172" t="s">
-        <v>38</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J172" t="s">
+        <v>44</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="173" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L172" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="173" spans="2:12">
       <c r="B173" s="2">
         <v>1004034</v>
       </c>
@@ -6572,22 +7100,25 @@
         <v>10</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H173" t="s">
-        <v>37</v>
-      </c>
-      <c r="I173" t="s">
-        <v>38</v>
-      </c>
-      <c r="J173" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J173" t="s">
+        <v>44</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="174" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L173" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="174" spans="2:12">
       <c r="B174" s="2">
         <v>1004035</v>
       </c>
@@ -6604,22 +7135,25 @@
         <v>10</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H174" t="s">
-        <v>37</v>
-      </c>
-      <c r="I174" t="s">
-        <v>38</v>
-      </c>
-      <c r="J174" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J174" t="s">
+        <v>44</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="175" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L174" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="175" spans="2:12">
       <c r="B175" s="2">
         <v>1004036</v>
       </c>
@@ -6636,22 +7170,25 @@
         <v>10</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H175" t="s">
-        <v>37</v>
-      </c>
-      <c r="I175" t="s">
-        <v>38</v>
-      </c>
-      <c r="J175" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J175" t="s">
+        <v>44</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="176" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L175" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="176" spans="2:12">
       <c r="B176" s="2">
         <v>1004037</v>
       </c>
@@ -6668,22 +7205,25 @@
         <v>11</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H176" t="s">
-        <v>37</v>
-      </c>
-      <c r="I176" t="s">
-        <v>38</v>
-      </c>
-      <c r="J176" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J176" t="s">
+        <v>44</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="177" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L176" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="177" spans="2:12">
       <c r="B177" s="2">
         <v>1004038</v>
       </c>
@@ -6700,22 +7240,25 @@
         <v>11</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H177" t="s">
-        <v>37</v>
-      </c>
-      <c r="I177" t="s">
-        <v>38</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J177" t="s">
+        <v>44</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="178" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L177" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="2:12">
       <c r="B178" s="2">
         <v>1004039</v>
       </c>
@@ -6732,22 +7275,25 @@
         <v>11</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H178" t="s">
-        <v>37</v>
-      </c>
-      <c r="I178" t="s">
-        <v>38</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J178" t="s">
+        <v>44</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="179" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L178" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="179" spans="2:12">
       <c r="B179" s="2">
         <v>1004040</v>
       </c>
@@ -6764,22 +7310,25 @@
         <v>11</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H179" t="s">
-        <v>37</v>
-      </c>
-      <c r="I179" t="s">
-        <v>38</v>
-      </c>
-      <c r="J179" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J179" t="s">
+        <v>44</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="180" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L179" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="180" spans="2:12">
       <c r="B180" s="2">
         <v>1004041</v>
       </c>
@@ -6796,22 +7345,25 @@
         <v>12</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H180" t="s">
-        <v>37</v>
-      </c>
-      <c r="I180" t="s">
-        <v>38</v>
-      </c>
-      <c r="J180" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J180" t="s">
+        <v>44</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="181" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L180" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="181" spans="2:12">
       <c r="B181" s="2">
         <v>1004042</v>
       </c>
@@ -6828,22 +7380,25 @@
         <v>12</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H181" t="s">
-        <v>37</v>
-      </c>
-      <c r="I181" t="s">
-        <v>38</v>
-      </c>
-      <c r="J181" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J181" t="s">
+        <v>44</v>
       </c>
       <c r="K181" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="182" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L181" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="182" spans="2:12">
       <c r="B182" s="2">
         <v>1004043</v>
       </c>
@@ -6860,22 +7415,25 @@
         <v>12</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H182" t="s">
-        <v>37</v>
-      </c>
-      <c r="I182" t="s">
-        <v>38</v>
-      </c>
-      <c r="J182" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J182" t="s">
+        <v>44</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="183" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L182" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="183" spans="2:12">
       <c r="B183" s="2">
         <v>1004044</v>
       </c>
@@ -6892,22 +7450,25 @@
         <v>12</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H183" t="s">
-        <v>37</v>
-      </c>
-      <c r="I183" t="s">
-        <v>38</v>
-      </c>
-      <c r="J183" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J183" t="s">
+        <v>44</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="185" spans="2:11">
+        <v>40</v>
+      </c>
+      <c r="L183" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="185" spans="2:12">
       <c r="B185" s="1">
         <v>1005001</v>
       </c>
@@ -6924,22 +7485,25 @@
         <v>1</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K185" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="186" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L185" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="186" spans="2:12">
       <c r="B186" s="1">
         <v>1005002</v>
       </c>
@@ -6956,22 +7520,25 @@
         <v>1</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K186" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="187" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L186" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="187" spans="2:12">
       <c r="B187" s="1">
         <v>1005003</v>
       </c>
@@ -6988,22 +7555,25 @@
         <v>1</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K187" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="188" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L187" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="188" spans="2:12">
       <c r="B188" s="1">
         <v>1005004</v>
       </c>
@@ -7020,22 +7590,25 @@
         <v>1</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K188" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="189" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L188" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="189" spans="2:12">
       <c r="B189" s="1">
         <v>1005005</v>
       </c>
@@ -7052,22 +7625,25 @@
         <v>2</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K189" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="190" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L189" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="190" spans="2:12">
       <c r="B190" s="1">
         <v>1005006</v>
       </c>
@@ -7084,22 +7660,25 @@
         <v>2</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="191" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L190" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="191" spans="2:12">
       <c r="B191" s="1">
         <v>1005007</v>
       </c>
@@ -7116,22 +7695,25 @@
         <v>2</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="192" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L191" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="192" spans="2:12">
       <c r="B192" s="1">
         <v>1005008</v>
       </c>
@@ -7148,22 +7730,25 @@
         <v>2</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="193" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L192" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="193" spans="2:12">
       <c r="B193" s="2">
         <v>1005009</v>
       </c>
@@ -7180,22 +7765,25 @@
         <v>3</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H193" t="s">
-        <v>39</v>
-      </c>
-      <c r="I193" t="s">
-        <v>40</v>
-      </c>
-      <c r="J193" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J193" t="s">
+        <v>47</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="194" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L193" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="194" spans="2:12">
       <c r="B194" s="2">
         <v>1005010</v>
       </c>
@@ -7212,22 +7800,25 @@
         <v>3</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H194" t="s">
-        <v>39</v>
-      </c>
-      <c r="I194" t="s">
-        <v>40</v>
-      </c>
-      <c r="J194" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J194" t="s">
+        <v>47</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="195" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L194" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="195" spans="2:12">
       <c r="B195" s="2">
         <v>1005011</v>
       </c>
@@ -7244,22 +7835,25 @@
         <v>3</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H195" t="s">
-        <v>39</v>
-      </c>
-      <c r="I195" t="s">
-        <v>40</v>
-      </c>
-      <c r="J195" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J195" t="s">
+        <v>47</v>
       </c>
       <c r="K195" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="196" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L195" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="196" spans="2:12">
       <c r="B196" s="2">
         <v>1005012</v>
       </c>
@@ -7276,22 +7870,25 @@
         <v>3</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H196" t="s">
-        <v>39</v>
-      </c>
-      <c r="I196" t="s">
-        <v>40</v>
-      </c>
-      <c r="J196" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J196" t="s">
+        <v>47</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="197" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L196" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="197" spans="2:12">
       <c r="B197" s="2">
         <v>1005013</v>
       </c>
@@ -7308,22 +7905,25 @@
         <v>3</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H197" t="s">
-        <v>39</v>
-      </c>
-      <c r="I197" t="s">
-        <v>40</v>
-      </c>
-      <c r="J197" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J197" t="s">
+        <v>47</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="198" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L197" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="198" spans="2:12">
       <c r="B198" s="2">
         <v>1005014</v>
       </c>
@@ -7340,22 +7940,25 @@
         <v>3</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H198" t="s">
-        <v>39</v>
-      </c>
-      <c r="I198" t="s">
-        <v>40</v>
-      </c>
-      <c r="J198" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J198" t="s">
+        <v>47</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="199" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L198" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="199" spans="2:12">
       <c r="B199" s="2">
         <v>1005015</v>
       </c>
@@ -7372,22 +7975,25 @@
         <v>3</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H199" t="s">
-        <v>39</v>
-      </c>
-      <c r="I199" t="s">
-        <v>40</v>
-      </c>
-      <c r="J199" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J199" t="s">
+        <v>47</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="200" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L199" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="200" spans="2:12">
       <c r="B200" s="2">
         <v>1005016</v>
       </c>
@@ -7404,22 +8010,25 @@
         <v>3</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H200" t="s">
-        <v>39</v>
-      </c>
-      <c r="I200" t="s">
-        <v>40</v>
-      </c>
-      <c r="J200" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J200" t="s">
+        <v>47</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="201" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L200" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="201" spans="2:12">
       <c r="B201" s="2">
         <v>1005017</v>
       </c>
@@ -7436,22 +8045,25 @@
         <v>4</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H201" t="s">
-        <v>39</v>
-      </c>
-      <c r="I201" t="s">
-        <v>40</v>
-      </c>
-      <c r="J201" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J201" t="s">
+        <v>47</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="202" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L201" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="202" spans="2:12">
       <c r="B202" s="2">
         <v>1005018</v>
       </c>
@@ -7468,22 +8080,25 @@
         <v>4</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H202" t="s">
-        <v>39</v>
-      </c>
-      <c r="I202" t="s">
-        <v>40</v>
-      </c>
-      <c r="J202" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I202" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J202" t="s">
+        <v>47</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="203" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L202" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="203" spans="2:12">
       <c r="B203" s="2">
         <v>1005019</v>
       </c>
@@ -7500,22 +8115,25 @@
         <v>4</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H203" t="s">
-        <v>39</v>
-      </c>
-      <c r="I203" t="s">
-        <v>40</v>
-      </c>
-      <c r="J203" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J203" t="s">
+        <v>47</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="204" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L203" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="204" spans="2:12">
       <c r="B204" s="2">
         <v>1005020</v>
       </c>
@@ -7532,22 +8150,25 @@
         <v>4</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H204" t="s">
-        <v>39</v>
-      </c>
-      <c r="I204" t="s">
-        <v>40</v>
-      </c>
-      <c r="J204" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J204" t="s">
+        <v>47</v>
       </c>
       <c r="K204" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="205" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L204" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="205" spans="2:12">
       <c r="B205" s="2">
         <v>1005021</v>
       </c>
@@ -7564,22 +8185,25 @@
         <v>5</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H205" t="s">
-        <v>39</v>
-      </c>
-      <c r="I205" t="s">
-        <v>40</v>
-      </c>
-      <c r="J205" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J205" t="s">
+        <v>47</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="206" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L205" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="206" spans="2:12">
       <c r="B206" s="2">
         <v>1005022</v>
       </c>
@@ -7596,22 +8220,25 @@
         <v>5</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H206" t="s">
-        <v>39</v>
-      </c>
-      <c r="I206" t="s">
-        <v>40</v>
-      </c>
-      <c r="J206" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J206" t="s">
+        <v>47</v>
       </c>
       <c r="K206" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="207" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L206" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="207" spans="2:12">
       <c r="B207" s="2">
         <v>1005023</v>
       </c>
@@ -7628,22 +8255,25 @@
         <v>5</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H207" t="s">
-        <v>39</v>
-      </c>
-      <c r="I207" t="s">
-        <v>40</v>
-      </c>
-      <c r="J207" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J207" t="s">
+        <v>47</v>
       </c>
       <c r="K207" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="208" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L207" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="208" spans="2:12">
       <c r="B208" s="2">
         <v>1005024</v>
       </c>
@@ -7660,22 +8290,25 @@
         <v>5</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H208" t="s">
-        <v>39</v>
-      </c>
-      <c r="I208" t="s">
-        <v>40</v>
-      </c>
-      <c r="J208" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J208" t="s">
+        <v>47</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="209" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L208" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="209" spans="2:12">
       <c r="B209" s="2">
         <v>1005025</v>
       </c>
@@ -7692,22 +8325,25 @@
         <v>5</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H209" t="s">
-        <v>39</v>
-      </c>
-      <c r="I209" t="s">
-        <v>40</v>
-      </c>
-      <c r="J209" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J209" t="s">
+        <v>47</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="210" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L209" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="210" spans="2:12">
       <c r="B210" s="2">
         <v>1005026</v>
       </c>
@@ -7724,22 +8360,25 @@
         <v>5</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H210" t="s">
-        <v>39</v>
-      </c>
-      <c r="I210" t="s">
-        <v>40</v>
-      </c>
-      <c r="J210" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J210" t="s">
+        <v>47</v>
       </c>
       <c r="K210" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="211" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L210" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="211" spans="2:12">
       <c r="B211" s="2">
         <v>1005027</v>
       </c>
@@ -7756,22 +8395,25 @@
         <v>5</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H211" t="s">
-        <v>39</v>
-      </c>
-      <c r="I211" t="s">
-        <v>40</v>
-      </c>
-      <c r="J211" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J211" t="s">
+        <v>47</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="212" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L211" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="212" spans="2:12">
       <c r="B212" s="2">
         <v>1005028</v>
       </c>
@@ -7788,22 +8430,25 @@
         <v>5</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H212" t="s">
-        <v>39</v>
-      </c>
-      <c r="I212" t="s">
-        <v>40</v>
-      </c>
-      <c r="J212" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J212" t="s">
+        <v>47</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="213" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L212" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="213" spans="2:12">
       <c r="B213" s="2">
         <v>1005029</v>
       </c>
@@ -7820,22 +8465,25 @@
         <v>6</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H213" t="s">
-        <v>39</v>
-      </c>
-      <c r="I213" t="s">
-        <v>40</v>
-      </c>
-      <c r="J213" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J213" t="s">
+        <v>47</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="214" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L213" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="214" spans="2:12">
       <c r="B214" s="2">
         <v>1005030</v>
       </c>
@@ -7852,22 +8500,25 @@
         <v>6</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H214" t="s">
-        <v>39</v>
-      </c>
-      <c r="I214" t="s">
-        <v>40</v>
-      </c>
-      <c r="J214" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J214" t="s">
+        <v>47</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="215" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L214" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="215" spans="2:12">
       <c r="B215" s="2">
         <v>1005031</v>
       </c>
@@ -7884,22 +8535,25 @@
         <v>6</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H215" t="s">
-        <v>39</v>
-      </c>
-      <c r="I215" t="s">
-        <v>40</v>
-      </c>
-      <c r="J215" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J215" t="s">
+        <v>47</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="216" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L215" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="216" spans="2:12">
       <c r="B216" s="2">
         <v>1005032</v>
       </c>
@@ -7916,22 +8570,25 @@
         <v>6</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H216" t="s">
-        <v>39</v>
-      </c>
-      <c r="I216" t="s">
-        <v>40</v>
-      </c>
-      <c r="J216" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J216" t="s">
+        <v>47</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="217" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L216" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="217" spans="2:12">
       <c r="B217" s="2">
         <v>1005033</v>
       </c>
@@ -7948,22 +8605,25 @@
         <v>7</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H217" t="s">
-        <v>39</v>
-      </c>
-      <c r="I217" t="s">
-        <v>40</v>
-      </c>
-      <c r="J217" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J217" t="s">
+        <v>47</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="218" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L217" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="218" spans="2:12">
       <c r="B218" s="2">
         <v>1005034</v>
       </c>
@@ -7980,22 +8640,25 @@
         <v>7</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H218" t="s">
-        <v>39</v>
-      </c>
-      <c r="I218" t="s">
-        <v>40</v>
-      </c>
-      <c r="J218" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I218" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J218" t="s">
+        <v>47</v>
       </c>
       <c r="K218" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="219" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L218" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="219" spans="2:12">
       <c r="B219" s="2">
         <v>1005035</v>
       </c>
@@ -8012,22 +8675,25 @@
         <v>7</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H219" t="s">
-        <v>39</v>
-      </c>
-      <c r="I219" t="s">
-        <v>40</v>
-      </c>
-      <c r="J219" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J219" t="s">
+        <v>47</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="220" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L219" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="220" spans="2:12">
       <c r="B220" s="2">
         <v>1005036</v>
       </c>
@@ -8044,22 +8710,25 @@
         <v>7</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H220" t="s">
-        <v>39</v>
-      </c>
-      <c r="I220" t="s">
-        <v>40</v>
-      </c>
-      <c r="J220" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J220" t="s">
+        <v>47</v>
       </c>
       <c r="K220" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="221" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L220" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="221" spans="2:12">
       <c r="B221" s="2">
         <v>1005037</v>
       </c>
@@ -8076,22 +8745,25 @@
         <v>7</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H221" t="s">
-        <v>39</v>
-      </c>
-      <c r="I221" t="s">
-        <v>40</v>
-      </c>
-      <c r="J221" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J221" t="s">
+        <v>47</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="222" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L221" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="222" spans="2:12">
       <c r="B222" s="2">
         <v>1005038</v>
       </c>
@@ -8108,22 +8780,25 @@
         <v>7</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H222" t="s">
-        <v>39</v>
-      </c>
-      <c r="I222" t="s">
-        <v>40</v>
-      </c>
-      <c r="J222" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J222" t="s">
+        <v>47</v>
       </c>
       <c r="K222" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="223" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L222" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="223" spans="2:12">
       <c r="B223" s="2">
         <v>1005039</v>
       </c>
@@ -8140,22 +8815,25 @@
         <v>7</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H223" t="s">
-        <v>39</v>
-      </c>
-      <c r="I223" t="s">
-        <v>40</v>
-      </c>
-      <c r="J223" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J223" t="s">
+        <v>47</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="224" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L223" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="224" spans="2:12">
       <c r="B224" s="2">
         <v>1005040</v>
       </c>
@@ -8172,22 +8850,25 @@
         <v>7</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H224" t="s">
-        <v>39</v>
-      </c>
-      <c r="I224" t="s">
-        <v>40</v>
-      </c>
-      <c r="J224" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J224" t="s">
+        <v>47</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="225" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L224" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="225" spans="2:12">
       <c r="B225" s="2">
         <v>1005041</v>
       </c>
@@ -8204,22 +8885,25 @@
         <v>8</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H225" t="s">
-        <v>39</v>
-      </c>
-      <c r="I225" t="s">
-        <v>40</v>
-      </c>
-      <c r="J225" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J225" t="s">
+        <v>47</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="226" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L225" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="226" spans="2:12">
       <c r="B226" s="2">
         <v>1005042</v>
       </c>
@@ -8236,22 +8920,25 @@
         <v>8</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H226" t="s">
-        <v>39</v>
-      </c>
-      <c r="I226" t="s">
-        <v>40</v>
-      </c>
-      <c r="J226" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J226" t="s">
+        <v>47</v>
       </c>
       <c r="K226" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="227" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L226" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="227" spans="2:12">
       <c r="B227" s="2">
         <v>1005043</v>
       </c>
@@ -8268,22 +8955,25 @@
         <v>8</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H227" t="s">
-        <v>39</v>
-      </c>
-      <c r="I227" t="s">
-        <v>40</v>
-      </c>
-      <c r="J227" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J227" t="s">
+        <v>47</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="228" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L227" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="228" spans="2:12">
       <c r="B228" s="2">
         <v>1005044</v>
       </c>
@@ -8300,22 +8990,25 @@
         <v>8</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H228" t="s">
-        <v>39</v>
-      </c>
-      <c r="I228" t="s">
-        <v>40</v>
-      </c>
-      <c r="J228" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J228" t="s">
+        <v>47</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="230" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L228" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="230" spans="2:12">
       <c r="B230" s="1">
         <v>2001001</v>
       </c>
@@ -8332,22 +9025,25 @@
         <v>4</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K230" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="231" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L230" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="231" spans="2:12">
       <c r="B231" s="1">
         <v>2001002</v>
       </c>
@@ -8364,22 +9060,25 @@
         <v>6</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K231" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="232" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L231" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="232" spans="2:12">
       <c r="B232" s="2">
         <v>2001003</v>
       </c>
@@ -8396,22 +9095,25 @@
         <v>8</v>
       </c>
       <c r="G232" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H232" t="s">
-        <v>44</v>
-      </c>
-      <c r="I232" t="s">
-        <v>45</v>
-      </c>
-      <c r="J232" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J232" t="s">
+        <v>53</v>
       </c>
       <c r="K232" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="233" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L232" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="233" spans="2:12">
       <c r="B233" s="2">
         <v>2001004</v>
       </c>
@@ -8428,22 +9130,25 @@
         <v>10</v>
       </c>
       <c r="G233" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H233" t="s">
-        <v>44</v>
-      </c>
-      <c r="I233" t="s">
-        <v>45</v>
-      </c>
-      <c r="J233" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J233" t="s">
+        <v>53</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="234" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L233" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="234" spans="2:12">
       <c r="B234" s="2">
         <v>2001005</v>
       </c>
@@ -8460,22 +9165,25 @@
         <v>12</v>
       </c>
       <c r="G234" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H234" t="s">
-        <v>44</v>
-      </c>
-      <c r="I234" t="s">
-        <v>45</v>
-      </c>
-      <c r="J234" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J234" t="s">
+        <v>53</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="235" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L234" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="235" spans="2:12">
       <c r="B235" s="2">
         <v>2001006</v>
       </c>
@@ -8492,22 +9200,25 @@
         <v>14</v>
       </c>
       <c r="G235" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H235" t="s">
-        <v>44</v>
-      </c>
-      <c r="I235" t="s">
-        <v>45</v>
-      </c>
-      <c r="J235" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J235" t="s">
+        <v>53</v>
       </c>
       <c r="K235" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="236" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L235" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="236" spans="2:12">
       <c r="B236" s="2">
         <v>2001007</v>
       </c>
@@ -8524,22 +9235,25 @@
         <v>16</v>
       </c>
       <c r="G236" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H236" t="s">
-        <v>44</v>
-      </c>
-      <c r="I236" t="s">
-        <v>45</v>
-      </c>
-      <c r="J236" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J236" t="s">
+        <v>53</v>
       </c>
       <c r="K236" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="237" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L236" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="237" spans="2:12">
       <c r="B237" s="2">
         <v>2001008</v>
       </c>
@@ -8556,22 +9270,25 @@
         <v>18</v>
       </c>
       <c r="G237" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H237" t="s">
-        <v>44</v>
-      </c>
-      <c r="I237" t="s">
-        <v>45</v>
-      </c>
-      <c r="J237" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J237" t="s">
+        <v>53</v>
       </c>
       <c r="K237" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="238" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L237" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="238" spans="2:12">
       <c r="B238" s="2">
         <v>2001009</v>
       </c>
@@ -8588,22 +9305,25 @@
         <v>20</v>
       </c>
       <c r="G238" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H238" t="s">
-        <v>44</v>
-      </c>
-      <c r="I238" t="s">
-        <v>45</v>
-      </c>
-      <c r="J238" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J238" t="s">
+        <v>53</v>
       </c>
       <c r="K238" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="239" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L238" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="239" spans="2:12">
       <c r="B239" s="2">
         <v>2001010</v>
       </c>
@@ -8620,22 +9340,25 @@
         <v>22</v>
       </c>
       <c r="G239" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H239" t="s">
-        <v>44</v>
-      </c>
-      <c r="I239" t="s">
-        <v>45</v>
-      </c>
-      <c r="J239" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J239" t="s">
+        <v>53</v>
       </c>
       <c r="K239" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="240" spans="2:11">
+        <v>48</v>
+      </c>
+      <c r="L239" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="240" spans="2:12">
       <c r="B240" s="2">
         <v>2001011</v>
       </c>
@@ -8652,152 +9375,155 @@
         <v>24</v>
       </c>
       <c r="G240" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H240" t="s">
-        <v>44</v>
-      </c>
-      <c r="I240" t="s">
-        <v>45</v>
-      </c>
-      <c r="J240" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J240" t="s">
+        <v>53</v>
       </c>
       <c r="K240" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="241" spans="10:11">
-      <c r="J241"/>
+        <v>48</v>
+      </c>
+      <c r="L240" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="241" spans="11:12">
       <c r="K241"/>
-    </row>
-    <row r="242" spans="10:11">
-      <c r="J242"/>
+      <c r="L241"/>
+    </row>
+    <row r="242" spans="11:12">
       <c r="K242"/>
-    </row>
-    <row r="243" spans="10:11">
-      <c r="J243"/>
+      <c r="L242"/>
+    </row>
+    <row r="243" spans="11:12">
       <c r="K243"/>
-    </row>
-    <row r="244" spans="10:11">
-      <c r="J244"/>
+      <c r="L243"/>
+    </row>
+    <row r="244" spans="11:12">
       <c r="K244"/>
-    </row>
-    <row r="245" spans="10:11">
-      <c r="J245"/>
+      <c r="L244"/>
+    </row>
+    <row r="245" spans="11:12">
       <c r="K245"/>
-    </row>
-    <row r="246" spans="10:11">
-      <c r="J246"/>
+      <c r="L245"/>
+    </row>
+    <row r="246" spans="11:12">
       <c r="K246"/>
-    </row>
-    <row r="247" spans="10:11">
-      <c r="J247"/>
+      <c r="L246"/>
+    </row>
+    <row r="247" spans="11:12">
       <c r="K247"/>
-    </row>
-    <row r="248" spans="10:11">
-      <c r="J248"/>
+      <c r="L247"/>
+    </row>
+    <row r="248" spans="11:12">
       <c r="K248"/>
-    </row>
-    <row r="249" spans="10:11">
-      <c r="J249"/>
+      <c r="L248"/>
+    </row>
+    <row r="249" spans="11:12">
       <c r="K249"/>
-    </row>
-    <row r="250" spans="10:11">
-      <c r="J250"/>
+      <c r="L249"/>
+    </row>
+    <row r="250" spans="11:12">
       <c r="K250"/>
-    </row>
-    <row r="251" spans="10:11">
-      <c r="J251"/>
+      <c r="L250"/>
+    </row>
+    <row r="251" spans="11:12">
       <c r="K251"/>
-    </row>
-    <row r="252" spans="10:11">
-      <c r="J252"/>
+      <c r="L251"/>
+    </row>
+    <row r="252" spans="11:12">
       <c r="K252"/>
-    </row>
-    <row r="253" spans="10:11">
-      <c r="J253"/>
+      <c r="L252"/>
+    </row>
+    <row r="253" spans="11:12">
       <c r="K253"/>
-    </row>
-    <row r="254" spans="10:11">
-      <c r="J254"/>
+      <c r="L253"/>
+    </row>
+    <row r="254" spans="11:12">
       <c r="K254"/>
-    </row>
-    <row r="255" spans="10:11">
-      <c r="J255"/>
+      <c r="L254"/>
+    </row>
+    <row r="255" spans="11:12">
       <c r="K255"/>
-    </row>
-    <row r="256" spans="10:11">
-      <c r="J256"/>
+      <c r="L255"/>
+    </row>
+    <row r="256" spans="11:12">
       <c r="K256"/>
-    </row>
-    <row r="257" spans="10:11">
-      <c r="J257"/>
+      <c r="L256"/>
+    </row>
+    <row r="257" spans="11:12">
       <c r="K257"/>
-    </row>
-    <row r="258" spans="10:11">
-      <c r="J258"/>
+      <c r="L257"/>
+    </row>
+    <row r="258" spans="11:12">
       <c r="K258"/>
-    </row>
-    <row r="259" spans="10:11">
-      <c r="J259"/>
+      <c r="L258"/>
+    </row>
+    <row r="259" spans="11:12">
       <c r="K259"/>
-    </row>
-    <row r="260" spans="10:11">
-      <c r="J260"/>
+      <c r="L259"/>
+    </row>
+    <row r="260" spans="11:12">
       <c r="K260"/>
-    </row>
-    <row r="261" spans="10:11">
-      <c r="J261"/>
+      <c r="L260"/>
+    </row>
+    <row r="261" spans="11:12">
       <c r="K261"/>
-    </row>
-    <row r="262" spans="10:11">
-      <c r="J262"/>
+      <c r="L261"/>
+    </row>
+    <row r="262" spans="11:12">
       <c r="K262"/>
-    </row>
-    <row r="263" spans="10:11">
-      <c r="J263"/>
+      <c r="L262"/>
+    </row>
+    <row r="263" spans="11:12">
       <c r="K263"/>
-    </row>
-    <row r="264" spans="10:11">
-      <c r="J264"/>
+      <c r="L263"/>
+    </row>
+    <row r="264" spans="11:12">
       <c r="K264"/>
-    </row>
-    <row r="265" spans="10:11">
-      <c r="J265"/>
+      <c r="L264"/>
+    </row>
+    <row r="265" spans="11:12">
       <c r="K265"/>
-    </row>
-    <row r="266" spans="10:11">
-      <c r="J266"/>
+      <c r="L265"/>
+    </row>
+    <row r="266" spans="11:12">
       <c r="K266"/>
-    </row>
-    <row r="267" spans="10:11">
-      <c r="J267"/>
+      <c r="L266"/>
+    </row>
+    <row r="267" spans="11:12">
       <c r="K267"/>
-    </row>
-    <row r="268" spans="10:11">
-      <c r="J268"/>
+      <c r="L267"/>
+    </row>
+    <row r="268" spans="11:12">
       <c r="K268"/>
-    </row>
-    <row r="269" spans="10:11">
-      <c r="J269"/>
+      <c r="L268"/>
+    </row>
+    <row r="269" spans="11:12">
       <c r="K269"/>
-    </row>
-    <row r="270" spans="10:11">
-      <c r="J270"/>
+      <c r="L269"/>
+    </row>
+    <row r="270" spans="11:12">
       <c r="K270"/>
-    </row>
-    <row r="271" spans="10:11">
-      <c r="J271"/>
+      <c r="L270"/>
+    </row>
+    <row r="271" spans="11:12">
       <c r="K271"/>
-    </row>
-    <row r="272" spans="10:11">
-      <c r="J272"/>
+      <c r="L271"/>
+    </row>
+    <row r="272" spans="11:12">
       <c r="K272"/>
-    </row>
-    <row r="273" spans="10:11">
-      <c r="J273"/>
+      <c r="L272"/>
+    </row>
+    <row r="273" spans="11:12">
       <c r="K273"/>
+      <c r="L273"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1008</v>
+        <v>330</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2513</v>
+        <v>440</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>528</v>
+        <v>498</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>19</v>
@@ -1556,7 +1556,7 @@
         <v>7</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1287</v>
+        <v>1148</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>19</v>
@@ -1697,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>609</v>
+        <v>576</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>20</v>
@@ -1744,7 +1744,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1614</v>
+        <v>1451</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>20</v>
@@ -1885,7 +1885,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>704</v>
+        <v>667</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>21</v>
@@ -1932,7 +1932,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1994</v>
+        <v>1804</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>21</v>
@@ -2073,7 +2073,7 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>807</v>
+        <v>767</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>21</v>
@@ -2120,7 +2120,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2447</v>
+        <v>2227</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>21</v>
@@ -2261,7 +2261,7 @@
         <v>22</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>913</v>
+        <v>870</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>22</v>
@@ -2308,7 +2308,7 @@
         <v>23</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2966</v>
+        <v>2713</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>22</v>
@@ -2449,7 +2449,7 @@
         <v>26</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1035</v>
+        <v>988</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>23</v>
@@ -2496,7 +2496,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>3569</v>
+        <v>3282</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>23</v>
@@ -2637,7 +2637,7 @@
         <v>30</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1159</v>
+        <v>1108</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>23</v>
@@ -2825,7 +2825,7 @@
         <v>34</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1302</v>
+        <v>1246</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>24</v>
@@ -3013,7 +3013,7 @@
         <v>38</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1445</v>
+        <v>1385</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>25</v>
@@ -3201,7 +3201,7 @@
         <v>42</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1620</v>
+        <v>1555</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>25</v>
@@ -3343,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         <v>2</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>409</v>
+        <v>200</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
@@ -3437,10 +3437,10 @@
         <v>3</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>916</v>
+        <v>300</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
@@ -3484,10 +3484,10 @@
         <v>4</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>2285</v>
+        <v>400</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>6</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>29</v>
@@ -3625,7 +3625,7 @@
         <v>7</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>1170</v>
+        <v>1044</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>29</v>
@@ -3766,7 +3766,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>30</v>
@@ -3813,7 +3813,7 @@
         <v>11</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1467</v>
+        <v>1319</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>30</v>
@@ -3954,7 +3954,7 @@
         <v>14</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>640</v>
+        <v>607</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>31</v>
@@ -4001,7 +4001,7 @@
         <v>15</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1813</v>
+        <v>1640</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>31</v>
@@ -4142,7 +4142,7 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>734</v>
+        <v>698</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>32</v>
@@ -4189,7 +4189,7 @@
         <v>19</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>2225</v>
+        <v>2025</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>32</v>
@@ -4330,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>830</v>
+        <v>790</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>33</v>
@@ -4377,7 +4377,7 @@
         <v>23</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>2696</v>
+        <v>2466</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>33</v>
@@ -4518,7 +4518,7 @@
         <v>26</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>941</v>
+        <v>898</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>34</v>
@@ -4565,7 +4565,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>3244</v>
+        <v>2984</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>34</v>
@@ -4706,7 +4706,7 @@
         <v>30</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1054</v>
+        <v>1007</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>35</v>
@@ -4894,7 +4894,7 @@
         <v>34</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1183</v>
+        <v>1133</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>36</v>
@@ -5082,7 +5082,7 @@
         <v>38</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>1314</v>
+        <v>1259</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>37</v>
@@ -5270,7 +5270,7 @@
         <v>42</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1473</v>
+        <v>1414</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>38</v>
@@ -5412,10 +5412,10 @@
         <v>1</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
@@ -5459,10 +5459,10 @@
         <v>2</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>393</v>
+        <v>192</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
@@ -5506,10 +5506,10 @@
         <v>3</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>880</v>
+        <v>288</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
@@ -5553,10 +5553,10 @@
         <v>4</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>2193</v>
+        <v>384</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>6</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="F100" s="1" t="n">
         <v>39</v>
@@ -5694,7 +5694,7 @@
         <v>7</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>1123</v>
+        <v>1002</v>
       </c>
       <c r="F101" s="1" t="n">
         <v>39</v>
@@ -5835,7 +5835,7 @@
         <v>10</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>40</v>
@@ -5882,7 +5882,7 @@
         <v>11</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>1409</v>
+        <v>1266</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>40</v>
@@ -6023,7 +6023,7 @@
         <v>14</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>614</v>
+        <v>582</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>41</v>
@@ -6070,7 +6070,7 @@
         <v>15</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>1740</v>
+        <v>1574</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>41</v>
@@ -6211,7 +6211,7 @@
         <v>18</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>705</v>
+        <v>670</v>
       </c>
       <c r="F112" s="2" t="n">
         <v>43</v>
@@ -6258,7 +6258,7 @@
         <v>19</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>2136</v>
+        <v>1944</v>
       </c>
       <c r="F113" s="2" t="n">
         <v>43</v>
@@ -6399,7 +6399,7 @@
         <v>22</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>797</v>
+        <v>759</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>44</v>
@@ -6446,7 +6446,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>2588</v>
+        <v>2368</v>
       </c>
       <c r="F117" s="2" t="n">
         <v>44</v>
@@ -6587,7 +6587,7 @@
         <v>26</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>904</v>
+        <v>862</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>45</v>
@@ -6634,7 +6634,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>3115</v>
+        <v>2865</v>
       </c>
       <c r="F121" s="2" t="n">
         <v>45</v>
@@ -6775,7 +6775,7 @@
         <v>30</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>1012</v>
+        <v>967</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>47</v>
@@ -6963,7 +6963,7 @@
         <v>34</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>1136</v>
+        <v>1087</v>
       </c>
       <c r="F128" s="2" t="n">
         <v>48</v>
@@ -7151,7 +7151,7 @@
         <v>38</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>1261</v>
+        <v>1209</v>
       </c>
       <c r="F132" s="2" t="n">
         <v>49</v>
@@ -7339,7 +7339,7 @@
         <v>42</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>1414</v>
+        <v>1357</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>51</v>
@@ -7481,10 +7481,10 @@
         <v>1</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="F140" s="1" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
@@ -7528,10 +7528,10 @@
         <v>2</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>344</v>
+        <v>168</v>
       </c>
       <c r="F141" s="1" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
@@ -7575,10 +7575,10 @@
         <v>3</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>770</v>
+        <v>252</v>
       </c>
       <c r="F142" s="1" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
@@ -7622,10 +7622,10 @@
         <v>4</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>1919</v>
+        <v>336</v>
       </c>
       <c r="F143" s="1" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>6</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="F145" s="1" t="n">
         <v>29</v>
@@ -7763,7 +7763,7 @@
         <v>7</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>983</v>
+        <v>877</v>
       </c>
       <c r="F146" s="1" t="n">
         <v>29</v>
@@ -7904,7 +7904,7 @@
         <v>10</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>30</v>
@@ -7951,7 +7951,7 @@
         <v>11</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>1232</v>
+        <v>1108</v>
       </c>
       <c r="F150" s="2" t="n">
         <v>30</v>
@@ -8092,7 +8092,7 @@
         <v>14</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>537</v>
+        <v>510</v>
       </c>
       <c r="F153" s="2" t="n">
         <v>31</v>
@@ -8139,7 +8139,7 @@
         <v>15</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>1523</v>
+        <v>1378</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>31</v>
@@ -8280,7 +8280,7 @@
         <v>18</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>32</v>
@@ -8327,7 +8327,7 @@
         <v>19</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>1869</v>
+        <v>1701</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>32</v>
@@ -8468,7 +8468,7 @@
         <v>22</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>697</v>
+        <v>664</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>33</v>
@@ -8515,7 +8515,7 @@
         <v>23</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>2265</v>
+        <v>2072</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>33</v>
@@ -8656,7 +8656,7 @@
         <v>26</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>791</v>
+        <v>754</v>
       </c>
       <c r="F165" s="2" t="n">
         <v>34</v>
@@ -8703,7 +8703,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>2725</v>
+        <v>2506</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>34</v>
@@ -8844,7 +8844,7 @@
         <v>30</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>885</v>
+        <v>846</v>
       </c>
       <c r="F169" s="2" t="n">
         <v>35</v>
@@ -9032,7 +9032,7 @@
         <v>34</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>994</v>
+        <v>951</v>
       </c>
       <c r="F173" s="2" t="n">
         <v>36</v>
@@ -9220,7 +9220,7 @@
         <v>38</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>1103</v>
+        <v>1058</v>
       </c>
       <c r="F177" s="2" t="n">
         <v>37</v>
@@ -9408,7 +9408,7 @@
         <v>42</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>1237</v>
+        <v>1187</v>
       </c>
       <c r="F181" s="2" t="n">
         <v>38</v>
@@ -9550,10 +9550,10 @@
         <v>1</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="F185" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G185" s="1" t="inlineStr">
         <is>
@@ -9597,10 +9597,10 @@
         <v>2</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>474</v>
+        <v>232</v>
       </c>
       <c r="F186" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G186" s="1" t="inlineStr">
         <is>
@@ -9644,10 +9644,10 @@
         <v>3</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>1063</v>
+        <v>348</v>
       </c>
       <c r="F187" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G187" s="1" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
         <v>4</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>2650</v>
+        <v>464</v>
       </c>
       <c r="F188" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G188" s="1" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>6</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>557</v>
+        <v>526</v>
       </c>
       <c r="F190" s="1" t="n">
         <v>19</v>
@@ -9832,7 +9832,7 @@
         <v>7</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>1357</v>
+        <v>1211</v>
       </c>
       <c r="F191" s="1" t="n">
         <v>19</v>
@@ -9973,7 +9973,7 @@
         <v>10</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>642</v>
+        <v>608</v>
       </c>
       <c r="F194" s="2" t="n">
         <v>20</v>
@@ -10020,7 +10020,7 @@
         <v>11</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>1702</v>
+        <v>1530</v>
       </c>
       <c r="F195" s="2" t="n">
         <v>20</v>
@@ -10161,7 +10161,7 @@
         <v>14</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>742</v>
+        <v>704</v>
       </c>
       <c r="F198" s="2" t="n">
         <v>21</v>
@@ -10208,7 +10208,7 @@
         <v>15</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>2103</v>
+        <v>1902</v>
       </c>
       <c r="F199" s="2" t="n">
         <v>21</v>
@@ -10349,7 +10349,7 @@
         <v>18</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>851</v>
+        <v>809</v>
       </c>
       <c r="F202" s="2" t="n">
         <v>21</v>
@@ -10396,7 +10396,7 @@
         <v>19</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>2581</v>
+        <v>2349</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>21</v>
@@ -10537,7 +10537,7 @@
         <v>22</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>963</v>
+        <v>917</v>
       </c>
       <c r="F206" s="2" t="n">
         <v>22</v>
@@ -10584,7 +10584,7 @@
         <v>23</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>3128</v>
+        <v>2861</v>
       </c>
       <c r="F207" s="2" t="n">
         <v>22</v>
@@ -10725,7 +10725,7 @@
         <v>26</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>1092</v>
+        <v>1042</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>23</v>
@@ -10772,7 +10772,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>3764</v>
+        <v>3461</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>23</v>
@@ -10913,7 +10913,7 @@
         <v>30</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>1222</v>
+        <v>1168</v>
       </c>
       <c r="F214" s="2" t="n">
         <v>23</v>
@@ -11101,7 +11101,7 @@
         <v>34</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>1373</v>
+        <v>1314</v>
       </c>
       <c r="F218" s="2" t="n">
         <v>24</v>
@@ -11289,7 +11289,7 @@
         <v>38</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>1524</v>
+        <v>1460</v>
       </c>
       <c r="F222" s="2" t="n">
         <v>25</v>
@@ -11477,7 +11477,7 @@
         <v>42</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>1708</v>
+        <v>1640</v>
       </c>
       <c r="F226" s="2" t="n">
         <v>25</v>
@@ -11619,10 +11619,10 @@
         <v>1</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>7664</v>
+        <v>4531</v>
       </c>
       <c r="F230" s="1" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G230" s="1" t="inlineStr">
         <is>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14715" windowHeight="11025"/>
+    <workbookView windowWidth="16725" windowHeight="10200"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1184,9 +1184,10 @@
     <col min="6" max="6" width="5.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.95" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.475" style="1" customWidth="1"/>
-    <col min="9" max="10" width="8.91666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.36666666666667" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.4333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.91666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.475" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.93333333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.34166666666667" style="1" customWidth="1"/>
     <col min="13" max="13" width="12.4916666666667" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1" customWidth="1"/>
   </cols>

--- a/Config/MonsterConfig.xlsx
+++ b/Config/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17640" windowHeight="10290"/>
+    <workbookView windowWidth="17640" windowHeight="11355"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -238,7 +238,7 @@
     <t>蝙蝠猫</t>
   </si>
   <si>
-    <t>昼伏夜出,叫声瘆人</t>
+    <t>昼伏夜出,叫声吓人</t>
   </si>
   <si>
     <t>enemy23</t>
